--- a/supplementary/tables/Table_S1.xlsx
+++ b/supplementary/tables/Table_S1.xlsx
@@ -1,2954 +1,2933 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\zwhqd_dcm_hf\supplementary\tables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE9579D-8247-4B21-B9B7-B262B39EDE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="zwhqd_compounds_raw_dcabm" sheetId="1" r:id="rId1"/>
-    <sheet name="zwhqd_compounds_raw_structured" sheetId="2" r:id="rId2"/>
-    <sheet name="zwhqd_compounds_cleaned" sheetId="3" r:id="rId3"/>
+    <sheet name="zwhqd_compounds_raw_dcabm" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="zwhqd_compounds_raw_structured" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="zwhqd_compounds_cleaned" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2953" uniqueCount="967">
-  <si>
-    <t>Herb.Name.Chinese</t>
-  </si>
-  <si>
-    <t>Herb.Name.Pinyin</t>
-  </si>
-  <si>
-    <t>Herb.Name.English</t>
-  </si>
-  <si>
-    <t>Herb.Name.Latin</t>
-  </si>
-  <si>
-    <t>Compounds</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>附子</t>
-  </si>
-  <si>
-    <t>FU ZI</t>
-  </si>
-  <si>
-    <t>Aconiti Lateralis Radix Praeparata</t>
-  </si>
-  <si>
-    <t>Aconitum carmichaelii Debeaux</t>
-  </si>
-  <si>
-    <t>talatisamine(C24H39NO5) (Pubchem CID:159891) (DCABM ID:BC1966_S)|neoline(C24H39NO6) (Pubchem CID:120682) (DCABM ID:BC719_S)|mesaconitine(C33H45NO11) (Pubchem CID:441747) (DCABM ID:BC727_S)|hypaconitine(C33H45NO10) (Pubchem CID:441737) (DCABM ID:BC1167_S)|benzoylmesaconine(C31H43NO10) (Pubchem CID:24832659) (DCABM ID:BC319_S)|benzoylaconine(C32H45NO10) (Pubchem CID:20055771) (DCABM ID:BC167_S)|acetyltalatisamine(C26H41NO6) (Pubchem CID:101596809) (DCABM ID:BC2620_S)|benzoylhypaconine(C31H43NO9) (Pubchem CID:78358526) (DCABM ID:BC268_S)|senbusine c(C24H39NO7) (Pubchem CID:14163819) (DCABM ID:BC623_S)|toroko base ii(C25H41NO6) (Pubchem CID:20055812) (DCABM ID:BC3573_S)|glucuronide conjugation of fuziline(C30H47NO13) (Pubchem CID:-) (DCABM ID:BC2073)|songorine(C22H31NO3) (Pubchem CID:71456946) (DCABM ID:BC3125_S)|senbusine b(C23H37NO6) (Pubchem CID:-) (DCABM ID:BC3240)|senbusine a(C23H37NO6) (Pubchem CID:158048) (DCABM ID:BC2894_S)|6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8,14-pentol(C24H39NO9) (Pubchem CID:76189547) (DCABM ID:BC3153_S)|aconitine(C34H47NO11) (Pubchem CID:245005) (DCABM ID:BC1410_S)|10-hydroxytalatizamine(C24H39NO6) (Pubchem CID:101636479) (DCABM ID:BC2959_S)|sulfate conjugation of unknown(C25H41NO9S) (Pubchem CID:-) (DCABM ID:BC509)|s-cysteine conjugation of unknown(C25H36N2O5S) (Pubchem CID:-) (DCABM ID:BC2370)|s-cysteine conjugation of unknown(C28H46N2O11S) (Pubchem CID:-) (DCABM ID:BC2363)|reduction of unknown(C31H45NO10) (Pubchem CID:-) (DCABM ID:BC545)|reduction of unknown(C22H33NO3) (Pubchem CID:-) (DCABM ID:BC966)|methylation +sulfate conjugation of unknown(C24H39NO9S) (Pubchem CID:-) (DCABM ID:BC1459)|hydroxymethylene loss of unknown(C24H39NO5) (Pubchem CID:-) (DCABM ID:BC1293)|hydroxylation + sulfation of unknown(C24H39NO9S) (Pubchem CID:-) (DCABM ID:BC2904)|hydration of unknown(C25H43NO7) (Pubchem CID:-) (DCABM ID:BC2998)|glycine conjugation of unknown(C27H44N2O7) (Pubchem CID:-) (DCABM ID:BC3556)|glycine conjugation of unknown(C26H42N2O7) (Pubchem CID:-) (DCABM ID:BC1478)|demethylation of unknown(C24H37NO9) (Pubchem CID:-) (DCABM ID:BC1607)|cysteine conjugation of unknown(C28H46N2O7S) (Pubchem CID:-) (DCABM ID:BC1103)|cysteine conjugation of unknown(C28H46N2O10S) (Pubchem CID:-) (DCABM ID:BC3051)|cysteine conjugation of unknown(C27H44N2O6S) (Pubchem CID:-) (DCABM ID:BC1638)|acetylation of unknown(C26H41NO6) (Pubchem CID:-) (DCABM ID:BC2074)|benzoylmesaconitine(C31H43NO10) (Pubchem CID:122173204) (DCABM ID:BC2104_S)|[5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate(C31H43NO9) (Pubchem CID:13343336) (DCABM ID:BC1707_S)|carmicheline(C22H35NO4) (Pubchem CID:441742) (DCABM ID:BC1574_S)|3-deoxyaconitine(C34H47NO10) (Pubchem CID:21598997) (DCABM ID:BC1567_S)|14-o-acetyl-talatisamine(C26H41NO6) (Pubchem CID:156166) (DCABM ID:BC220_S)|20-ethyl-16-methoxy-4-(methoxymethyl)aconitane-1,8,14-triol(C23H37NO5) (Pubchem CID:3084020) (DCABM ID:BC2059_S)|demethylated metabolite of talatizamine(C23H37NO5) (Pubchem CID:-) (DCABM ID:BC1588)|demethylated metabolite of neoline(C23H37NO6) (Pubchem CID:-) (DCABM ID:BC2616)|demethylated metabolite of isotalatizidine(C22H35NO5) (Pubchem CID:-) (DCABM ID:BC1449)|dehydrated benzoylmesaconine(C31H41O9N) (Pubchem CID:-) (DCABM ID:BC2045)|dehydrated benzoylhypaconine(C31H41O8N) (Pubchem CID:-) (DCABM ID:BC2230)|cammaconine(C23H37NO5) (Pubchem CID:441715) (DCABM ID:BC1708_S)|10-oh-mesaconitine(C33H45NO12) (Pubchem CID:78358536) (DCABM ID:BC3530_S)|acetyltalatizamine(C26H41O6N) (Pubchem CID:-) (DCABM ID:BC584)|10-oh-benzoylmesaconine(C31H43O11N) (Pubchem CID:-) (DCABM ID:BC2865)|isotalatisamine(C23H37NO5) (Pubchem CID:-) (DCABM ID:BC3100)|isodelphinine(C33H45NO9) (Pubchem CID:102146471) (DCABM ID:BC43_S)|[(1s,2r,3r,4r,5r,6s,7s,8r,9r,10r,13s,16s,17r,18r)-5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate(C31H43NO9) (Pubchem CID:24832662) (DCABM ID:BC2839_S)|jesaconine(C25H41NO9) (Pubchem CID:20054813) (DCABM ID:BC2434_S)|benzoylhypacoitine(C31H43NO9) (Pubchem CID:3047329) (DCABM ID:BC3088_S)|3,13-deoxybenzoylaconine(C31H44NO8) (Pubchem CID:-) (DCABM ID:BC861)|10-oh-benzoylaconine(C31H43NO11) (Pubchem CID:-) (DCABM ID:BC211)</t>
-  </si>
-  <si>
-    <t>Constituents</t>
-  </si>
-  <si>
-    <t>talatisamine(C24H39NO5) (Pubchem CID:159891) (DCABM ID:BC1966_S)|neoline(C24H39NO6) (Pubchem CID:120682) (DCABM ID:BC719_S)|mesaconitine(C33H45NO11) (Pubchem CID:441747) (DCABM ID:BC727_S)|hypaconitine(C33H45NO10) (Pubchem CID:441737) (DCABM ID:BC1167_S)|benzoylmesaconine(C31H43NO10) (Pubchem CID:24832659) (DCABM ID:BC319_S)|benzoylaconine(C32H45NO10) (Pubchem CID:20055771) (DCABM ID:BC167_S)|acetyltalatisamine(C26H41NO6) (Pubchem CID:101596809) (DCABM ID:BC2620_S)|benzoylhypaconine(C31H43NO9) (Pubchem CID:78358526) (DCABM ID:BC268_S)|senbusine c(C24H39NO7) (Pubchem CID:14163819) (DCABM ID:BC623_S)|toroko base ii(C25H41NO6) (Pubchem CID:20055812) (DCABM ID:BC3573_S)|songorine(C22H31NO3) (Pubchem CID:71456946) (DCABM ID:BC3125_S)|senbusine b(C23H37NO6) (Pubchem CID:-) (DCABM ID:BC3240)|senbusine a(C23H37NO6) (Pubchem CID:158048) (DCABM ID:BC2894_S)|6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8,14-pentol(C24H39NO9) (Pubchem CID:76189547) (DCABM ID:BC3153_S)|aconitine(C34H47NO11) (Pubchem CID:245005) (DCABM ID:BC1410_S)|10-hydroxytalatizamine(C24H39NO6) (Pubchem CID:101636479) (DCABM ID:BC2959_S)|carmicheline(C22H35NO4) (Pubchem CID:441742) (DCABM ID:BC1574_S)|3-deoxyaconitine(C34H47NO10) (Pubchem CID:21598997) (DCABM ID:BC1567_S)|14-o-acetyl-talatisamine(C26H41NO6) (Pubchem CID:156166) (DCABM ID:BC220_S)|20-ethyl-16-methoxy-4-(methoxymethyl)aconitane-1,8,14-triol(C23H37NO5) (Pubchem CID:3084020) (DCABM ID:BC2059_S)|[5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate(C31H43NO9) (Pubchem CID:13343336) (DCABM ID:BC1707_S)</t>
-  </si>
-  <si>
-    <t>Prototype</t>
-  </si>
-  <si>
-    <t>glucuronide conjugation of fuziline(C30H47NO13) (Pubchem CID:-) (DCABM ID:BC2073)|sulfate conjugation of unknown(C25H41NO9S) (Pubchem CID:-) (DCABM ID:BC509)|s-cysteine conjugation of unknown(C25H36N2O5S) (Pubchem CID:-) (DCABM ID:BC2370)|s-cysteine conjugation of unknown(C28H46N2O11S) (Pubchem CID:-) (DCABM ID:BC2363)|reduction of unknown(C31H45NO10) (Pubchem CID:-) (DCABM ID:BC545)|reduction of unknown(C22H33NO3) (Pubchem CID:-) (DCABM ID:BC966)|methylation +sulfate conjugation of unknown(C24H39NO9S) (Pubchem CID:-) (DCABM ID:BC1459)|hydroxymethylene loss of unknown(C24H39NO5) (Pubchem CID:-) (DCABM ID:BC1293)|hydroxylation + sulfation of unknown(C24H39NO9S) (Pubchem CID:-) (DCABM ID:BC2904)|hydration of unknown(C25H43NO7) (Pubchem CID:-) (DCABM ID:BC2998)|glycine conjugation of unknown(C27H44N2O7) (Pubchem CID:-) (DCABM ID:BC3556)|glycine conjugation of unknown(C26H42N2O7) (Pubchem CID:-) (DCABM ID:BC1478)|demethylation of unknown(C24H37NO9) (Pubchem CID:-) (DCABM ID:BC1607)|cysteine conjugation of unknown(C28H46N2O7S) (Pubchem CID:-) (DCABM ID:BC1103)|cysteine conjugation of unknown(C28H46N2O10S) (Pubchem CID:-) (DCABM ID:BC3051)|cysteine conjugation of unknown(C27H44N2O6S) (Pubchem CID:-) (DCABM ID:BC1638)|acetylation of unknown(C26H41NO6) (Pubchem CID:-) (DCABM ID:BC2074)|demethylated metabolite of talatizamine(C23H37NO5) (Pubchem CID:-) (DCABM ID:BC1588)|demethylated metabolite of neoline(C23H37NO6) (Pubchem CID:-) (DCABM ID:BC2616)|demethylated metabolite of isotalatizidine(C22H35NO5) (Pubchem CID:-) (DCABM ID:BC1449)</t>
-  </si>
-  <si>
-    <t>Metabolite</t>
-  </si>
-  <si>
-    <t>黄芪</t>
-  </si>
-  <si>
-    <t>HUANG QI</t>
-  </si>
-  <si>
-    <t>Astragali Radix</t>
-  </si>
-  <si>
-    <t>Astragalus membranaceus (Fisch.) Bunge</t>
-  </si>
-  <si>
-    <t>formononetin(C16H12O4) (Pubchem CID:5280378) (DCABM ID:BC1373_S)|calycosin(C16H12O5) (Pubchem CID:5280448) (DCABM ID:BC2822_S)|sulfate conjugation of unknown(C16H12O7S) (Pubchem CID:-) (DCABM ID:BC409)|s-cysteine conjugation of unknown(C19H17NO7S) (Pubchem CID:-) (DCABM ID:BC652)|hydroxylation + glucuronide conjugation of unknown(C22H20O11) (Pubchem CID:-) (DCABM ID:BC1668)|glucuronide conjugation of unknown(C21H21O9) (Pubchem CID:-) (DCABM ID:BC802)|decarboxylation + glucuronidation of unknown(C21H20O10) (Pubchem CID:-) (DCABM ID:BC635)|ononin(C22H22O9) (Pubchem CID:442813) (DCABM ID:BC1324_S)|methylnissolin(C17H16O5) (Pubchem CID:5319733) (DCABM ID:BC190_S)|calycosin 7-o-glucoside(C22H22O10) (Pubchem CID:5318267) (DCABM ID:BC465_S)|astragaloside iv(C41H68O14) (Pubchem CID:13943297) (DCABM ID:BC2906_S)|9,10-dimethoxypterocarpan-3-o-beta-d-glucoside(C23H26O10) (Pubchem CID:86566448) (DCABM ID:BC1147_S)|(r)-isomucronulatol(C17H18O5) (Pubchem CID:10380176) (DCABM ID:BC1554_S)|astragaloside ii(C43H70O15) (Pubchem CID:13996693) (DCABM ID:BC2112_S)|formononetin 7-o-glucuronide(C22H20O10) (Pubchem CID:71316927) (DCABM ID:BC1923_S)|daidzein-7-o-glucuronide(C21H18O10) (Pubchem CID:11316354) (DCABM ID:BC1514_S)|calycosin-7-β-glucoside-3'-glucuronide(C28H30O16) (Pubchem CID:-) (DCABM ID:BC424)|calycosin-3'-o-glucuronide(C22H20O11) (Pubchem CID:-) (DCABM ID:BC2660)|tyrosine(C9H11NO3) (Pubchem CID:6057) (DCABM ID:BC2240_S)|tryptophan(C11H12N2O2) (Pubchem CID:6305) (DCABM ID:BC542_S)|syringin(C17H24O9) (Pubchem CID:5316860) (DCABM ID:BC2409_S)|syringic acid(C9H10O5) (Pubchem CID:10742) (DCABM ID:BC1295_S)|syringaldehyde(C9H10O4) (Pubchem CID:8655) (DCABM ID:BC3250_S)|soyasaponin i(C48H78O18) (Pubchem CID:122097) (DCABM ID:BC2991_S)|sinapic acid(C11H12O5) (Pubchem CID:637775) (DCABM ID:BC389_S)|rhamnocitrin 3,4'-diglucoside(C28H32O16) (Pubchem CID:44259548) (DCABM ID:BC2934_S)|raffinose(C18H32O16) (Pubchem CID:439242) (DCABM ID:BC3267_S)|pratensein 7-o-glucoside(C22H22O11) (Pubchem CID:44257307) (DCABM ID:BC192_S)|phenylalanine(C9H11NO2) (Pubchem CID:6140) (DCABM ID:BC2196_S)|nicotinic acid(C6H5NO2) (Pubchem CID:938) (DCABM ID:BC3558_S)|markhamioside f(C19H26O13) (Pubchem CID:101182651) (DCABM ID:BC363_S)|leucine(C6H13NO2) (Pubchem CID:6106) (DCABM ID:BC3158_S)|isomucronulatol-2',5'-di-o-glucoside(C29H38O16) (Pubchem CID:-) (DCABM ID:BC2364)|isomucronulatol 7-o-glucoside(C23H28O10) (Pubchem CID:125142) (DCABM ID:BC2238_S)|isomucronulatol 7,2'-di-o-glucoside(C29H38O15) (Pubchem CID:15689653) (DCABM ID:BC2298_S)|isoferulic acid(C10H10O4) (Pubchem CID:736186) (DCABM ID:BC957_S)|isoastragaloside i(C45H72O16) (Pubchem CID:60148697) (DCABM ID:BC1030_S)|hexose(C6H12O6) (Pubchem CID:206) (DCABM ID:BC999_S)|gamma-aminobutyric acid(C4H9NO2) (Pubchem CID:119) (DCABM ID:BC3118_S)|ferulic acid(C10H10O4) (Pubchem CID:445858) (DCABM ID:BC2197_S)|emodin-di-o-glucoside(C27H30O15) (Pubchem CID:-) (DCABM ID:BC1696)|2-(hydroxymethyl)-6-[[3,4,5-trihydroxy-5-(hydroxymethyl)oxolan-2-yl]methoxy]oxane-3,4,5-triol(C12H22O11) (Pubchem CID:3749604) (DCABM ID:BC3220_S)|cosmosiin(C21H20O10) (Pubchem CID:5280704) (DCABM ID:BC2297_S)|nona-2,4-dienoic acid(C9H14O2) (Pubchem CID:54498674) (DCABM ID:BC1786_S)|choline(C5H14NO+) (Pubchem CID:305) (DCABM ID:BC2275_S)|caffeic acid(C9H8O4) (Pubchem CID:689043) (DCABM ID:BC672_S)|azelaic acid(C9H16O4) (Pubchem CID:2266) (DCABM ID:BC3501_S)|wistariasaponin c(C47H76O17) (Pubchem CID:21634074) (DCABM ID:BC2092_S)|astragaloside vii(C47H78O19) (Pubchem CID:14241100) (DCABM ID:BC1153_S)|astragaloside vi(C47H78O19) (Pubchem CID:71448940) (DCABM ID:BC2412_S)|astragaloside v(C47H78O19) (Pubchem CID:71448939) (DCABM ID:BC3423_S)|astragaloside iii(C41H68O14) (Pubchem CID:441905) (DCABM ID:BC3608_S)|astrasieversianin iv(C45H72O16) (Pubchem CID:13996685) (DCABM ID:BC1413_S)|asparagine(C4H8N2O3) (Pubchem CID:6267) (DCABM ID:BC3092_S)|adenosine(C10H13N5O4) (Pubchem CID:60961) (DCABM ID:BC910_S)|acetyl astragaloside i(C47H74O17) (Pubchem CID:-) (DCABM ID:BC3342)|6''-o-acetylononin(C24H24O10) (Pubchem CID:102463148) (DCABM ID:BC324_S)|3,4-dihydroxybenzoic acid(C7H6O4) (Pubchem CID:72) (DCABM ID:BC3682_S)|cyclocanthoside e(C41H70O14) (Pubchem CID:21633193) (DCABM ID:BC451_S)|sulfated isomucronulatol(C17H18O8S) (Pubchem CID:-) (DCABM ID:BC142)|sulfated formononetin(C16H12O7S) (Pubchem CID:-) (DCABM ID:BC3277)|sulfated calycosin(C16H12O8S) (Pubchem CID:-) (DCABM ID:BC2760)|rhamnocitrin(C16H12O6) (Pubchem CID:5320946) (DCABM ID:BC2623_S)|isomucronulatol(C17H18O5) (Pubchem CID:602152) (DCABM ID:BC3021_S)|glucuronidated rhamnocitrin(C22H20O12) (Pubchem CID:-) (DCABM ID:BC2650)|glucuronidated isomucronulatol(C23H26O11) (Pubchem CID:-) (DCABM ID:BC3336)|formononetin 7-glucuronide(C22H20O10) (Pubchem CID:101220281) (DCABM ID:BC3241_S)|glucuronidated calycosin(C22H20O11) (Pubchem CID:-) (DCABM ID:BC934)|betaine(C5H11NO2) (Pubchem CID:247) (DCABM ID:BC109_S)|5-hydroxy-7,8-dimethoxyflavanone + glucuronide conjugation(C23H24O11) (Pubchem CID:-) (DCABM ID:BC2717)|isomer of 3-hydro-9, 10-dimethoxypterocarpan(C17H16O5) (Pubchem CID:-) (DCABM ID:BC128)|daidzein(C15H10O4) (Pubchem CID:5281708) (DCABM ID:BC33_S)|hydroxylation of calycosin(C16H12O6) (Pubchem CID:-) (DCABM ID:BC714)|glucuronic acid conjugate of formononetin(C22H20O10) (Pubchem CID:-) (DCABM ID:BC22)|glucuronic acid conjugate of demethylcalycosin(C21H18O11) (Pubchem CID:-) (DCABM ID:BC3376)|glucuronic acid conjugate of daidzein(C21H18O10) (Pubchem CID:-) (DCABM ID:BC1536)|glucuronic acid conjugate of calycosin(C22H20O11) (Pubchem CID:-) (DCABM ID:BC174)|glucuronic acid conjugate of 3-hydro-9, 10-dimp(C23H24O11) (Pubchem CID:-) (DCABM ID:BC2495)|kaempferitrin(C27H30O14) (Pubchem CID:5486199) (DCABM ID:BC1938_S)|astragaloside-ii(C41H66O15) (Pubchem CID:71306915) (DCABM ID:BC1611_S)|3,4-dihydro-3-(2-hydroxy-3,4-dimethoxyphenyl)-2h-1-benzopyran-7-yl beta-d-glucopyranoside(C23H28O10) (Pubchem CID:53461957) (DCABM ID:BC2635_S)|wogonin(C16H12O5) (Pubchem CID:5281703) (DCABM ID:BC89_S)|nicotiflorin(C27H30O15) (Pubchem CID:5318767) (DCABM ID:BC2356_S)</t>
-  </si>
-  <si>
-    <t>formononetin(C16H12O4) (Pubchem CID:5280378) (DCABM ID:BC1373_S)|calycosin(C16H12O5) (Pubchem CID:5280448) (DCABM ID:BC2822_S)|tyrosine(C9H11NO3) (Pubchem CID:6057) (DCABM ID:BC2240_S)|tryptophan(C11H12N2O2) (Pubchem CID:6305) (DCABM ID:BC542_S)|syringin(C17H24O9) (Pubchem CID:5316860) (DCABM ID:BC2409_S)|syringic acid(C9H10O5) (Pubchem CID:10742) (DCABM ID:BC1295_S)|syringaldehyde(C9H10O4) (Pubchem CID:8655) (DCABM ID:BC3250_S)|soyasaponin i(C48H78O18) (Pubchem CID:122097) (DCABM ID:BC2991_S)|sinapic acid(C11H12O5) (Pubchem CID:637775) (DCABM ID:BC389_S)|rhamnocitrin 3,4'-diglucoside(C28H32O16) (Pubchem CID:44259548) (DCABM ID:BC2934_S)|raffinose(C18H32O16) (Pubchem CID:439242) (DCABM ID:BC3267_S)|pratensein 7-o-glucoside(C22H22O11) (Pubchem CID:44257307) (DCABM ID:BC192_S)|phenylalanine(C9H11NO2) (Pubchem CID:6140) (DCABM ID:BC2196_S)|ononin(C22H22O9) (Pubchem CID:442813) (DCABM ID:BC1324_S)|nicotinic acid(C6H5NO2) (Pubchem CID:938) (DCABM ID:BC3558_S)|markhamioside f(C19H26O13) (Pubchem CID:101182651) (DCABM ID:BC363_S)|leucine(C6H13NO2) (Pubchem CID:6106) (DCABM ID:BC3158_S)|isomucronulatol-2',5'-di-o-glucoside(C29H38O16) (Pubchem CID:-) (DCABM ID:BC2364)|isomucronulatol 7-o-glucoside(C23H28O10) (Pubchem CID:125142) (DCABM ID:BC2238_S)|isomucronulatol 7,2'-di-o-glucoside(C29H38O15) (Pubchem CID:15689653) (DCABM ID:BC2298_S)|isoferulic acid(C10H10O4) (Pubchem CID:736186) (DCABM ID:BC957_S)|isoastragaloside i(C45H72O16) (Pubchem CID:60148697) (DCABM ID:BC1030_S)|hexose(C6H12O6) (Pubchem CID:206) (DCABM ID:BC999_S)|gamma-aminobutyric acid(C4H9NO2) (Pubchem CID:119) (DCABM ID:BC3118_S)|ferulic acid(C10H10O4) (Pubchem CID:445858) (DCABM ID:BC2197_S)|emodin-di-o-glucoside(C27H30O15) (Pubchem CID:-) (DCABM ID:BC1696)|2-(hydroxymethyl)-6-[[3,4,5-trihydroxy-5-(hydroxymethyl)oxolan-2-yl]methoxy]oxane-3,4,5-triol(C12H22O11) (Pubchem CID:3749604) (DCABM ID:BC3220_S)|cosmosiin(C21H20O10) (Pubchem CID:5280704) (DCABM ID:BC2297_S)|nona-2,4-dienoic acid(C9H14O2) (Pubchem CID:54498674) (DCABM ID:BC1786_S)|choline(C5H14NO+) (Pubchem CID:305) (DCABM ID:BC2275_S)|calycosin 7-o-glucoside(C22H22O10) (Pubchem CID:5318267) (DCABM ID:BC465_S)|caffeic acid(C9H8O4) (Pubchem CID:689043) (DCABM ID:BC672_S)|azelaic acid(C9H16O4) (Pubchem CID:2266) (DCABM ID:BC3501_S)|wistariasaponin c(C47H76O17) (Pubchem CID:21634074) (DCABM ID:BC2092_S)|astragaloside vii(C47H78O19) (Pubchem CID:14241100) (DCABM ID:BC1153_S)|astragaloside vi(C47H78O19) (Pubchem CID:71448940) (DCABM ID:BC2412_S)|astragaloside v(C47H78O19) (Pubchem CID:71448939) (DCABM ID:BC3423_S)|astragaloside iv(C41H68O14) (Pubchem CID:13943297) (DCABM ID:BC2906_S)|astragaloside iii(C41H68O14) (Pubchem CID:441905) (DCABM ID:BC3608_S)|astragaloside ii(C43H70O15) (Pubchem CID:13996693) (DCABM ID:BC2112_S)|astrasieversianin iv(C45H72O16) (Pubchem CID:13996685) (DCABM ID:BC1413_S)|asparagine(C4H8N2O3) (Pubchem CID:6267) (DCABM ID:BC3092_S)|adenosine(C10H13N5O4) (Pubchem CID:60961) (DCABM ID:BC910_S)|acetyl astragaloside i(C47H74O17) (Pubchem CID:-) (DCABM ID:BC3342)|9,10-dimethoxypterocarpan-3-o-beta-d-glucoside(C23H26O10) (Pubchem CID:86566448) (DCABM ID:BC1147_S)|6''-o-acetylononin(C24H24O10) (Pubchem CID:102463148) (DCABM ID:BC324_S)|3,4-dihydroxybenzoic acid(C7H6O4) (Pubchem CID:72) (DCABM ID:BC3682_S)|cyclocanthoside e(C41H70O14) (Pubchem CID:21633193) (DCABM ID:BC451_S)|betaine(C5H11NO2) (Pubchem CID:247) (DCABM ID:BC109_S)|isomer of 3-hydro-9, 10-dimethoxypterocarpan(C17H16O5) (Pubchem CID:-) (DCABM ID:BC128)|daidzein(C15H10O4) (Pubchem CID:5281708) (DCABM ID:BC33_S)</t>
-  </si>
-  <si>
-    <t>sulfate conjugation of unknown(C16H12O7S) (Pubchem CID:-) (DCABM ID:BC409)|s-cysteine conjugation of unknown(C19H17NO7S) (Pubchem CID:-) (DCABM ID:BC652)|hydroxylation + glucuronide conjugation of unknown(C22H20O11) (Pubchem CID:-) (DCABM ID:BC1668)|glucuronide conjugation of unknown(C21H21O9) (Pubchem CID:-) (DCABM ID:BC802)|decarboxylation + glucuronidation of unknown(C21H20O10) (Pubchem CID:-) (DCABM ID:BC635)|sulfated isomucronulatol(C17H18O8S) (Pubchem CID:-) (DCABM ID:BC142)|sulfated formononetin(C16H12O7S) (Pubchem CID:-) (DCABM ID:BC3277)|sulfated calycosin(C16H12O8S) (Pubchem CID:-) (DCABM ID:BC2760)|rhamnocitrin(C16H12O6) (Pubchem CID:5320946) (DCABM ID:BC2623_S)|isomucronulatol(C17H18O5) (Pubchem CID:602152) (DCABM ID:BC3021_S)|glucuronidated rhamnocitrin(C22H20O12) (Pubchem CID:-) (DCABM ID:BC2650)|glucuronidated isomucronulatol(C23H26O11) (Pubchem CID:-) (DCABM ID:BC3336)|formononetin 7-glucuronide(C22H20O10) (Pubchem CID:101220281) (DCABM ID:BC3241_S)|glucuronidated calycosin(C22H20O11) (Pubchem CID:-) (DCABM ID:BC934)|5-hydroxy-7,8-dimethoxyflavanone + glucuronide conjugation(C23H24O11) (Pubchem CID:-) (DCABM ID:BC2717)|hydroxylation of calycosin(C16H12O6) (Pubchem CID:-) (DCABM ID:BC714)|glucuronic acid conjugate of formononetin(C22H20O10) (Pubchem CID:-) (DCABM ID:BC22)|glucuronic acid conjugate of demethylcalycosin(C21H18O11) (Pubchem CID:-) (DCABM ID:BC3376)|glucuronic acid conjugate of daidzein(C21H18O10) (Pubchem CID:-) (DCABM ID:BC1536)|glucuronic acid conjugate of calycosin(C22H20O11) (Pubchem CID:-) (DCABM ID:BC174)|glucuronic acid conjugate of 3-hydro-9, 10-dimp(C23H24O11) (Pubchem CID:-) (DCABM ID:BC2495)|(r)-isomucronulatol(C17H18O5) (Pubchem CID:10380176) (DCABM ID:BC1554_S)</t>
-  </si>
-  <si>
-    <t>白术</t>
-  </si>
-  <si>
-    <t>BAI ZHU</t>
-  </si>
-  <si>
-    <t>Atractylodis Macrocephalae Rhizoma</t>
-  </si>
-  <si>
-    <t>Atractylodes macrocephala Koidz.</t>
-  </si>
-  <si>
-    <t>umbelliferone(C9H6O3) (Pubchem CID:5281426) (DCABM ID:BC2631_S)|atractylenolide ii(C15H20O2) (Pubchem CID:14448070) (DCABM ID:BC1972_S)|atractylenolide i(C15H18O2) (Pubchem CID:5321018) (DCABM ID:BC1945_S)|atractylenolide iii(C15H20O3) (Pubchem CID:155948) (DCABM ID:BC206_S)</t>
-  </si>
-  <si>
-    <t>茯苓</t>
-  </si>
-  <si>
-    <t>FU LING</t>
-  </si>
-  <si>
-    <t>Poria Cocos</t>
-  </si>
-  <si>
-    <t>Poria cocos (Schw.) Wolf</t>
-  </si>
-  <si>
-    <t>vanillin(C8H8O3) (Pubchem CID:1183) (DCABM ID:BC2864_S)|sucrose(C12H22O11) (Pubchem CID:5988) (DCABM ID:BC2506_S)|succinic acid(C4H6O4) (Pubchem CID:1110) (DCABM ID:BC3362_S)|3,4-dihydroxybenzoic acid(C7H6O4) (Pubchem CID:72) (DCABM ID:BC3682_S)|d-mannose(C6H12O6) (Pubchem CID:18950) (DCABM ID:BC496_S)|citric acid(C6H8O7) (Pubchem CID:311) (DCABM ID:BC171_S)|azelaic acid(C9H16O4) (Pubchem CID:2266) (DCABM ID:BC3501_S)|3-tert-butyladipic acid(C10H18O4) (Pubchem CID:98967) (DCABM ID:BC176_S)|oxidation,glucuronide conjugation of benzoic acid(C13H14O9) (Pubchem CID:-) (DCABM ID:BC2642)|dehydrotumulosic acid(C31H48O4) (Pubchem CID:15225964) (DCABM ID:BC2465_S)|2-[(2r,3r,3ar,6s,7s,9br)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid(C30H44O5) (Pubchem CID:3086648) (DCABM ID:BC186_S)|3β,16α- dihydroxylanostene-triene-21-acid(C30H46O4) (Pubchem CID:-) (DCABM ID:BC1483)|poricoic acid e(C30H44O6) (Pubchem CID:15225966) (DCABM ID:BC1246_S)|tumulosic acid(C31H50O4) (Pubchem CID:12314446) (DCABM ID:BC1732_S)|dehydropachymic acid(C33H50O5) (Pubchem CID:15226717) (DCABM ID:BC373_S)|poricoic acid h(C31H48O5) (Pubchem CID:10918099) (DCABM ID:BC539_S)|poricoic acid g(C30H46O5) (Pubchem CID:5471966) (DCABM ID:BC2007_S)|fomefficinic acid a(C31H48O3) (Pubchem CID:11431307) (DCABM ID:BC1561_S)|daedaleanic acid a(C31H46O4) (Pubchem CID:11179164) (DCABM ID:BC1869_S)|adenine(C5H5N5) (Pubchem CID:190) (DCABM ID:BC3652_S)|3β-hydroxy-16α-acetoxy-lanosta-7,9(11),24-trien-21-oic acid(C32H48O5) (Pubchem CID:-) (DCABM ID:BC2201)|3β,16α-dihydroxylanosta-7,9(11),24-trien-21-oic acid(C30H46O4) (Pubchem CID:-) (DCABM ID:BC333)|6,7-dehydroporicoic acid h(C31H46O5) (Pubchem CID:44556878) (DCABM ID:BC3636_S)|16-deoxyporicoic acid b(C30H44O4) (Pubchem CID:16736458) (DCABM ID:BC811_S)|(r)-dimethyl 2-hydroxysuccinate(C6H10O5) (Pubchem CID:11062697) (DCABM ID:BC2757_S)|unknown(C33H48O4) (Pubchem CID:-) (DCABM ID:BC2224)|(5ξ,20s)-24- methylene-3- oxolanosta-7,9(11)- dien-21-oic acid(C31H46O3) (Pubchem CID:-) (DCABM ID:BC2214)|trametenolic acid(C30H48O3) (Pubchem CID:12309443) (DCABM ID:BC2079_S)|poricoic acid f(C31H46O6) (Pubchem CID:101928114) (DCABM ID:BC1176_S)|poricoic acid am(C32H48O5) (Pubchem CID:46882717) (DCABM ID:BC1279_S)|(2r)-2-[(3s,5r,10s,13r,14r,16r,17r)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid(C30H46O5) (Pubchem CID:137648664) (DCABM ID:BC1974_S)|(2r)-2-[(3r,5r,10s,13r,14r,16r,17r)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid(C30H46O5) (Pubchem CID:137654023) (DCABM ID:BC664_S)|polyporenic acid c(C31H46O4) (Pubchem CID:9805290) (DCABM ID:BC2675_S)|pachymic acid(C33H52O5) (Pubchem CID:5484385) (DCABM ID:BC3085_S)|eburicoic acid(C31H50O3) (Pubchem CID:73402) (DCABM ID:BC1971_S)|6-hydroxy-dehydrotumulosic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC571)|3β-hydroxy-16-acetoxylanosta-7,-9(11)-24-trien-21-oic acid(C32H48O5) (Pubchem CID:-) (DCABM ID:BC836)|3β,16α-dihydroxy-lanosta-8,24-dien-21-oic acid(C30H48O4) (Pubchem CID:-) (DCABM ID:BC2049)|3β,16α-dihydroxy-7-oxolanosta-8,24-dien-21-oic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC138)|3α,16β-dihydroxylanosta-7,9(11),24-trien-21-oic acid(C30H46O4) (Pubchem CID:-) (DCABM ID:BC3308)|3-oxo-16α-hydroxylanosta-7,9(11),24-trien-21-oic acid(C31H44O4) (Pubchem CID:-) (DCABM ID:BC1586)|3-o-acetyl-16α,26-dihydroxytrametenolic acid(C32H50O6) (Pubchem CID:-) (DCABM ID:BC1438)|3-o-acetyl-16alpha-hydroxytrametenolic acid(C32H50O5) (Pubchem CID:15226712) (DCABM ID:BC2731_S)|3-o-16α,25-dihydroxy-lanosta-8,24(3)-dieen-21-oic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC1057)|3-epidehydrotumulosic acid(C31H48O4) (Pubchem CID:10005581) (DCABM ID:BC514_S)|3-epidehydropachymic acid(C33H50O5) (Pubchem CID:15226716) (DCABM ID:BC2875_S)|3-epi-(3'-hydroxy-3'-methylglutaryloxyl)-dehydrotum ulosic acid(C37H56O8) (Pubchem CID:-) (DCABM ID:BC2949)|3-dehydrotrametenolic acid(C30H46O3) (Pubchem CID:15391340) (DCABM ID:BC3203_S)|29-hydroxydehydropachymic acid(C33H50O6) (Pubchem CID:137355885) (DCABM ID:BC54_S)|26-hydroxy-poricoic acid g(C30H46O6) (Pubchem CID:-) (DCABM ID:BC1196)|26-hydroxy-dehydrotumuloosic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC1698)|25α-hydroxytumulosic acid(C31H50O5) (Pubchem CID:-) (DCABM ID:BC1530)|25-hydroxytumulosic acid(C31H50O5) (Pubchem CID:-) (DCABM ID:BC1838)|25-hydroxyporicoic acid h(C31H48O6) (Pubchem CID:16736865) (DCABM ID:BC1420_S)|25-hydroxypachymic acid(C33H52O6) (Pubchem CID:-) (DCABM ID:BC1594)|25-hydroxl-3β,16α-diacetoxylanosta-8-en-21-oic acid(C35H54O7) (Pubchem CID:-) (DCABM ID:BC1714)|25-hydroxyporicoic acid c(C31H46O5) (Pubchem CID:44556811) (DCABM ID:BC1079_S)|16α,25-hydroxydehydroeburicoinic acid(C31H46O5) (Pubchem CID:-) (DCABM ID:BC1626)|daedaleanic acid b(C30H48O5) (Pubchem CID:11465951) (DCABM ID:BC2276_S)|poricoic acid ce(C33H50O4) (Pubchem CID:102480393) (DCABM ID:BC3473_S)|tumulosic acid +o(C31H50O5) (Pubchem CID:-) (DCABM ID:BC3266)|trametenolic acid+o2-h2(C30H46O5) (Pubchem CID:-) (DCABM ID:BC726)|trametenolic acid+o2(C30H48O5) (Pubchem CID:-) (DCABM ID:BC2563)|poricoic bm+o-h2(C32H48O5) (Pubchem CID:-) (DCABM ID:BC2771)|poricoic b+o(C31H46O5) (Pubchem CID:-) (DCABM ID:BC2560)|poricoic acid h+o(C31H46O6) (Pubchem CID:-) (DCABM ID:BC2183)|polyporenic acid c+o(C31H46O5) (Pubchem CID:-) (DCABM ID:BC2857)|hydroxyporicoic acid h+o(C31H48O6) (Pubchem CID:-) (DCABM ID:BC3372)|eburiconic acid+o2-h2(C31H48O4) (Pubchem CID:-) (DCABM ID:BC378)|eburiconic acid +o(C31H50O4) (Pubchem CID:-) (DCABM ID:BC2699)|dehydrotumulosic acid+o-2h(C31H46O5) (Pubchem CID:-) (DCABM ID:BC2674)|dehydrotumulosic acid+2o-2h(C31H46O6) (Pubchem CID:-) (DCABM ID:BC1527)|dehydrotumulosic acid+o2(C31H48O6) (Pubchem CID:-) (DCABM ID:BC1630)|dehydrotumulosic acid +o(C31H48O5) (Pubchem CID:-) (DCABM ID:BC2885)|dehydrotrametenoic acid +o-h2(C30H46O4) (Pubchem CID:-) (DCABM ID:BC1856)|dehydrotrametenoic acid +o(C30H48O4) (Pubchem CID:-) (DCABM ID:BC1296)|16-oxy-acetoxypachymic acid methyl ester)(C36H56O6) (Pubchem CID:-) (DCABM ID:BC107)|16-oxy-acetoxypachymic acid(C35H54O6) (Pubchem CID:-) (DCABM ID:BC3218)|ursolic acid acetate(C32H50O4) (Pubchem CID:6475119) (DCABM ID:BC3306_S)|methyl (2r)-2-[(3s,5r,10s,13r,14r,16r,17r)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoate(C34H54O5) (Pubchem CID:72202422) (DCABM ID:BC2006_S)|pachymic acid c(C31H46O4) (Pubchem CID:-) (DCABM ID:BC1316)</t>
-  </si>
-  <si>
-    <t>vanillin(C8H8O3) (Pubchem CID:1183) (DCABM ID:BC2864_S)|sucrose(C12H22O11) (Pubchem CID:5988) (DCABM ID:BC2506_S)|succinic acid(C4H6O4) (Pubchem CID:1110) (DCABM ID:BC3362_S)|3,4-dihydroxybenzoic acid(C7H6O4) (Pubchem CID:72) (DCABM ID:BC3682_S)|d-mannose(C6H12O6) (Pubchem CID:18950) (DCABM ID:BC496_S)|citric acid(C6H8O7) (Pubchem CID:311) (DCABM ID:BC171_S)|azelaic acid(C9H16O4) (Pubchem CID:2266) (DCABM ID:BC3501_S)|3-tert-butyladipic acid(C10H18O4) (Pubchem CID:98967) (DCABM ID:BC176_S)|dehydrotumulosic acid(C31H48O4) (Pubchem CID:15225964) (DCABM ID:BC2465_S)|2-[(2r,3r,3ar,6s,7s,9br)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid(C30H44O5) (Pubchem CID:3086648) (DCABM ID:BC186_S)|3β,16α- dihydroxylanostene-triene-21-acid(C30H46O4) (Pubchem CID:-) (DCABM ID:BC1483)|poricoic acid e(C30H44O6) (Pubchem CID:15225966) (DCABM ID:BC1246_S)|tumulosic acid(C31H50O4) (Pubchem CID:12314446) (DCABM ID:BC1732_S)|poricoic acid h(C31H48O5) (Pubchem CID:10918099) (DCABM ID:BC539_S)|poricoic acid g(C30H46O5) (Pubchem CID:5471966) (DCABM ID:BC2007_S)|fomefficinic acid a(C31H48O3) (Pubchem CID:11431307) (DCABM ID:BC1561_S)|daedaleanic acid a(C31H46O4) (Pubchem CID:11179164) (DCABM ID:BC1869_S)|adenine(C5H5N5) (Pubchem CID:190) (DCABM ID:BC3652_S)|3β-hydroxy-16α-acetoxy-lanosta-7,9(11),24-trien-21-oic acid(C32H48O5) (Pubchem CID:-) (DCABM ID:BC2201)|3β,16α-dihydroxylanosta-7,9(11),24-trien-21-oic acid(C30H46O4) (Pubchem CID:-) (DCABM ID:BC333)|6,7-dehydroporicoic acid h(C31H46O5) (Pubchem CID:44556878) (DCABM ID:BC3636_S)|16-deoxyporicoic acid b(C30H44O4) (Pubchem CID:16736458) (DCABM ID:BC811_S)|(r)-dimethyl 2-hydroxysuccinate(C6H10O5) (Pubchem CID:11062697) (DCABM ID:BC2757_S)|trametenolic acid(C30H48O3) (Pubchem CID:12309443) (DCABM ID:BC2079_S)|poricoic acid f(C31H46O6) (Pubchem CID:101928114) (DCABM ID:BC1176_S)|poricoic acid am(C32H48O5) (Pubchem CID:46882717) (DCABM ID:BC1279_S)|(2r)-2-[(3s,5r,10s,13r,14r,16r,17r)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid(C30H46O5) (Pubchem CID:137648664) (DCABM ID:BC1974_S)|(2r)-2-[(3r,5r,10s,13r,14r,16r,17r)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid(C30H46O5) (Pubchem CID:137654023) (DCABM ID:BC664_S)|polyporenic acid c(C31H46O4) (Pubchem CID:9805290) (DCABM ID:BC2675_S)|pachymic acid(C33H52O5) (Pubchem CID:5484385) (DCABM ID:BC3085_S)|eburicoic acid(C31H50O3) (Pubchem CID:73402) (DCABM ID:BC1971_S)|dehydropachymic acid(C33H50O5) (Pubchem CID:15226717) (DCABM ID:BC373_S)|6-hydroxy-dehydrotumulosic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC571)|3β-hydroxy-16-acetoxylanosta-7,-9(11)-24-trien-21-oic acid(C32H48O5) (Pubchem CID:-) (DCABM ID:BC836)|3β,16α-dihydroxy-lanosta-8,24-dien-21-oic acid(C30H48O4) (Pubchem CID:-) (DCABM ID:BC2049)|3β,16α-dihydroxy-7-oxolanosta-8,24-dien-21-oic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC138)|3α,16β-dihydroxylanosta-7,9(11),24-trien-21-oic acid(C30H46O4) (Pubchem CID:-) (DCABM ID:BC3308)|3-oxo-16α-hydroxylanosta-7,9(11),24-trien-21-oic acid(C31H44O4) (Pubchem CID:-) (DCABM ID:BC1586)|3-o-acetyl-16α,26-dihydroxytrametenolic acid(C32H50O6) (Pubchem CID:-) (DCABM ID:BC1438)|3-o-acetyl-16alpha-hydroxytrametenolic acid(C32H50O5) (Pubchem CID:15226712) (DCABM ID:BC2731_S)|3-o-16α,25-dihydroxy-lanosta-8,24(3)-dieen-21-oic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC1057)|3-epidehydrotumulosic acid(C31H48O4) (Pubchem CID:10005581) (DCABM ID:BC514_S)|3-epidehydropachymic acid(C33H50O5) (Pubchem CID:15226716) (DCABM ID:BC2875_S)|3-epi-(3'-hydroxy-3'-methylglutaryloxyl)-dehydrotum ulosic acid(C37H56O8) (Pubchem CID:-) (DCABM ID:BC2949)|3-dehydrotrametenolic acid(C30H46O3) (Pubchem CID:15391340) (DCABM ID:BC3203_S)|29-hydroxydehydropachymic acid(C33H50O6) (Pubchem CID:137355885) (DCABM ID:BC54_S)|26-hydroxy-poricoic acid g(C30H46O6) (Pubchem CID:-) (DCABM ID:BC1196)|26-hydroxy-dehydrotumuloosic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC1698)|25α-hydroxytumulosic acid(C31H50O5) (Pubchem CID:-) (DCABM ID:BC1530)|25-hydroxytumulosic acid(C31H50O5) (Pubchem CID:-) (DCABM ID:BC1838)|25-hydroxyporicoic acid h(C31H48O6) (Pubchem CID:16736865) (DCABM ID:BC1420_S)|25-hydroxypachymic acid(C33H52O6) (Pubchem CID:-) (DCABM ID:BC1594)|25-hydroxl-3β,16α-diacetoxylanosta-8-en-21-oic acid(C35H54O7) (Pubchem CID:-) (DCABM ID:BC1714)|25-hydroxyporicoic acid c(C31H46O5) (Pubchem CID:44556811) (DCABM ID:BC1079_S)|16α,25-hydroxydehydroeburicoinic acid(C31H46O5) (Pubchem CID:-) (DCABM ID:BC1626)|daedaleanic acid b(C30H48O5) (Pubchem CID:11465951) (DCABM ID:BC2276_S)|poricoic acid ce(C33H50O4) (Pubchem CID:102480393) (DCABM ID:BC3473_S)|ursolic acid acetate(C32H50O4) (Pubchem CID:6475119) (DCABM ID:BC3306_S)|pachymic acid c(C31H46O4) (Pubchem CID:-) (DCABM ID:BC1316)</t>
-  </si>
-  <si>
-    <t>oxidation,glucuronide conjugation of benzoic acid(C13H14O9) (Pubchem CID:-) (DCABM ID:BC2642)|tumulosic acid(C31H50O4) (Pubchem CID:12314446) (DCABM ID:BC1732_S)|dehydropachymic acid(C33H50O5) (Pubchem CID:15226717) (DCABM ID:BC373_S)|unknown(C33H48O4) (Pubchem CID:-) (DCABM ID:BC2224)|(5ξ,20s)-24- methylene-3- oxolanosta-7,9(11)- dien-21-oic acid(C31H46O3) (Pubchem CID:-) (DCABM ID:BC2214)|tumulosic acid +o(C31H50O5) (Pubchem CID:-) (DCABM ID:BC3266)|trametenolic acid+o2-h2(C30H46O5) (Pubchem CID:-) (DCABM ID:BC726)|trametenolic acid+o2(C30H48O5) (Pubchem CID:-) (DCABM ID:BC2563)|poricoic bm+o-h2(C32H48O5) (Pubchem CID:-) (DCABM ID:BC2771)|poricoic b+o(C31H46O5) (Pubchem CID:-) (DCABM ID:BC2560)|poricoic acid h+o(C31H46O6) (Pubchem CID:-) (DCABM ID:BC2183)|polyporenic acid c+o(C31H46O5) (Pubchem CID:-) (DCABM ID:BC2857)|hydroxyporicoic acid h+o(C31H48O6) (Pubchem CID:-) (DCABM ID:BC3372)|eburiconic acid+o2-h2(C31H48O4) (Pubchem CID:-) (DCABM ID:BC378)|eburiconic acid +o(C31H50O4) (Pubchem CID:-) (DCABM ID:BC2699)|dehydrotumulosic acid+o-2h(C31H46O5) (Pubchem CID:-) (DCABM ID:BC2674)|dehydrotumulosic acid+2o-2h(C31H46O6) (Pubchem CID:-) (DCABM ID:BC1527)|dehydrotumulosic acid+o2(C31H48O6) (Pubchem CID:-) (DCABM ID:BC1630)|dehydrotumulosic acid +o(C31H48O5) (Pubchem CID:-) (DCABM ID:BC2885)|dehydrotrametenoic acid +o-h2(C30H46O4) (Pubchem CID:-) (DCABM ID:BC1856)|dehydrotrametenoic acid +o(C30H48O4) (Pubchem CID:-) (DCABM ID:BC1296)|2-[(2r,3r,3ar,6s,7s,9br)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid(C30H44O5) (Pubchem CID:3086648) (DCABM ID:BC186_S)|3β-hydroxy-16-acetoxylanosta-7,-9(11)-24-trien-21-oic acid(C32H48O5) (Pubchem CID:-) (DCABM ID:BC836)|3-dehydrotrametenolic acid(C30H46O3) (Pubchem CID:15391340) (DCABM ID:BC3203_S)|16-oxy-acetoxypachymic acid methyl ester)(C36H56O6) (Pubchem CID:-) (DCABM ID:BC107)|16-oxy-acetoxypachymic acid(C35H54O6) (Pubchem CID:-) (DCABM ID:BC3218)</t>
-  </si>
-  <si>
-    <t>白芍</t>
-  </si>
-  <si>
-    <t>BAI SHAO</t>
-  </si>
-  <si>
-    <t>Paeoniae Radix Alba</t>
-  </si>
-  <si>
-    <t>Paeonia lactiflora Pall.</t>
-  </si>
-  <si>
-    <t>paeoniflorin(C23H28O11) (Pubchem CID:442534) (DCABM ID:BC1367_S)|desbenzoylpaeoniflorin(C16H24O10) (Pubchem CID:-) (DCABM ID:BC741)|pinellic acid(C18H34O5) (Pubchem CID:9858729) (DCABM ID:BC3302_S)|oxidation of unknown(C23H28O12) (Pubchem CID:-) (DCABM ID:BC1984)|methylation of unknown(C24H30O11) (Pubchem CID:-) (DCABM ID:BC622)|glucuronide conjugation of unknown(C29H36O17) (Pubchem CID:-) (DCABM ID:BC5)|gallic acid(C7H6O5) (Pubchem CID:370) (DCABM ID:BC2804_S)|cianidanol(C15H14O6) (Pubchem CID:9064) (DCABM ID:BC3510_S)|[(1r,4r)-4-hydroxy-6-methyl-8-oxo-1-[(2s,3r,4s,5s,6r)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-7-oxatricyclo[4.3.0.03,9]nonan-9-yl]methyl benzoate(C23H28O11) (Pubchem CID:51346141) (DCABM ID:BC3242_S)|(-)-epicatechin(C15H14O6) (Pubchem CID:72276) (DCABM ID:BC2294_S)|gallic acid glucuronide(C13H14O11) (Pubchem CID:-) (DCABM ID:BC1220)|ferulic acid 4-sulfate(C10H10O7S) (Pubchem CID:6305574) (DCABM ID:BC3254_S)|3'-o-methyl (epi)catechin 7- or 4'-o-glucuronide(C22H24O12) (Pubchem CID:-) (DCABM ID:BC1507)|3-methoxy-4-hydroxy-phenylpropionic acid sulfate(C10H12O7S) (Pubchem CID:-) (DCABM ID:BC2704)|unknown(C9H10O3) (Pubchem CID:-) (DCABM ID:BC2922)|oxypaeoniflora(C23H28O12) (Pubchem CID:21631105) (DCABM ID:BC388_S)|paeoniflorin sulfonate(C23H28O14S) (Pubchem CID:101382399) (DCABM ID:BC245_S)|galloyl paeoniflorin or galloylalbiflorin(C30H32O15) (Pubchem CID:-) (DCABM ID:BC2915)|debenzoylgalloylpaeoniflorin(C23H28O14) (Pubchem CID:101001427) (DCABM ID:BC2518_S)|pentagalloylglucose(C41H32O26) (Pubchem CID:65238) (DCABM ID:BC1515_S)|paeoniflorin sulfite(C23H28O13S) (Pubchem CID:162642241) (DCABM ID:BC588_S)|naringenin(C15H12O5) (Pubchem CID:439246) (DCABM ID:BC614_S)|dephenyl paeoniflorin(C16H24O10) (Pubchem CID:-) (DCABM ID:BC1894)|benzoylpaeoniflorin(C30H32O12) (Pubchem CID:21631106) (DCABM ID:BC66_S)|[(1r,2s,3r,5r,6s,8s)-6-hydroxy-8-methyl-3-[(2s,3r,4s,5s,6r)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-2-yl]methyl benzoate(C23H28O11) (Pubchem CID:132616773) (DCABM ID:BC800_S)|isobenzoyl paeoniflorin(C30H32O12) (Pubchem CID:-) (DCABM ID:BC1835)</t>
-  </si>
-  <si>
-    <t>paeoniflorin(C23H28O11) (Pubchem CID:442534) (DCABM ID:BC1367_S)|desbenzoylpaeoniflorin(C16H24O10) (Pubchem CID:-) (DCABM ID:BC741)|pinellic acid(C18H34O5) (Pubchem CID:9858729) (DCABM ID:BC3302_S)|gallic acid(C7H6O5) (Pubchem CID:370) (DCABM ID:BC2804_S)|cianidanol(C15H14O6) (Pubchem CID:9064) (DCABM ID:BC3510_S)|[(1r,4r)-4-hydroxy-6-methyl-8-oxo-1-[(2s,3r,4s,5s,6r)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-7-oxatricyclo[4.3.0.03,9]nonan-9-yl]methyl benzoate(C23H28O11) (Pubchem CID:51346141) (DCABM ID:BC3242_S)|(-)-epicatechin(C15H14O6) (Pubchem CID:72276) (DCABM ID:BC2294_S)|paeoniflorin sulfonate(C23H28O14S) (Pubchem CID:101382399) (DCABM ID:BC245_S)|galloyl paeoniflorin or galloylalbiflorin(C30H32O15) (Pubchem CID:-) (DCABM ID:BC2915)|debenzoylgalloylpaeoniflorin(C23H28O14) (Pubchem CID:101001427) (DCABM ID:BC2518_S)|pentagalloylglucose(C41H32O26) (Pubchem CID:65238) (DCABM ID:BC1515_S)|oxypaeoniflora(C23H28O12) (Pubchem CID:21631105) (DCABM ID:BC388_S)|benzoylpaeoniflorin(C30H32O12) (Pubchem CID:21631106) (DCABM ID:BC66_S)</t>
-  </si>
-  <si>
-    <t>oxidation of unknown(C23H28O12) (Pubchem CID:-) (DCABM ID:BC1984)|methylation of unknown(C24H30O11) (Pubchem CID:-) (DCABM ID:BC622)|glucuronide conjugation of unknown(C29H36O17) (Pubchem CID:-) (DCABM ID:BC5)|gallic acid glucuronide(C13H14O11) (Pubchem CID:-) (DCABM ID:BC1220)|ferulic acid 4-sulfate(C10H10O7S) (Pubchem CID:6305574) (DCABM ID:BC3254_S)|3'-o-methyl (epi)catechin 7- or 4'-o-glucuronide(C22H24O12) (Pubchem CID:-) (DCABM ID:BC1507)|3-methoxy-4-hydroxy-phenylpropionic acid sulfate(C10H12O7S) (Pubchem CID:-) (DCABM ID:BC2704)</t>
-  </si>
-  <si>
-    <t>生姜</t>
-  </si>
-  <si>
-    <t>SHENG JIANG</t>
-  </si>
-  <si>
-    <t>Zingiberis Rhizoma Recens</t>
-  </si>
-  <si>
-    <t>Zingiber officinale Roscoe</t>
-  </si>
-  <si>
-    <t>gingerol(C17H26O4) (Pubchem CID:442793) (DCABM ID:BC2314_S)|shogaol(C17H24O3) (Pubchem CID:5281794) (DCABM ID:BC1238_S)|(8)-gingerol(C19H30O4) (Pubchem CID:168114) (DCABM ID:BC3561_S)</t>
-  </si>
-  <si>
-    <t>gingerol(C17H26O4) (Pubchem CID:442793) (DCABM ID:BC2314_S)</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>Compound</t>
-  </si>
-  <si>
-    <t>Formula</t>
-  </si>
-  <si>
-    <t>159891</t>
-  </si>
-  <si>
-    <t>talatisamine</t>
-  </si>
-  <si>
-    <t>C24H39NO5</t>
-  </si>
-  <si>
-    <t>120682</t>
-  </si>
-  <si>
-    <t>neoline</t>
-  </si>
-  <si>
-    <t>C24H39NO6</t>
-  </si>
-  <si>
-    <t>441747</t>
-  </si>
-  <si>
-    <t>mesaconitine</t>
-  </si>
-  <si>
-    <t>C33H45NO11</t>
-  </si>
-  <si>
-    <t>441737</t>
-  </si>
-  <si>
-    <t>hypaconitine</t>
-  </si>
-  <si>
-    <t>C33H45NO10</t>
-  </si>
-  <si>
-    <t>24832659</t>
-  </si>
-  <si>
-    <t>benzoylmesaconine</t>
-  </si>
-  <si>
-    <t>C31H43NO10</t>
-  </si>
-  <si>
-    <t>20055771</t>
-  </si>
-  <si>
-    <t>benzoylaconine</t>
-  </si>
-  <si>
-    <t>C32H45NO10</t>
-  </si>
-  <si>
-    <t>101596809</t>
-  </si>
-  <si>
-    <t>acetyltalatisamine</t>
-  </si>
-  <si>
-    <t>C26H41NO6</t>
-  </si>
-  <si>
-    <t>78358526</t>
-  </si>
-  <si>
-    <t>benzoylhypaconine</t>
-  </si>
-  <si>
-    <t>C31H43NO9</t>
-  </si>
-  <si>
-    <t>14163819</t>
-  </si>
-  <si>
-    <t>senbusine c</t>
-  </si>
-  <si>
-    <t>C24H39NO7</t>
-  </si>
-  <si>
-    <t>20055812</t>
-  </si>
-  <si>
-    <t>toroko base ii</t>
-  </si>
-  <si>
-    <t>C25H41NO6</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>glucuronide conjugation of fuziline</t>
-  </si>
-  <si>
-    <t>C30H47NO13</t>
-  </si>
-  <si>
-    <t>71456946</t>
-  </si>
-  <si>
-    <t>songorine</t>
-  </si>
-  <si>
-    <t>C22H31NO3</t>
-  </si>
-  <si>
-    <t>senbusine b</t>
-  </si>
-  <si>
-    <t>C23H37NO6</t>
-  </si>
-  <si>
-    <t>158048</t>
-  </si>
-  <si>
-    <t>senbusine a</t>
-  </si>
-  <si>
-    <t>76189547</t>
-  </si>
-  <si>
-    <t>6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8,14-pentol</t>
-  </si>
-  <si>
-    <t>C24H39NO9</t>
-  </si>
-  <si>
-    <t>245005</t>
-  </si>
-  <si>
-    <t>aconitine</t>
-  </si>
-  <si>
-    <t>C34H47NO11</t>
-  </si>
-  <si>
-    <t>101636479</t>
-  </si>
-  <si>
-    <t>10-hydroxytalatizamine</t>
-  </si>
-  <si>
-    <t>sulfate conjugation of unknown</t>
-  </si>
-  <si>
-    <t>C25H41NO9S</t>
-  </si>
-  <si>
-    <t>s-cysteine conjugation of unknown</t>
-  </si>
-  <si>
-    <t>C25H36N2O5S</t>
-  </si>
-  <si>
-    <t>C28H46N2O11S</t>
-  </si>
-  <si>
-    <t>reduction of unknown</t>
-  </si>
-  <si>
-    <t>C31H45NO10</t>
-  </si>
-  <si>
-    <t>C22H33NO3</t>
-  </si>
-  <si>
-    <t>methylation +sulfate conjugation of unknown</t>
-  </si>
-  <si>
-    <t>C24H39NO9S</t>
-  </si>
-  <si>
-    <t>hydroxymethylene loss of unknown</t>
-  </si>
-  <si>
-    <t>hydroxylation + sulfation of unknown</t>
-  </si>
-  <si>
-    <t>hydration of unknown</t>
-  </si>
-  <si>
-    <t>C25H43NO7</t>
-  </si>
-  <si>
-    <t>glycine conjugation of unknown</t>
-  </si>
-  <si>
-    <t>C27H44N2O7</t>
-  </si>
-  <si>
-    <t>C26H42N2O7</t>
-  </si>
-  <si>
-    <t>demethylation of unknown</t>
-  </si>
-  <si>
-    <t>C24H37NO9</t>
-  </si>
-  <si>
-    <t>cysteine conjugation of unknown</t>
-  </si>
-  <si>
-    <t>C28H46N2O7S</t>
-  </si>
-  <si>
-    <t>C28H46N2O10S</t>
-  </si>
-  <si>
-    <t>C27H44N2O6S</t>
-  </si>
-  <si>
-    <t>acetylation of unknown</t>
-  </si>
-  <si>
-    <t>122173204</t>
-  </si>
-  <si>
-    <t>benzoylmesaconitine</t>
-  </si>
-  <si>
-    <t>13343336</t>
-  </si>
-  <si>
-    <t>[5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
-  </si>
-  <si>
-    <t>441742</t>
-  </si>
-  <si>
-    <t>carmicheline</t>
-  </si>
-  <si>
-    <t>C22H35NO4</t>
-  </si>
-  <si>
-    <t>21598997</t>
-  </si>
-  <si>
-    <t>3-deoxyaconitine</t>
-  </si>
-  <si>
-    <t>C34H47NO10</t>
-  </si>
-  <si>
-    <t>156166</t>
-  </si>
-  <si>
-    <t>14-o-acetyl-talatisamine</t>
-  </si>
-  <si>
-    <t>3084020</t>
-  </si>
-  <si>
-    <t>20-ethyl-16-methoxy-4-(methoxymethyl)aconitane-1,8,14-triol</t>
-  </si>
-  <si>
-    <t>C23H37NO5</t>
-  </si>
-  <si>
-    <t>demethylated metabolite of talatizamine</t>
-  </si>
-  <si>
-    <t>demethylated metabolite of neoline</t>
-  </si>
-  <si>
-    <t>demethylated metabolite of isotalatizidine</t>
-  </si>
-  <si>
-    <t>C22H35NO5</t>
-  </si>
-  <si>
-    <t>dehydrated benzoylmesaconine</t>
-  </si>
-  <si>
-    <t>C31H41O9N</t>
-  </si>
-  <si>
-    <t>dehydrated benzoylhypaconine</t>
-  </si>
-  <si>
-    <t>C31H41O8N</t>
-  </si>
-  <si>
-    <t>441715</t>
-  </si>
-  <si>
-    <t>cammaconine</t>
-  </si>
-  <si>
-    <t>78358536</t>
-  </si>
-  <si>
-    <t>10-oh-mesaconitine</t>
-  </si>
-  <si>
-    <t>C33H45NO12</t>
-  </si>
-  <si>
-    <t>acetyltalatizamine</t>
-  </si>
-  <si>
-    <t>C26H41O6N</t>
-  </si>
-  <si>
-    <t>10-oh-benzoylmesaconine</t>
-  </si>
-  <si>
-    <t>C31H43O11N</t>
-  </si>
-  <si>
-    <t>isotalatisamine</t>
-  </si>
-  <si>
-    <t>102146471</t>
-  </si>
-  <si>
-    <t>isodelphinine</t>
-  </si>
-  <si>
-    <t>C33H45NO9</t>
-  </si>
-  <si>
-    <t>24832662</t>
-  </si>
-  <si>
-    <t>[(1s,2r,3r,4r,5r,6s,7s,8r,9r,10r,13s,16s,17r,18r)-5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
-  </si>
-  <si>
-    <t>20054813</t>
-  </si>
-  <si>
-    <t>jesaconine</t>
-  </si>
-  <si>
-    <t>C25H41NO9</t>
-  </si>
-  <si>
-    <t>3047329</t>
-  </si>
-  <si>
-    <t>benzoylhypacoitine</t>
-  </si>
-  <si>
-    <t>3,13-deoxybenzoylaconine</t>
-  </si>
-  <si>
-    <t>C31H44NO8</t>
-  </si>
-  <si>
-    <t>10-oh-benzoylaconine</t>
-  </si>
-  <si>
-    <t>C31H43NO11</t>
-  </si>
-  <si>
-    <t>5280378</t>
-  </si>
-  <si>
-    <t>formononetin</t>
-  </si>
-  <si>
-    <t>C16H12O4</t>
-  </si>
-  <si>
-    <t>5280448</t>
-  </si>
-  <si>
-    <t>calycosin</t>
-  </si>
-  <si>
-    <t>C16H12O5</t>
-  </si>
-  <si>
-    <t>C16H12O7S</t>
-  </si>
-  <si>
-    <t>C19H17NO7S</t>
-  </si>
-  <si>
-    <t>hydroxylation + glucuronide conjugation of unknown</t>
-  </si>
-  <si>
-    <t>C22H20O11</t>
-  </si>
-  <si>
-    <t>glucuronide conjugation of unknown</t>
-  </si>
-  <si>
-    <t>C21H21O9</t>
-  </si>
-  <si>
-    <t>decarboxylation + glucuronidation of unknown</t>
-  </si>
-  <si>
-    <t>C21H20O10</t>
-  </si>
-  <si>
-    <t>442813</t>
-  </si>
-  <si>
-    <t>ononin</t>
-  </si>
-  <si>
-    <t>C22H22O9</t>
-  </si>
-  <si>
-    <t>5319733</t>
-  </si>
-  <si>
-    <t>methylnissolin</t>
-  </si>
-  <si>
-    <t>C17H16O5</t>
-  </si>
-  <si>
-    <t>5318267</t>
-  </si>
-  <si>
-    <t>calycosin 7-o-glucoside</t>
-  </si>
-  <si>
-    <t>C22H22O10</t>
-  </si>
-  <si>
-    <t>13943297</t>
-  </si>
-  <si>
-    <t>astragaloside iv</t>
-  </si>
-  <si>
-    <t>C41H68O14</t>
-  </si>
-  <si>
-    <t>86566448</t>
-  </si>
-  <si>
-    <t>9,10-dimethoxypterocarpan-3-o-beta-d-glucoside</t>
-  </si>
-  <si>
-    <t>C23H26O10</t>
-  </si>
-  <si>
-    <t>10380176</t>
-  </si>
-  <si>
-    <t>(r)-isomucronulatol</t>
-  </si>
-  <si>
-    <t>C17H18O5</t>
-  </si>
-  <si>
-    <t>13996693</t>
-  </si>
-  <si>
-    <t>astragaloside ii</t>
-  </si>
-  <si>
-    <t>C43H70O15</t>
-  </si>
-  <si>
-    <t>71316927</t>
-  </si>
-  <si>
-    <t>formononetin 7-o-glucuronide</t>
-  </si>
-  <si>
-    <t>C22H20O10</t>
-  </si>
-  <si>
-    <t>11316354</t>
-  </si>
-  <si>
-    <t>daidzein-7-o-glucuronide</t>
-  </si>
-  <si>
-    <t>C21H18O10</t>
-  </si>
-  <si>
-    <t>calycosin-7-β-glucoside-3'-glucuronide</t>
-  </si>
-  <si>
-    <t>C28H30O16</t>
-  </si>
-  <si>
-    <t>calycosin-3'-o-glucuronide</t>
-  </si>
-  <si>
-    <t>6057</t>
-  </si>
-  <si>
-    <t>tyrosine</t>
-  </si>
-  <si>
-    <t>C9H11NO3</t>
-  </si>
-  <si>
-    <t>6305</t>
-  </si>
-  <si>
-    <t>tryptophan</t>
-  </si>
-  <si>
-    <t>C11H12N2O2</t>
-  </si>
-  <si>
-    <t>5316860</t>
-  </si>
-  <si>
-    <t>syringin</t>
-  </si>
-  <si>
-    <t>C17H24O9</t>
-  </si>
-  <si>
-    <t>10742</t>
-  </si>
-  <si>
-    <t>syringic acid</t>
-  </si>
-  <si>
-    <t>C9H10O5</t>
-  </si>
-  <si>
-    <t>8655</t>
-  </si>
-  <si>
-    <t>syringaldehyde</t>
-  </si>
-  <si>
-    <t>C9H10O4</t>
-  </si>
-  <si>
-    <t>122097</t>
-  </si>
-  <si>
-    <t>soyasaponin i</t>
-  </si>
-  <si>
-    <t>C48H78O18</t>
-  </si>
-  <si>
-    <t>637775</t>
-  </si>
-  <si>
-    <t>sinapic acid</t>
-  </si>
-  <si>
-    <t>C11H12O5</t>
-  </si>
-  <si>
-    <t>44259548</t>
-  </si>
-  <si>
-    <t>rhamnocitrin 3,4'-diglucoside</t>
-  </si>
-  <si>
-    <t>C28H32O16</t>
-  </si>
-  <si>
-    <t>439242</t>
-  </si>
-  <si>
-    <t>raffinose</t>
-  </si>
-  <si>
-    <t>C18H32O16</t>
-  </si>
-  <si>
-    <t>44257307</t>
-  </si>
-  <si>
-    <t>pratensein 7-o-glucoside</t>
-  </si>
-  <si>
-    <t>C22H22O11</t>
-  </si>
-  <si>
-    <t>6140</t>
-  </si>
-  <si>
-    <t>phenylalanine</t>
-  </si>
-  <si>
-    <t>C9H11NO2</t>
-  </si>
-  <si>
-    <t>938</t>
-  </si>
-  <si>
-    <t>nicotinic acid</t>
-  </si>
-  <si>
-    <t>C6H5NO2</t>
-  </si>
-  <si>
-    <t>101182651</t>
-  </si>
-  <si>
-    <t>markhamioside f</t>
-  </si>
-  <si>
-    <t>C19H26O13</t>
-  </si>
-  <si>
-    <t>6106</t>
-  </si>
-  <si>
-    <t>leucine</t>
-  </si>
-  <si>
-    <t>C6H13NO2</t>
-  </si>
-  <si>
-    <t>isomucronulatol-2',5'-di-o-glucoside</t>
-  </si>
-  <si>
-    <t>C29H38O16</t>
-  </si>
-  <si>
-    <t>125142</t>
-  </si>
-  <si>
-    <t>isomucronulatol 7-o-glucoside</t>
-  </si>
-  <si>
-    <t>C23H28O10</t>
-  </si>
-  <si>
-    <t>15689653</t>
-  </si>
-  <si>
-    <t>isomucronulatol 7,2'-di-o-glucoside</t>
-  </si>
-  <si>
-    <t>C29H38O15</t>
-  </si>
-  <si>
-    <t>736186</t>
-  </si>
-  <si>
-    <t>isoferulic acid</t>
-  </si>
-  <si>
-    <t>C10H10O4</t>
-  </si>
-  <si>
-    <t>60148697</t>
-  </si>
-  <si>
-    <t>isoastragaloside i</t>
-  </si>
-  <si>
-    <t>C45H72O16</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>hexose</t>
-  </si>
-  <si>
-    <t>C6H12O6</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>gamma-aminobutyric acid</t>
-  </si>
-  <si>
-    <t>C4H9NO2</t>
-  </si>
-  <si>
-    <t>445858</t>
-  </si>
-  <si>
-    <t>ferulic acid</t>
-  </si>
-  <si>
-    <t>emodin-di-o-glucoside</t>
-  </si>
-  <si>
-    <t>C27H30O15</t>
-  </si>
-  <si>
-    <t>3749604</t>
-  </si>
-  <si>
-    <t>2-(hydroxymethyl)-6-[[3,4,5-trihydroxy-5-(hydroxymethyl)oxolan-2-yl]methoxy]oxane-3,4,5-triol</t>
-  </si>
-  <si>
-    <t>C12H22O11</t>
-  </si>
-  <si>
-    <t>5280704</t>
-  </si>
-  <si>
-    <t>cosmosiin</t>
-  </si>
-  <si>
-    <t>54498674</t>
-  </si>
-  <si>
-    <t>nona-2,4-dienoic acid</t>
-  </si>
-  <si>
-    <t>C9H14O2</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>choline</t>
-  </si>
-  <si>
-    <t>C5H14NO+</t>
-  </si>
-  <si>
-    <t>689043</t>
-  </si>
-  <si>
-    <t>caffeic acid</t>
-  </si>
-  <si>
-    <t>C9H8O4</t>
-  </si>
-  <si>
-    <t>2266</t>
-  </si>
-  <si>
-    <t>azelaic acid</t>
-  </si>
-  <si>
-    <t>C9H16O4</t>
-  </si>
-  <si>
-    <t>21634074</t>
-  </si>
-  <si>
-    <t>wistariasaponin c</t>
-  </si>
-  <si>
-    <t>C47H76O17</t>
-  </si>
-  <si>
-    <t>14241100</t>
-  </si>
-  <si>
-    <t>astragaloside vii</t>
-  </si>
-  <si>
-    <t>C47H78O19</t>
-  </si>
-  <si>
-    <t>71448940</t>
-  </si>
-  <si>
-    <t>astragaloside vi</t>
-  </si>
-  <si>
-    <t>71448939</t>
-  </si>
-  <si>
-    <t>astragaloside v</t>
-  </si>
-  <si>
-    <t>441905</t>
-  </si>
-  <si>
-    <t>astragaloside iii</t>
-  </si>
-  <si>
-    <t>13996685</t>
-  </si>
-  <si>
-    <t>astrasieversianin iv</t>
-  </si>
-  <si>
-    <t>6267</t>
-  </si>
-  <si>
-    <t>asparagine</t>
-  </si>
-  <si>
-    <t>C4H8N2O3</t>
-  </si>
-  <si>
-    <t>60961</t>
-  </si>
-  <si>
-    <t>adenosine</t>
-  </si>
-  <si>
-    <t>C10H13N5O4</t>
-  </si>
-  <si>
-    <t>acetyl astragaloside i</t>
-  </si>
-  <si>
-    <t>C47H74O17</t>
-  </si>
-  <si>
-    <t>102463148</t>
-  </si>
-  <si>
-    <t>6''-o-acetylononin</t>
-  </si>
-  <si>
-    <t>C24H24O10</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>3,4-dihydroxybenzoic acid</t>
-  </si>
-  <si>
-    <t>C7H6O4</t>
-  </si>
-  <si>
-    <t>21633193</t>
-  </si>
-  <si>
-    <t>cyclocanthoside e</t>
-  </si>
-  <si>
-    <t>C41H70O14</t>
-  </si>
-  <si>
-    <t>sulfated isomucronulatol</t>
-  </si>
-  <si>
-    <t>C17H18O8S</t>
-  </si>
-  <si>
-    <t>sulfated formononetin</t>
-  </si>
-  <si>
-    <t>sulfated calycosin</t>
-  </si>
-  <si>
-    <t>C16H12O8S</t>
-  </si>
-  <si>
-    <t>5320946</t>
-  </si>
-  <si>
-    <t>rhamnocitrin</t>
-  </si>
-  <si>
-    <t>C16H12O6</t>
-  </si>
-  <si>
-    <t>602152</t>
-  </si>
-  <si>
-    <t>isomucronulatol</t>
-  </si>
-  <si>
-    <t>glucuronidated rhamnocitrin</t>
-  </si>
-  <si>
-    <t>C22H20O12</t>
-  </si>
-  <si>
-    <t>glucuronidated isomucronulatol</t>
-  </si>
-  <si>
-    <t>C23H26O11</t>
-  </si>
-  <si>
-    <t>101220281</t>
-  </si>
-  <si>
-    <t>formononetin 7-glucuronide</t>
-  </si>
-  <si>
-    <t>glucuronidated calycosin</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>betaine</t>
-  </si>
-  <si>
-    <t>C5H11NO2</t>
-  </si>
-  <si>
-    <t>5-hydroxy-7,8-dimethoxyflavanone + glucuronide conjugation</t>
-  </si>
-  <si>
-    <t>C23H24O11</t>
-  </si>
-  <si>
-    <t>isomer of 3-hydro-9, 10-dimethoxypterocarpan</t>
-  </si>
-  <si>
-    <t>5281708</t>
-  </si>
-  <si>
-    <t>daidzein</t>
-  </si>
-  <si>
-    <t>C15H10O4</t>
-  </si>
-  <si>
-    <t>hydroxylation of calycosin</t>
-  </si>
-  <si>
-    <t>glucuronic acid conjugate of formononetin</t>
-  </si>
-  <si>
-    <t>glucuronic acid conjugate of demethylcalycosin</t>
-  </si>
-  <si>
-    <t>C21H18O11</t>
-  </si>
-  <si>
-    <t>glucuronic acid conjugate of daidzein</t>
-  </si>
-  <si>
-    <t>glucuronic acid conjugate of calycosin</t>
-  </si>
-  <si>
-    <t>glucuronic acid conjugate of 3-hydro-9, 10-dimp</t>
-  </si>
-  <si>
-    <t>5486199</t>
-  </si>
-  <si>
-    <t>kaempferitrin</t>
-  </si>
-  <si>
-    <t>C27H30O14</t>
-  </si>
-  <si>
-    <t>71306915</t>
-  </si>
-  <si>
-    <t>astragaloside-ii</t>
-  </si>
-  <si>
-    <t>C41H66O15</t>
-  </si>
-  <si>
-    <t>53461957</t>
-  </si>
-  <si>
-    <t>3,4-dihydro-3-(2-hydroxy-3,4-dimethoxyphenyl)-2h-1-benzopyran-7-yl beta-d-glucopyranoside</t>
-  </si>
-  <si>
-    <t>5281703</t>
-  </si>
-  <si>
-    <t>wogonin</t>
-  </si>
-  <si>
-    <t>5318767</t>
-  </si>
-  <si>
-    <t>nicotiflorin</t>
-  </si>
-  <si>
-    <t>5281426</t>
-  </si>
-  <si>
-    <t>umbelliferone</t>
-  </si>
-  <si>
-    <t>C9H6O3</t>
-  </si>
-  <si>
-    <t>14448070</t>
-  </si>
-  <si>
-    <t>atractylenolide ii</t>
-  </si>
-  <si>
-    <t>C15H20O2</t>
-  </si>
-  <si>
-    <t>5321018</t>
-  </si>
-  <si>
-    <t>atractylenolide i</t>
-  </si>
-  <si>
-    <t>C15H18O2</t>
-  </si>
-  <si>
-    <t>155948</t>
-  </si>
-  <si>
-    <t>atractylenolide iii</t>
-  </si>
-  <si>
-    <t>C15H20O3</t>
-  </si>
-  <si>
-    <t>1183</t>
-  </si>
-  <si>
-    <t>vanillin</t>
-  </si>
-  <si>
-    <t>C8H8O3</t>
-  </si>
-  <si>
-    <t>5988</t>
-  </si>
-  <si>
-    <t>sucrose</t>
-  </si>
-  <si>
-    <t>1110</t>
-  </si>
-  <si>
-    <t>succinic acid</t>
-  </si>
-  <si>
-    <t>C4H6O4</t>
-  </si>
-  <si>
-    <t>18950</t>
-  </si>
-  <si>
-    <t>d-mannose</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>citric acid</t>
-  </si>
-  <si>
-    <t>C6H8O7</t>
-  </si>
-  <si>
-    <t>98967</t>
-  </si>
-  <si>
-    <t>3-tert-butyladipic acid</t>
-  </si>
-  <si>
-    <t>C10H18O4</t>
-  </si>
-  <si>
-    <t>oxidation,glucuronide conjugation of benzoic acid</t>
-  </si>
-  <si>
-    <t>C13H14O9</t>
-  </si>
-  <si>
-    <t>15225964</t>
-  </si>
-  <si>
-    <t>dehydrotumulosic acid</t>
-  </si>
-  <si>
-    <t>C31H48O4</t>
-  </si>
-  <si>
-    <t>3086648</t>
-  </si>
-  <si>
-    <t>2-[(2r,3r,3ar,6s,7s,9br)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid</t>
-  </si>
-  <si>
-    <t>C30H44O5</t>
-  </si>
-  <si>
-    <t>3β,16α- dihydroxylanostene-triene-21-acid</t>
-  </si>
-  <si>
-    <t>C30H46O4</t>
-  </si>
-  <si>
-    <t>15225966</t>
-  </si>
-  <si>
-    <t>poricoic acid e</t>
-  </si>
-  <si>
-    <t>C30H44O6</t>
-  </si>
-  <si>
-    <t>12314446</t>
-  </si>
-  <si>
-    <t>tumulosic acid</t>
-  </si>
-  <si>
-    <t>C31H50O4</t>
-  </si>
-  <si>
-    <t>15226717</t>
-  </si>
-  <si>
-    <t>dehydropachymic acid</t>
-  </si>
-  <si>
-    <t>C33H50O5</t>
-  </si>
-  <si>
-    <t>10918099</t>
-  </si>
-  <si>
-    <t>poricoic acid h</t>
-  </si>
-  <si>
-    <t>C31H48O5</t>
-  </si>
-  <si>
-    <t>5471966</t>
-  </si>
-  <si>
-    <t>poricoic acid g</t>
-  </si>
-  <si>
-    <t>C30H46O5</t>
-  </si>
-  <si>
-    <t>11431307</t>
-  </si>
-  <si>
-    <t>fomefficinic acid a</t>
-  </si>
-  <si>
-    <t>C31H48O3</t>
-  </si>
-  <si>
-    <t>11179164</t>
-  </si>
-  <si>
-    <t>daedaleanic acid a</t>
-  </si>
-  <si>
-    <t>C31H46O4</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
-    <t>adenine</t>
-  </si>
-  <si>
-    <t>C5H5N5</t>
-  </si>
-  <si>
-    <t>3β-hydroxy-16α-acetoxy-lanosta-7,9(11),24-trien-21-oic acid</t>
-  </si>
-  <si>
-    <t>C32H48O5</t>
-  </si>
-  <si>
-    <t>3β,16α-dihydroxylanosta-7,9(11),24-trien-21-oic acid</t>
-  </si>
-  <si>
-    <t>44556878</t>
-  </si>
-  <si>
-    <t>6,7-dehydroporicoic acid h</t>
-  </si>
-  <si>
-    <t>C31H46O5</t>
-  </si>
-  <si>
-    <t>16736458</t>
-  </si>
-  <si>
-    <t>16-deoxyporicoic acid b</t>
-  </si>
-  <si>
-    <t>C30H44O4</t>
-  </si>
-  <si>
-    <t>11062697</t>
-  </si>
-  <si>
-    <t>(r)-dimethyl 2-hydroxysuccinate</t>
-  </si>
-  <si>
-    <t>C6H10O5</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>C33H48O4</t>
-  </si>
-  <si>
-    <t>(5ξ,20s)-24- methylene-3- oxolanosta-7,9(11)- dien-21-oic acid</t>
-  </si>
-  <si>
-    <t>C31H46O3</t>
-  </si>
-  <si>
-    <t>12309443</t>
-  </si>
-  <si>
-    <t>trametenolic acid</t>
-  </si>
-  <si>
-    <t>C30H48O3</t>
-  </si>
-  <si>
-    <t>101928114</t>
-  </si>
-  <si>
-    <t>poricoic acid f</t>
-  </si>
-  <si>
-    <t>C31H46O6</t>
-  </si>
-  <si>
-    <t>46882717</t>
-  </si>
-  <si>
-    <t>poricoic acid am</t>
-  </si>
-  <si>
-    <t>137648664</t>
-  </si>
-  <si>
-    <t>(2r)-2-[(3s,5r,10s,13r,14r,16r,17r)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid</t>
-  </si>
-  <si>
-    <t>137654023</t>
-  </si>
-  <si>
-    <t>(2r)-2-[(3r,5r,10s,13r,14r,16r,17r)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid</t>
-  </si>
-  <si>
-    <t>9805290</t>
-  </si>
-  <si>
-    <t>polyporenic acid c</t>
-  </si>
-  <si>
-    <t>5484385</t>
-  </si>
-  <si>
-    <t>pachymic acid</t>
-  </si>
-  <si>
-    <t>C33H52O5</t>
-  </si>
-  <si>
-    <t>73402</t>
-  </si>
-  <si>
-    <t>eburicoic acid</t>
-  </si>
-  <si>
-    <t>C31H50O3</t>
-  </si>
-  <si>
-    <t>6-hydroxy-dehydrotumulosic acid</t>
-  </si>
-  <si>
-    <t>3β-hydroxy-16-acetoxylanosta-7,-9(11)-24-trien-21-oic acid</t>
-  </si>
-  <si>
-    <t>3β,16α-dihydroxy-lanosta-8,24-dien-21-oic acid</t>
-  </si>
-  <si>
-    <t>C30H48O4</t>
-  </si>
-  <si>
-    <t>3β,16α-dihydroxy-7-oxolanosta-8,24-dien-21-oic acid</t>
-  </si>
-  <si>
-    <t>3α,16β-dihydroxylanosta-7,9(11),24-trien-21-oic acid</t>
-  </si>
-  <si>
-    <t>3-oxo-16α-hydroxylanosta-7,9(11),24-trien-21-oic acid</t>
-  </si>
-  <si>
-    <t>C31H44O4</t>
-  </si>
-  <si>
-    <t>3-o-acetyl-16α,26-dihydroxytrametenolic acid</t>
-  </si>
-  <si>
-    <t>C32H50O6</t>
-  </si>
-  <si>
-    <t>15226712</t>
-  </si>
-  <si>
-    <t>3-o-acetyl-16alpha-hydroxytrametenolic acid</t>
-  </si>
-  <si>
-    <t>C32H50O5</t>
-  </si>
-  <si>
-    <t>3-o-16α,25-dihydroxy-lanosta-8,24(3)-dieen-21-oic acid</t>
-  </si>
-  <si>
-    <t>10005581</t>
-  </si>
-  <si>
-    <t>3-epidehydrotumulosic acid</t>
-  </si>
-  <si>
-    <t>15226716</t>
-  </si>
-  <si>
-    <t>3-epidehydropachymic acid</t>
-  </si>
-  <si>
-    <t>3-epi-(3'-hydroxy-3'-methylglutaryloxyl)-dehydrotum ulosic acid</t>
-  </si>
-  <si>
-    <t>C37H56O8</t>
-  </si>
-  <si>
-    <t>15391340</t>
-  </si>
-  <si>
-    <t>3-dehydrotrametenolic acid</t>
-  </si>
-  <si>
-    <t>C30H46O3</t>
-  </si>
-  <si>
-    <t>137355885</t>
-  </si>
-  <si>
-    <t>29-hydroxydehydropachymic acid</t>
-  </si>
-  <si>
-    <t>C33H50O6</t>
-  </si>
-  <si>
-    <t>26-hydroxy-poricoic acid g</t>
-  </si>
-  <si>
-    <t>C30H46O6</t>
-  </si>
-  <si>
-    <t>26-hydroxy-dehydrotumuloosic acid</t>
-  </si>
-  <si>
-    <t>25α-hydroxytumulosic acid</t>
-  </si>
-  <si>
-    <t>C31H50O5</t>
-  </si>
-  <si>
-    <t>25-hydroxytumulosic acid</t>
-  </si>
-  <si>
-    <t>16736865</t>
-  </si>
-  <si>
-    <t>25-hydroxyporicoic acid h</t>
-  </si>
-  <si>
-    <t>C31H48O6</t>
-  </si>
-  <si>
-    <t>25-hydroxypachymic acid</t>
-  </si>
-  <si>
-    <t>C33H52O6</t>
-  </si>
-  <si>
-    <t>25-hydroxl-3β,16α-diacetoxylanosta-8-en-21-oic acid</t>
-  </si>
-  <si>
-    <t>C35H54O7</t>
-  </si>
-  <si>
-    <t>44556811</t>
-  </si>
-  <si>
-    <t>25-hydroxyporicoic acid c</t>
-  </si>
-  <si>
-    <t>16α,25-hydroxydehydroeburicoinic acid</t>
-  </si>
-  <si>
-    <t>11465951</t>
-  </si>
-  <si>
-    <t>daedaleanic acid b</t>
-  </si>
-  <si>
-    <t>C30H48O5</t>
-  </si>
-  <si>
-    <t>102480393</t>
-  </si>
-  <si>
-    <t>poricoic acid ce</t>
-  </si>
-  <si>
-    <t>C33H50O4</t>
-  </si>
-  <si>
-    <t>tumulosic acid +o</t>
-  </si>
-  <si>
-    <t>trametenolic acid+o2-h2</t>
-  </si>
-  <si>
-    <t>trametenolic acid+o2</t>
-  </si>
-  <si>
-    <t>poricoic bm+o-h2</t>
-  </si>
-  <si>
-    <t>poricoic b+o</t>
-  </si>
-  <si>
-    <t>poricoic acid h+o</t>
-  </si>
-  <si>
-    <t>polyporenic acid c+o</t>
-  </si>
-  <si>
-    <t>hydroxyporicoic acid h+o</t>
-  </si>
-  <si>
-    <t>eburiconic acid+o2-h2</t>
-  </si>
-  <si>
-    <t>eburiconic acid +o</t>
-  </si>
-  <si>
-    <t>dehydrotumulosic acid+o-2h</t>
-  </si>
-  <si>
-    <t>dehydrotumulosic acid+2o-2h</t>
-  </si>
-  <si>
-    <t>dehydrotumulosic acid+o2</t>
-  </si>
-  <si>
-    <t>dehydrotumulosic acid +o</t>
-  </si>
-  <si>
-    <t>dehydrotrametenoic acid +o-h2</t>
-  </si>
-  <si>
-    <t>dehydrotrametenoic acid +o</t>
-  </si>
-  <si>
-    <t>16-oxy-acetoxypachymic acid methyl ester)</t>
-  </si>
-  <si>
-    <t>C36H56O6</t>
-  </si>
-  <si>
-    <t>16-oxy-acetoxypachymic acid</t>
-  </si>
-  <si>
-    <t>C35H54O6</t>
-  </si>
-  <si>
-    <t>6475119</t>
-  </si>
-  <si>
-    <t>ursolic acid acetate</t>
-  </si>
-  <si>
-    <t>C32H50O4</t>
-  </si>
-  <si>
-    <t>72202422</t>
-  </si>
-  <si>
-    <t>methyl (2r)-2-[(3s,5r,10s,13r,14r,16r,17r)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoate</t>
-  </si>
-  <si>
-    <t>C34H54O5</t>
-  </si>
-  <si>
-    <t>pachymic acid c</t>
-  </si>
-  <si>
-    <t>442534</t>
-  </si>
-  <si>
-    <t>paeoniflorin</t>
-  </si>
-  <si>
-    <t>C23H28O11</t>
-  </si>
-  <si>
-    <t>desbenzoylpaeoniflorin</t>
-  </si>
-  <si>
-    <t>C16H24O10</t>
-  </si>
-  <si>
-    <t>9858729</t>
-  </si>
-  <si>
-    <t>pinellic acid</t>
-  </si>
-  <si>
-    <t>C18H34O5</t>
-  </si>
-  <si>
-    <t>oxidation of unknown</t>
-  </si>
-  <si>
-    <t>C23H28O12</t>
-  </si>
-  <si>
-    <t>methylation of unknown</t>
-  </si>
-  <si>
-    <t>C24H30O11</t>
-  </si>
-  <si>
-    <t>C29H36O17</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>gallic acid</t>
-  </si>
-  <si>
-    <t>C7H6O5</t>
-  </si>
-  <si>
-    <t>9064</t>
-  </si>
-  <si>
-    <t>cianidanol</t>
-  </si>
-  <si>
-    <t>C15H14O6</t>
-  </si>
-  <si>
-    <t>51346141</t>
-  </si>
-  <si>
-    <t>[(1r,4r)-4-hydroxy-6-methyl-8-oxo-1-[(2s,3r,4s,5s,6r)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-7-oxatricyclo[4.3.0.03,9]nonan-9-yl]methyl benzoate</t>
-  </si>
-  <si>
-    <t>72276</t>
-  </si>
-  <si>
-    <t>(-)-epicatechin</t>
-  </si>
-  <si>
-    <t>gallic acid glucuronide</t>
-  </si>
-  <si>
-    <t>C13H14O11</t>
-  </si>
-  <si>
-    <t>6305574</t>
-  </si>
-  <si>
-    <t>ferulic acid 4-sulfate</t>
-  </si>
-  <si>
-    <t>C10H10O7S</t>
-  </si>
-  <si>
-    <t>3'-o-methyl (epi)catechin 7- or 4'-o-glucuronide</t>
-  </si>
-  <si>
-    <t>C22H24O12</t>
-  </si>
-  <si>
-    <t>3-methoxy-4-hydroxy-phenylpropionic acid sulfate</t>
-  </si>
-  <si>
-    <t>C10H12O7S</t>
-  </si>
-  <si>
-    <t>C9H10O3</t>
-  </si>
-  <si>
-    <t>21631105</t>
-  </si>
-  <si>
-    <t>oxypaeoniflora</t>
-  </si>
-  <si>
-    <t>101382399</t>
-  </si>
-  <si>
-    <t>paeoniflorin sulfonate</t>
-  </si>
-  <si>
-    <t>C23H28O14S</t>
-  </si>
-  <si>
-    <t>galloyl paeoniflorin or galloylalbiflorin</t>
-  </si>
-  <si>
-    <t>C30H32O15</t>
-  </si>
-  <si>
-    <t>101001427</t>
-  </si>
-  <si>
-    <t>debenzoylgalloylpaeoniflorin</t>
-  </si>
-  <si>
-    <t>C23H28O14</t>
-  </si>
-  <si>
-    <t>65238</t>
-  </si>
-  <si>
-    <t>pentagalloylglucose</t>
-  </si>
-  <si>
-    <t>C41H32O26</t>
-  </si>
-  <si>
-    <t>162642241</t>
-  </si>
-  <si>
-    <t>paeoniflorin sulfite</t>
-  </si>
-  <si>
-    <t>C23H28O13S</t>
-  </si>
-  <si>
-    <t>439246</t>
-  </si>
-  <si>
-    <t>naringenin</t>
-  </si>
-  <si>
-    <t>C15H12O5</t>
-  </si>
-  <si>
-    <t>dephenyl paeoniflorin</t>
-  </si>
-  <si>
-    <t>21631106</t>
-  </si>
-  <si>
-    <t>benzoylpaeoniflorin</t>
-  </si>
-  <si>
-    <t>C30H32O12</t>
-  </si>
-  <si>
-    <t>132616773</t>
-  </si>
-  <si>
-    <t>[(1r,2s,3r,5r,6s,8s)-6-hydroxy-8-methyl-3-[(2s,3r,4s,5s,6r)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-2-yl]methyl benzoate</t>
-  </si>
-  <si>
-    <t>isobenzoyl paeoniflorin</t>
-  </si>
-  <si>
-    <t>442793</t>
-  </si>
-  <si>
-    <t>gingerol</t>
-  </si>
-  <si>
-    <t>C17H26O4</t>
-  </si>
-  <si>
-    <t>5281794</t>
-  </si>
-  <si>
-    <t>shogaol</t>
-  </si>
-  <si>
-    <t>C17H24O3</t>
-  </si>
-  <si>
-    <t>168114</t>
-  </si>
-  <si>
-    <t>(8)-gingerol</t>
-  </si>
-  <si>
-    <t>C19H30O4</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="967">
+  <si>
+    <t xml:space="preserve">Herb.Name.Chinese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herb.Name.Pinyin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herb.Name.English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herb.Name.Latin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compounds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">附子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FU ZI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aconiti Lateralis Radix Praeparata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aconitum carmichaelii Debeaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talatisamine(C24H39NO5) (Pubchem CID:159891) (DCABM ID:BC1966_S)|neoline(C24H39NO6) (Pubchem CID:120682) (DCABM ID:BC719_S)|mesaconitine(C33H45NO11) (Pubchem CID:441747) (DCABM ID:BC727_S)|hypaconitine(C33H45NO10) (Pubchem CID:441737) (DCABM ID:BC1167_S)|benzoylmesaconine(C31H43NO10) (Pubchem CID:24832659) (DCABM ID:BC319_S)|benzoylaconine(C32H45NO10) (Pubchem CID:20055771) (DCABM ID:BC167_S)|acetyltalatisamine(C26H41NO6) (Pubchem CID:101596809) (DCABM ID:BC2620_S)|benzoylhypaconine(C31H43NO9) (Pubchem CID:78358526) (DCABM ID:BC268_S)|senbusine c(C24H39NO7) (Pubchem CID:14163819) (DCABM ID:BC623_S)|toroko base ii(C25H41NO6) (Pubchem CID:20055812) (DCABM ID:BC3573_S)|glucuronide conjugation of fuziline(C30H47NO13) (Pubchem CID:-) (DCABM ID:BC2073)|songorine(C22H31NO3) (Pubchem CID:71456946) (DCABM ID:BC3125_S)|senbusine b(C23H37NO6) (Pubchem CID:-) (DCABM ID:BC3240)|senbusine a(C23H37NO6) (Pubchem CID:158048) (DCABM ID:BC2894_S)|6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8,14-pentol(C24H39NO9) (Pubchem CID:76189547) (DCABM ID:BC3153_S)|aconitine(C34H47NO11) (Pubchem CID:245005) (DCABM ID:BC1410_S)|10-hydroxytalatizamine(C24H39NO6) (Pubchem CID:101636479) (DCABM ID:BC2959_S)|sulfate conjugation of unknown(C25H41NO9S) (Pubchem CID:-) (DCABM ID:BC509)|s-cysteine conjugation of unknown(C25H36N2O5S) (Pubchem CID:-) (DCABM ID:BC2370)|s-cysteine conjugation of unknown(C28H46N2O11S) (Pubchem CID:-) (DCABM ID:BC2363)|reduction of unknown(C31H45NO10) (Pubchem CID:-) (DCABM ID:BC545)|reduction of unknown(C22H33NO3) (Pubchem CID:-) (DCABM ID:BC966)|methylation +sulfate conjugation of unknown(C24H39NO9S) (Pubchem CID:-) (DCABM ID:BC1459)|hydroxymethylene loss of unknown(C24H39NO5) (Pubchem CID:-) (DCABM ID:BC1293)|hydroxylation + sulfation of unknown(C24H39NO9S) (Pubchem CID:-) (DCABM ID:BC2904)|hydration of unknown(C25H43NO7) (Pubchem CID:-) (DCABM ID:BC2998)|glycine conjugation of unknown(C27H44N2O7) (Pubchem CID:-) (DCABM ID:BC3556)|glycine conjugation of unknown(C26H42N2O7) (Pubchem CID:-) (DCABM ID:BC1478)|demethylation of unknown(C24H37NO9) (Pubchem CID:-) (DCABM ID:BC1607)|cysteine conjugation of unknown(C28H46N2O7S) (Pubchem CID:-) (DCABM ID:BC1103)|cysteine conjugation of unknown(C28H46N2O10S) (Pubchem CID:-) (DCABM ID:BC3051)|cysteine conjugation of unknown(C27H44N2O6S) (Pubchem CID:-) (DCABM ID:BC1638)|acetylation of unknown(C26H41NO6) (Pubchem CID:-) (DCABM ID:BC2074)|benzoylmesaconitine(C31H43NO10) (Pubchem CID:122173204) (DCABM ID:BC2104_S)|[5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate(C31H43NO9) (Pubchem CID:13343336) (DCABM ID:BC1707_S)|carmicheline(C22H35NO4) (Pubchem CID:441742) (DCABM ID:BC1574_S)|3-deoxyaconitine(C34H47NO10) (Pubchem CID:21598997) (DCABM ID:BC1567_S)|14-o-acetyl-talatisamine(C26H41NO6) (Pubchem CID:156166) (DCABM ID:BC220_S)|20-ethyl-16-methoxy-4-(methoxymethyl)aconitane-1,8,14-triol(C23H37NO5) (Pubchem CID:3084020) (DCABM ID:BC2059_S)|demethylated metabolite of talatizamine(C23H37NO5) (Pubchem CID:-) (DCABM ID:BC1588)|demethylated metabolite of neoline(C23H37NO6) (Pubchem CID:-) (DCABM ID:BC2616)|demethylated metabolite of isotalatizidine(C22H35NO5) (Pubchem CID:-) (DCABM ID:BC1449)|dehydrated benzoylmesaconine(C31H41O9N) (Pubchem CID:-) (DCABM ID:BC2045)|dehydrated benzoylhypaconine(C31H41O8N) (Pubchem CID:-) (DCABM ID:BC2230)|cammaconine(C23H37NO5) (Pubchem CID:441715) (DCABM ID:BC1708_S)|10-oh-mesaconitine(C33H45NO12) (Pubchem CID:78358536) (DCABM ID:BC3530_S)|acetyltalatizamine(C26H41O6N) (Pubchem CID:-) (DCABM ID:BC584)|10-oh-benzoylmesaconine(C31H43O11N) (Pubchem CID:-) (DCABM ID:BC2865)|isotalatisamine(C23H37NO5) (Pubchem CID:-) (DCABM ID:BC3100)|isodelphinine(C33H45NO9) (Pubchem CID:102146471) (DCABM ID:BC43_S)|[(1s,2r,3r,4r,5r,6s,7s,8r,9r,10r,13s,16s,17r,18r)-5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate(C31H43NO9) (Pubchem CID:24832662) (DCABM ID:BC2839_S)|jesaconine(C25H41NO9) (Pubchem CID:20054813) (DCABM ID:BC2434_S)|benzoylhypacoitine(C31H43NO9) (Pubchem CID:3047329) (DCABM ID:BC3088_S)|3,13-deoxybenzoylaconine(C31H44NO8) (Pubchem CID:-) (DCABM ID:BC861)|10-oh-benzoylaconine(C31H43NO11) (Pubchem CID:-) (DCABM ID:BC211)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constituents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talatisamine(C24H39NO5) (Pubchem CID:159891) (DCABM ID:BC1966_S)|neoline(C24H39NO6) (Pubchem CID:120682) (DCABM ID:BC719_S)|mesaconitine(C33H45NO11) (Pubchem CID:441747) (DCABM ID:BC727_S)|hypaconitine(C33H45NO10) (Pubchem CID:441737) (DCABM ID:BC1167_S)|benzoylmesaconine(C31H43NO10) (Pubchem CID:24832659) (DCABM ID:BC319_S)|benzoylaconine(C32H45NO10) (Pubchem CID:20055771) (DCABM ID:BC167_S)|acetyltalatisamine(C26H41NO6) (Pubchem CID:101596809) (DCABM ID:BC2620_S)|benzoylhypaconine(C31H43NO9) (Pubchem CID:78358526) (DCABM ID:BC268_S)|senbusine c(C24H39NO7) (Pubchem CID:14163819) (DCABM ID:BC623_S)|toroko base ii(C25H41NO6) (Pubchem CID:20055812) (DCABM ID:BC3573_S)|songorine(C22H31NO3) (Pubchem CID:71456946) (DCABM ID:BC3125_S)|senbusine b(C23H37NO6) (Pubchem CID:-) (DCABM ID:BC3240)|senbusine a(C23H37NO6) (Pubchem CID:158048) (DCABM ID:BC2894_S)|6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8,14-pentol(C24H39NO9) (Pubchem CID:76189547) (DCABM ID:BC3153_S)|aconitine(C34H47NO11) (Pubchem CID:245005) (DCABM ID:BC1410_S)|10-hydroxytalatizamine(C24H39NO6) (Pubchem CID:101636479) (DCABM ID:BC2959_S)|carmicheline(C22H35NO4) (Pubchem CID:441742) (DCABM ID:BC1574_S)|3-deoxyaconitine(C34H47NO10) (Pubchem CID:21598997) (DCABM ID:BC1567_S)|14-o-acetyl-talatisamine(C26H41NO6) (Pubchem CID:156166) (DCABM ID:BC220_S)|20-ethyl-16-methoxy-4-(methoxymethyl)aconitane-1,8,14-triol(C23H37NO5) (Pubchem CID:3084020) (DCABM ID:BC2059_S)|[5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate(C31H43NO9) (Pubchem CID:13343336) (DCABM ID:BC1707_S)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prototype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glucuronide conjugation of fuziline(C30H47NO13) (Pubchem CID:-) (DCABM ID:BC2073)|sulfate conjugation of unknown(C25H41NO9S) (Pubchem CID:-) (DCABM ID:BC509)|s-cysteine conjugation of unknown(C25H36N2O5S) (Pubchem CID:-) (DCABM ID:BC2370)|s-cysteine conjugation of unknown(C28H46N2O11S) (Pubchem CID:-) (DCABM ID:BC2363)|reduction of unknown(C31H45NO10) (Pubchem CID:-) (DCABM ID:BC545)|reduction of unknown(C22H33NO3) (Pubchem CID:-) (DCABM ID:BC966)|methylation +sulfate conjugation of unknown(C24H39NO9S) (Pubchem CID:-) (DCABM ID:BC1459)|hydroxymethylene loss of unknown(C24H39NO5) (Pubchem CID:-) (DCABM ID:BC1293)|hydroxylation + sulfation of unknown(C24H39NO9S) (Pubchem CID:-) (DCABM ID:BC2904)|hydration of unknown(C25H43NO7) (Pubchem CID:-) (DCABM ID:BC2998)|glycine conjugation of unknown(C27H44N2O7) (Pubchem CID:-) (DCABM ID:BC3556)|glycine conjugation of unknown(C26H42N2O7) (Pubchem CID:-) (DCABM ID:BC1478)|demethylation of unknown(C24H37NO9) (Pubchem CID:-) (DCABM ID:BC1607)|cysteine conjugation of unknown(C28H46N2O7S) (Pubchem CID:-) (DCABM ID:BC1103)|cysteine conjugation of unknown(C28H46N2O10S) (Pubchem CID:-) (DCABM ID:BC3051)|cysteine conjugation of unknown(C27H44N2O6S) (Pubchem CID:-) (DCABM ID:BC1638)|acetylation of unknown(C26H41NO6) (Pubchem CID:-) (DCABM ID:BC2074)|demethylated metabolite of talatizamine(C23H37NO5) (Pubchem CID:-) (DCABM ID:BC1588)|demethylated metabolite of neoline(C23H37NO6) (Pubchem CID:-) (DCABM ID:BC2616)|demethylated metabolite of isotalatizidine(C22H35NO5) (Pubchem CID:-) (DCABM ID:BC1449)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metabolite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄芪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUANG QI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Astragali Radix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Astragalus membranaceus (Fisch.) Bunge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formononetin(C16H12O4) (Pubchem CID:5280378) (DCABM ID:BC1373_S)|calycosin(C16H12O5) (Pubchem CID:5280448) (DCABM ID:BC2822_S)|sulfate conjugation of unknown(C16H12O7S) (Pubchem CID:-) (DCABM ID:BC409)|s-cysteine conjugation of unknown(C19H17NO7S) (Pubchem CID:-) (DCABM ID:BC652)|hydroxylation + glucuronide conjugation of unknown(C22H20O11) (Pubchem CID:-) (DCABM ID:BC1668)|glucuronide conjugation of unknown(C21H21O9) (Pubchem CID:-) (DCABM ID:BC802)|decarboxylation + glucuronidation of unknown(C21H20O10) (Pubchem CID:-) (DCABM ID:BC635)|ononin(C22H22O9) (Pubchem CID:442813) (DCABM ID:BC1324_S)|methylnissolin(C17H16O5) (Pubchem CID:5319733) (DCABM ID:BC190_S)|calycosin 7-o-glucoside(C22H22O10) (Pubchem CID:5318267) (DCABM ID:BC465_S)|astragaloside iv(C41H68O14) (Pubchem CID:13943297) (DCABM ID:BC2906_S)|9,10-dimethoxypterocarpan-3-o-beta-d-glucoside(C23H26O10) (Pubchem CID:86566448) (DCABM ID:BC1147_S)|(r)-isomucronulatol(C17H18O5) (Pubchem CID:10380176) (DCABM ID:BC1554_S)|astragaloside ii(C43H70O15) (Pubchem CID:13996693) (DCABM ID:BC2112_S)|formononetin 7-o-glucuronide(C22H20O10) (Pubchem CID:71316927) (DCABM ID:BC1923_S)|daidzein-7-o-glucuronide(C21H18O10) (Pubchem CID:11316354) (DCABM ID:BC1514_S)|calycosin-7-β-glucoside-3'-glucuronide(C28H30O16) (Pubchem CID:-) (DCABM ID:BC424)|calycosin-3'-o-glucuronide(C22H20O11) (Pubchem CID:-) (DCABM ID:BC2660)|tyrosine(C9H11NO3) (Pubchem CID:6057) (DCABM ID:BC2240_S)|tryptophan(C11H12N2O2) (Pubchem CID:6305) (DCABM ID:BC542_S)|syringin(C17H24O9) (Pubchem CID:5316860) (DCABM ID:BC2409_S)|syringic acid(C9H10O5) (Pubchem CID:10742) (DCABM ID:BC1295_S)|syringaldehyde(C9H10O4) (Pubchem CID:8655) (DCABM ID:BC3250_S)|soyasaponin i(C48H78O18) (Pubchem CID:122097) (DCABM ID:BC2991_S)|sinapic acid(C11H12O5) (Pubchem CID:637775) (DCABM ID:BC389_S)|rhamnocitrin 3,4'-diglucoside(C28H32O16) (Pubchem CID:44259548) (DCABM ID:BC2934_S)|raffinose(C18H32O16) (Pubchem CID:439242) (DCABM ID:BC3267_S)|pratensein 7-o-glucoside(C22H22O11) (Pubchem CID:44257307) (DCABM ID:BC192_S)|phenylalanine(C9H11NO2) (Pubchem CID:6140) (DCABM ID:BC2196_S)|nicotinic acid(C6H5NO2) (Pubchem CID:938) (DCABM ID:BC3558_S)|markhamioside f(C19H26O13) (Pubchem CID:101182651) (DCABM ID:BC363_S)|leucine(C6H13NO2) (Pubchem CID:6106) (DCABM ID:BC3158_S)|isomucronulatol-2',5'-di-o-glucoside(C29H38O16) (Pubchem CID:-) (DCABM ID:BC2364)|isomucronulatol 7-o-glucoside(C23H28O10) (Pubchem CID:125142) (DCABM ID:BC2238_S)|isomucronulatol 7,2'-di-o-glucoside(C29H38O15) (Pubchem CID:15689653) (DCABM ID:BC2298_S)|isoferulic acid(C10H10O4) (Pubchem CID:736186) (DCABM ID:BC957_S)|isoastragaloside i(C45H72O16) (Pubchem CID:60148697) (DCABM ID:BC1030_S)|hexose(C6H12O6) (Pubchem CID:206) (DCABM ID:BC999_S)|gamma-aminobutyric acid(C4H9NO2) (Pubchem CID:119) (DCABM ID:BC3118_S)|ferulic acid(C10H10O4) (Pubchem CID:445858) (DCABM ID:BC2197_S)|emodin-di-o-glucoside(C27H30O15) (Pubchem CID:-) (DCABM ID:BC1696)|2-(hydroxymethyl)-6-[[3,4,5-trihydroxy-5-(hydroxymethyl)oxolan-2-yl]methoxy]oxane-3,4,5-triol(C12H22O11) (Pubchem CID:3749604) (DCABM ID:BC3220_S)|cosmosiin(C21H20O10) (Pubchem CID:5280704) (DCABM ID:BC2297_S)|nona-2,4-dienoic acid(C9H14O2) (Pubchem CID:54498674) (DCABM ID:BC1786_S)|choline(C5H14NO+) (Pubchem CID:305) (DCABM ID:BC2275_S)|caffeic acid(C9H8O4) (Pubchem CID:689043) (DCABM ID:BC672_S)|azelaic acid(C9H16O4) (Pubchem CID:2266) (DCABM ID:BC3501_S)|wistariasaponin c(C47H76O17) (Pubchem CID:21634074) (DCABM ID:BC2092_S)|astragaloside vii(C47H78O19) (Pubchem CID:14241100) (DCABM ID:BC1153_S)|astragaloside vi(C47H78O19) (Pubchem CID:71448940) (DCABM ID:BC2412_S)|astragaloside v(C47H78O19) (Pubchem CID:71448939) (DCABM ID:BC3423_S)|astragaloside iii(C41H68O14) (Pubchem CID:441905) (DCABM ID:BC3608_S)|astrasieversianin iv(C45H72O16) (Pubchem CID:13996685) (DCABM ID:BC1413_S)|asparagine(C4H8N2O3) (Pubchem CID:6267) (DCABM ID:BC3092_S)|adenosine(C10H13N5O4) (Pubchem CID:60961) (DCABM ID:BC910_S)|acetyl astragaloside i(C47H74O17) (Pubchem CID:-) (DCABM ID:BC3342)|6''-o-acetylononin(C24H24O10) (Pubchem CID:102463148) (DCABM ID:BC324_S)|3,4-dihydroxybenzoic acid(C7H6O4) (Pubchem CID:72) (DCABM ID:BC3682_S)|cyclocanthoside e(C41H70O14) (Pubchem CID:21633193) (DCABM ID:BC451_S)|sulfated isomucronulatol(C17H18O8S) (Pubchem CID:-) (DCABM ID:BC142)|sulfated formononetin(C16H12O7S) (Pubchem CID:-) (DCABM ID:BC3277)|sulfated calycosin(C16H12O8S) (Pubchem CID:-) (DCABM ID:BC2760)|rhamnocitrin(C16H12O6) (Pubchem CID:5320946) (DCABM ID:BC2623_S)|isomucronulatol(C17H18O5) (Pubchem CID:602152) (DCABM ID:BC3021_S)|glucuronidated rhamnocitrin(C22H20O12) (Pubchem CID:-) (DCABM ID:BC2650)|glucuronidated isomucronulatol(C23H26O11) (Pubchem CID:-) (DCABM ID:BC3336)|formononetin 7-glucuronide(C22H20O10) (Pubchem CID:101220281) (DCABM ID:BC3241_S)|glucuronidated calycosin(C22H20O11) (Pubchem CID:-) (DCABM ID:BC934)|betaine(C5H11NO2) (Pubchem CID:247) (DCABM ID:BC109_S)|5-hydroxy-7,8-dimethoxyflavanone + glucuronide conjugation(C23H24O11) (Pubchem CID:-) (DCABM ID:BC2717)|isomer of 3-hydro-9, 10-dimethoxypterocarpan(C17H16O5) (Pubchem CID:-) (DCABM ID:BC128)|daidzein(C15H10O4) (Pubchem CID:5281708) (DCABM ID:BC33_S)|hydroxylation of calycosin(C16H12O6) (Pubchem CID:-) (DCABM ID:BC714)|glucuronic acid conjugate of formononetin(C22H20O10) (Pubchem CID:-) (DCABM ID:BC22)|glucuronic acid conjugate of demethylcalycosin(C21H18O11) (Pubchem CID:-) (DCABM ID:BC3376)|glucuronic acid conjugate of daidzein(C21H18O10) (Pubchem CID:-) (DCABM ID:BC1536)|glucuronic acid conjugate of calycosin(C22H20O11) (Pubchem CID:-) (DCABM ID:BC174)|glucuronic acid conjugate of 3-hydro-9, 10-dimp(C23H24O11) (Pubchem CID:-) (DCABM ID:BC2495)|kaempferitrin(C27H30O14) (Pubchem CID:5486199) (DCABM ID:BC1938_S)|astragaloside-ii(C41H66O15) (Pubchem CID:71306915) (DCABM ID:BC1611_S)|3,4-dihydro-3-(2-hydroxy-3,4-dimethoxyphenyl)-2h-1-benzopyran-7-yl beta-d-glucopyranoside(C23H28O10) (Pubchem CID:53461957) (DCABM ID:BC2635_S)|wogonin(C16H12O5) (Pubchem CID:5281703) (DCABM ID:BC89_S)|nicotiflorin(C27H30O15) (Pubchem CID:5318767) (DCABM ID:BC2356_S)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formononetin(C16H12O4) (Pubchem CID:5280378) (DCABM ID:BC1373_S)|calycosin(C16H12O5) (Pubchem CID:5280448) (DCABM ID:BC2822_S)|tyrosine(C9H11NO3) (Pubchem CID:6057) (DCABM ID:BC2240_S)|tryptophan(C11H12N2O2) (Pubchem CID:6305) (DCABM ID:BC542_S)|syringin(C17H24O9) (Pubchem CID:5316860) (DCABM ID:BC2409_S)|syringic acid(C9H10O5) (Pubchem CID:10742) (DCABM ID:BC1295_S)|syringaldehyde(C9H10O4) (Pubchem CID:8655) (DCABM ID:BC3250_S)|soyasaponin i(C48H78O18) (Pubchem CID:122097) (DCABM ID:BC2991_S)|sinapic acid(C11H12O5) (Pubchem CID:637775) (DCABM ID:BC389_S)|rhamnocitrin 3,4'-diglucoside(C28H32O16) (Pubchem CID:44259548) (DCABM ID:BC2934_S)|raffinose(C18H32O16) (Pubchem CID:439242) (DCABM ID:BC3267_S)|pratensein 7-o-glucoside(C22H22O11) (Pubchem CID:44257307) (DCABM ID:BC192_S)|phenylalanine(C9H11NO2) (Pubchem CID:6140) (DCABM ID:BC2196_S)|ononin(C22H22O9) (Pubchem CID:442813) (DCABM ID:BC1324_S)|nicotinic acid(C6H5NO2) (Pubchem CID:938) (DCABM ID:BC3558_S)|markhamioside f(C19H26O13) (Pubchem CID:101182651) (DCABM ID:BC363_S)|leucine(C6H13NO2) (Pubchem CID:6106) (DCABM ID:BC3158_S)|isomucronulatol-2',5'-di-o-glucoside(C29H38O16) (Pubchem CID:-) (DCABM ID:BC2364)|isomucronulatol 7-o-glucoside(C23H28O10) (Pubchem CID:125142) (DCABM ID:BC2238_S)|isomucronulatol 7,2'-di-o-glucoside(C29H38O15) (Pubchem CID:15689653) (DCABM ID:BC2298_S)|isoferulic acid(C10H10O4) (Pubchem CID:736186) (DCABM ID:BC957_S)|isoastragaloside i(C45H72O16) (Pubchem CID:60148697) (DCABM ID:BC1030_S)|hexose(C6H12O6) (Pubchem CID:206) (DCABM ID:BC999_S)|gamma-aminobutyric acid(C4H9NO2) (Pubchem CID:119) (DCABM ID:BC3118_S)|ferulic acid(C10H10O4) (Pubchem CID:445858) (DCABM ID:BC2197_S)|emodin-di-o-glucoside(C27H30O15) (Pubchem CID:-) (DCABM ID:BC1696)|2-(hydroxymethyl)-6-[[3,4,5-trihydroxy-5-(hydroxymethyl)oxolan-2-yl]methoxy]oxane-3,4,5-triol(C12H22O11) (Pubchem CID:3749604) (DCABM ID:BC3220_S)|cosmosiin(C21H20O10) (Pubchem CID:5280704) (DCABM ID:BC2297_S)|nona-2,4-dienoic acid(C9H14O2) (Pubchem CID:54498674) (DCABM ID:BC1786_S)|choline(C5H14NO+) (Pubchem CID:305) (DCABM ID:BC2275_S)|calycosin 7-o-glucoside(C22H22O10) (Pubchem CID:5318267) (DCABM ID:BC465_S)|caffeic acid(C9H8O4) (Pubchem CID:689043) (DCABM ID:BC672_S)|azelaic acid(C9H16O4) (Pubchem CID:2266) (DCABM ID:BC3501_S)|wistariasaponin c(C47H76O17) (Pubchem CID:21634074) (DCABM ID:BC2092_S)|astragaloside vii(C47H78O19) (Pubchem CID:14241100) (DCABM ID:BC1153_S)|astragaloside vi(C47H78O19) (Pubchem CID:71448940) (DCABM ID:BC2412_S)|astragaloside v(C47H78O19) (Pubchem CID:71448939) (DCABM ID:BC3423_S)|astragaloside iv(C41H68O14) (Pubchem CID:13943297) (DCABM ID:BC2906_S)|astragaloside iii(C41H68O14) (Pubchem CID:441905) (DCABM ID:BC3608_S)|astragaloside ii(C43H70O15) (Pubchem CID:13996693) (DCABM ID:BC2112_S)|astrasieversianin iv(C45H72O16) (Pubchem CID:13996685) (DCABM ID:BC1413_S)|asparagine(C4H8N2O3) (Pubchem CID:6267) (DCABM ID:BC3092_S)|adenosine(C10H13N5O4) (Pubchem CID:60961) (DCABM ID:BC910_S)|acetyl astragaloside i(C47H74O17) (Pubchem CID:-) (DCABM ID:BC3342)|9,10-dimethoxypterocarpan-3-o-beta-d-glucoside(C23H26O10) (Pubchem CID:86566448) (DCABM ID:BC1147_S)|6''-o-acetylononin(C24H24O10) (Pubchem CID:102463148) (DCABM ID:BC324_S)|3,4-dihydroxybenzoic acid(C7H6O4) (Pubchem CID:72) (DCABM ID:BC3682_S)|cyclocanthoside e(C41H70O14) (Pubchem CID:21633193) (DCABM ID:BC451_S)|betaine(C5H11NO2) (Pubchem CID:247) (DCABM ID:BC109_S)|isomer of 3-hydro-9, 10-dimethoxypterocarpan(C17H16O5) (Pubchem CID:-) (DCABM ID:BC128)|daidzein(C15H10O4) (Pubchem CID:5281708) (DCABM ID:BC33_S)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sulfate conjugation of unknown(C16H12O7S) (Pubchem CID:-) (DCABM ID:BC409)|s-cysteine conjugation of unknown(C19H17NO7S) (Pubchem CID:-) (DCABM ID:BC652)|hydroxylation + glucuronide conjugation of unknown(C22H20O11) (Pubchem CID:-) (DCABM ID:BC1668)|glucuronide conjugation of unknown(C21H21O9) (Pubchem CID:-) (DCABM ID:BC802)|decarboxylation + glucuronidation of unknown(C21H20O10) (Pubchem CID:-) (DCABM ID:BC635)|sulfated isomucronulatol(C17H18O8S) (Pubchem CID:-) (DCABM ID:BC142)|sulfated formononetin(C16H12O7S) (Pubchem CID:-) (DCABM ID:BC3277)|sulfated calycosin(C16H12O8S) (Pubchem CID:-) (DCABM ID:BC2760)|rhamnocitrin(C16H12O6) (Pubchem CID:5320946) (DCABM ID:BC2623_S)|isomucronulatol(C17H18O5) (Pubchem CID:602152) (DCABM ID:BC3021_S)|glucuronidated rhamnocitrin(C22H20O12) (Pubchem CID:-) (DCABM ID:BC2650)|glucuronidated isomucronulatol(C23H26O11) (Pubchem CID:-) (DCABM ID:BC3336)|formononetin 7-glucuronide(C22H20O10) (Pubchem CID:101220281) (DCABM ID:BC3241_S)|glucuronidated calycosin(C22H20O11) (Pubchem CID:-) (DCABM ID:BC934)|5-hydroxy-7,8-dimethoxyflavanone + glucuronide conjugation(C23H24O11) (Pubchem CID:-) (DCABM ID:BC2717)|hydroxylation of calycosin(C16H12O6) (Pubchem CID:-) (DCABM ID:BC714)|glucuronic acid conjugate of formononetin(C22H20O10) (Pubchem CID:-) (DCABM ID:BC22)|glucuronic acid conjugate of demethylcalycosin(C21H18O11) (Pubchem CID:-) (DCABM ID:BC3376)|glucuronic acid conjugate of daidzein(C21H18O10) (Pubchem CID:-) (DCABM ID:BC1536)|glucuronic acid conjugate of calycosin(C22H20O11) (Pubchem CID:-) (DCABM ID:BC174)|glucuronic acid conjugate of 3-hydro-9, 10-dimp(C23H24O11) (Pubchem CID:-) (DCABM ID:BC2495)|(r)-isomucronulatol(C17H18O5) (Pubchem CID:10380176) (DCABM ID:BC1554_S)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白术</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAI ZHU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atractylodis Macrocephalae Rhizoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atractylodes macrocephala Koidz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">umbelliferone(C9H6O3) (Pubchem CID:5281426) (DCABM ID:BC2631_S)|atractylenolide ii(C15H20O2) (Pubchem CID:14448070) (DCABM ID:BC1972_S)|atractylenolide i(C15H18O2) (Pubchem CID:5321018) (DCABM ID:BC1945_S)|atractylenolide iii(C15H20O3) (Pubchem CID:155948) (DCABM ID:BC206_S)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">茯苓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FU LING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poria Cocos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poria cocos (Schw.) Wolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vanillin(C8H8O3) (Pubchem CID:1183) (DCABM ID:BC2864_S)|sucrose(C12H22O11) (Pubchem CID:5988) (DCABM ID:BC2506_S)|succinic acid(C4H6O4) (Pubchem CID:1110) (DCABM ID:BC3362_S)|3,4-dihydroxybenzoic acid(C7H6O4) (Pubchem CID:72) (DCABM ID:BC3682_S)|d-mannose(C6H12O6) (Pubchem CID:18950) (DCABM ID:BC496_S)|citric acid(C6H8O7) (Pubchem CID:311) (DCABM ID:BC171_S)|azelaic acid(C9H16O4) (Pubchem CID:2266) (DCABM ID:BC3501_S)|3-tert-butyladipic acid(C10H18O4) (Pubchem CID:98967) (DCABM ID:BC176_S)|oxidation,glucuronide conjugation of benzoic acid(C13H14O9) (Pubchem CID:-) (DCABM ID:BC2642)|dehydrotumulosic acid(C31H48O4) (Pubchem CID:15225964) (DCABM ID:BC2465_S)|2-[(2r,3r,3ar,6s,7s,9br)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid(C30H44O5) (Pubchem CID:3086648) (DCABM ID:BC186_S)|3β,16α- dihydroxylanostene-triene-21-acid(C30H46O4) (Pubchem CID:-) (DCABM ID:BC1483)|poricoic acid e(C30H44O6) (Pubchem CID:15225966) (DCABM ID:BC1246_S)|tumulosic acid(C31H50O4) (Pubchem CID:12314446) (DCABM ID:BC1732_S)|dehydropachymic acid(C33H50O5) (Pubchem CID:15226717) (DCABM ID:BC373_S)|poricoic acid h(C31H48O5) (Pubchem CID:10918099) (DCABM ID:BC539_S)|poricoic acid g(C30H46O5) (Pubchem CID:5471966) (DCABM ID:BC2007_S)|fomefficinic acid a(C31H48O3) (Pubchem CID:11431307) (DCABM ID:BC1561_S)|daedaleanic acid a(C31H46O4) (Pubchem CID:11179164) (DCABM ID:BC1869_S)|adenine(C5H5N5) (Pubchem CID:190) (DCABM ID:BC3652_S)|3β-hydroxy-16α-acetoxy-lanosta-7,9(11),24-trien-21-oic acid(C32H48O5) (Pubchem CID:-) (DCABM ID:BC2201)|3β,16α-dihydroxylanosta-7,9(11),24-trien-21-oic acid(C30H46O4) (Pubchem CID:-) (DCABM ID:BC333)|6,7-dehydroporicoic acid h(C31H46O5) (Pubchem CID:44556878) (DCABM ID:BC3636_S)|16-deoxyporicoic acid b(C30H44O4) (Pubchem CID:16736458) (DCABM ID:BC811_S)|(r)-dimethyl 2-hydroxysuccinate(C6H10O5) (Pubchem CID:11062697) (DCABM ID:BC2757_S)|unknown(C33H48O4) (Pubchem CID:-) (DCABM ID:BC2224)|(5ξ,20s)-24- methylene-3- oxolanosta-7,9(11)- dien-21-oic acid(C31H46O3) (Pubchem CID:-) (DCABM ID:BC2214)|trametenolic acid(C30H48O3) (Pubchem CID:12309443) (DCABM ID:BC2079_S)|poricoic acid f(C31H46O6) (Pubchem CID:101928114) (DCABM ID:BC1176_S)|poricoic acid am(C32H48O5) (Pubchem CID:46882717) (DCABM ID:BC1279_S)|(2r)-2-[(3s,5r,10s,13r,14r,16r,17r)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid(C30H46O5) (Pubchem CID:137648664) (DCABM ID:BC1974_S)|(2r)-2-[(3r,5r,10s,13r,14r,16r,17r)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid(C30H46O5) (Pubchem CID:137654023) (DCABM ID:BC664_S)|polyporenic acid c(C31H46O4) (Pubchem CID:9805290) (DCABM ID:BC2675_S)|pachymic acid(C33H52O5) (Pubchem CID:5484385) (DCABM ID:BC3085_S)|eburicoic acid(C31H50O3) (Pubchem CID:73402) (DCABM ID:BC1971_S)|6-hydroxy-dehydrotumulosic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC571)|3β-hydroxy-16-acetoxylanosta-7,-9(11)-24-trien-21-oic acid(C32H48O5) (Pubchem CID:-) (DCABM ID:BC836)|3β,16α-dihydroxy-lanosta-8,24-dien-21-oic acid(C30H48O4) (Pubchem CID:-) (DCABM ID:BC2049)|3β,16α-dihydroxy-7-oxolanosta-8,24-dien-21-oic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC138)|3α,16β-dihydroxylanosta-7,9(11),24-trien-21-oic acid(C30H46O4) (Pubchem CID:-) (DCABM ID:BC3308)|3-oxo-16α-hydroxylanosta-7,9(11),24-trien-21-oic acid(C31H44O4) (Pubchem CID:-) (DCABM ID:BC1586)|3-o-acetyl-16α,26-dihydroxytrametenolic acid(C32H50O6) (Pubchem CID:-) (DCABM ID:BC1438)|3-o-acetyl-16alpha-hydroxytrametenolic acid(C32H50O5) (Pubchem CID:15226712) (DCABM ID:BC2731_S)|3-o-16α,25-dihydroxy-lanosta-8,24(3)-dieen-21-oic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC1057)|3-epidehydrotumulosic acid(C31H48O4) (Pubchem CID:10005581) (DCABM ID:BC514_S)|3-epidehydropachymic acid(C33H50O5) (Pubchem CID:15226716) (DCABM ID:BC2875_S)|3-epi-(3'-hydroxy-3'-methylglutaryloxyl)-dehydrotum ulosic acid(C37H56O8) (Pubchem CID:-) (DCABM ID:BC2949)|3-dehydrotrametenolic acid(C30H46O3) (Pubchem CID:15391340) (DCABM ID:BC3203_S)|29-hydroxydehydropachymic acid(C33H50O6) (Pubchem CID:137355885) (DCABM ID:BC54_S)|26-hydroxy-poricoic acid g(C30H46O6) (Pubchem CID:-) (DCABM ID:BC1196)|26-hydroxy-dehydrotumuloosic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC1698)|25α-hydroxytumulosic acid(C31H50O5) (Pubchem CID:-) (DCABM ID:BC1530)|25-hydroxytumulosic acid(C31H50O5) (Pubchem CID:-) (DCABM ID:BC1838)|25-hydroxyporicoic acid h(C31H48O6) (Pubchem CID:16736865) (DCABM ID:BC1420_S)|25-hydroxypachymic acid(C33H52O6) (Pubchem CID:-) (DCABM ID:BC1594)|25-hydroxl-3β,16α-diacetoxylanosta-8-en-21-oic acid(C35H54O7) (Pubchem CID:-) (DCABM ID:BC1714)|25-hydroxyporicoic acid c(C31H46O5) (Pubchem CID:44556811) (DCABM ID:BC1079_S)|16α,25-hydroxydehydroeburicoinic acid(C31H46O5) (Pubchem CID:-) (DCABM ID:BC1626)|daedaleanic acid b(C30H48O5) (Pubchem CID:11465951) (DCABM ID:BC2276_S)|poricoic acid ce(C33H50O4) (Pubchem CID:102480393) (DCABM ID:BC3473_S)|tumulosic acid +o(C31H50O5) (Pubchem CID:-) (DCABM ID:BC3266)|trametenolic acid+o2-h2(C30H46O5) (Pubchem CID:-) (DCABM ID:BC726)|trametenolic acid+o2(C30H48O5) (Pubchem CID:-) (DCABM ID:BC2563)|poricoic bm+o-h2(C32H48O5) (Pubchem CID:-) (DCABM ID:BC2771)|poricoic b+o(C31H46O5) (Pubchem CID:-) (DCABM ID:BC2560)|poricoic acid h+o(C31H46O6) (Pubchem CID:-) (DCABM ID:BC2183)|polyporenic acid c+o(C31H46O5) (Pubchem CID:-) (DCABM ID:BC2857)|hydroxyporicoic acid h+o(C31H48O6) (Pubchem CID:-) (DCABM ID:BC3372)|eburiconic acid+o2-h2(C31H48O4) (Pubchem CID:-) (DCABM ID:BC378)|eburiconic acid +o(C31H50O4) (Pubchem CID:-) (DCABM ID:BC2699)|dehydrotumulosic acid+o-2h(C31H46O5) (Pubchem CID:-) (DCABM ID:BC2674)|dehydrotumulosic acid+2o-2h(C31H46O6) (Pubchem CID:-) (DCABM ID:BC1527)|dehydrotumulosic acid+o2(C31H48O6) (Pubchem CID:-) (DCABM ID:BC1630)|dehydrotumulosic acid +o(C31H48O5) (Pubchem CID:-) (DCABM ID:BC2885)|dehydrotrametenoic acid +o-h2(C30H46O4) (Pubchem CID:-) (DCABM ID:BC1856)|dehydrotrametenoic acid +o(C30H48O4) (Pubchem CID:-) (DCABM ID:BC1296)|16-oxy-acetoxypachymic acid methyl ester)(C36H56O6) (Pubchem CID:-) (DCABM ID:BC107)|16-oxy-acetoxypachymic acid(C35H54O6) (Pubchem CID:-) (DCABM ID:BC3218)|ursolic acid acetate(C32H50O4) (Pubchem CID:6475119) (DCABM ID:BC3306_S)|methyl (2r)-2-[(3s,5r,10s,13r,14r,16r,17r)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoate(C34H54O5) (Pubchem CID:72202422) (DCABM ID:BC2006_S)|pachymic acid c(C31H46O4) (Pubchem CID:-) (DCABM ID:BC1316)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vanillin(C8H8O3) (Pubchem CID:1183) (DCABM ID:BC2864_S)|sucrose(C12H22O11) (Pubchem CID:5988) (DCABM ID:BC2506_S)|succinic acid(C4H6O4) (Pubchem CID:1110) (DCABM ID:BC3362_S)|3,4-dihydroxybenzoic acid(C7H6O4) (Pubchem CID:72) (DCABM ID:BC3682_S)|d-mannose(C6H12O6) (Pubchem CID:18950) (DCABM ID:BC496_S)|citric acid(C6H8O7) (Pubchem CID:311) (DCABM ID:BC171_S)|azelaic acid(C9H16O4) (Pubchem CID:2266) (DCABM ID:BC3501_S)|3-tert-butyladipic acid(C10H18O4) (Pubchem CID:98967) (DCABM ID:BC176_S)|dehydrotumulosic acid(C31H48O4) (Pubchem CID:15225964) (DCABM ID:BC2465_S)|2-[(2r,3r,3ar,6s,7s,9br)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid(C30H44O5) (Pubchem CID:3086648) (DCABM ID:BC186_S)|3β,16α- dihydroxylanostene-triene-21-acid(C30H46O4) (Pubchem CID:-) (DCABM ID:BC1483)|poricoic acid e(C30H44O6) (Pubchem CID:15225966) (DCABM ID:BC1246_S)|tumulosic acid(C31H50O4) (Pubchem CID:12314446) (DCABM ID:BC1732_S)|poricoic acid h(C31H48O5) (Pubchem CID:10918099) (DCABM ID:BC539_S)|poricoic acid g(C30H46O5) (Pubchem CID:5471966) (DCABM ID:BC2007_S)|fomefficinic acid a(C31H48O3) (Pubchem CID:11431307) (DCABM ID:BC1561_S)|daedaleanic acid a(C31H46O4) (Pubchem CID:11179164) (DCABM ID:BC1869_S)|adenine(C5H5N5) (Pubchem CID:190) (DCABM ID:BC3652_S)|3β-hydroxy-16α-acetoxy-lanosta-7,9(11),24-trien-21-oic acid(C32H48O5) (Pubchem CID:-) (DCABM ID:BC2201)|3β,16α-dihydroxylanosta-7,9(11),24-trien-21-oic acid(C30H46O4) (Pubchem CID:-) (DCABM ID:BC333)|6,7-dehydroporicoic acid h(C31H46O5) (Pubchem CID:44556878) (DCABM ID:BC3636_S)|16-deoxyporicoic acid b(C30H44O4) (Pubchem CID:16736458) (DCABM ID:BC811_S)|(r)-dimethyl 2-hydroxysuccinate(C6H10O5) (Pubchem CID:11062697) (DCABM ID:BC2757_S)|trametenolic acid(C30H48O3) (Pubchem CID:12309443) (DCABM ID:BC2079_S)|poricoic acid f(C31H46O6) (Pubchem CID:101928114) (DCABM ID:BC1176_S)|poricoic acid am(C32H48O5) (Pubchem CID:46882717) (DCABM ID:BC1279_S)|(2r)-2-[(3s,5r,10s,13r,14r,16r,17r)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid(C30H46O5) (Pubchem CID:137648664) (DCABM ID:BC1974_S)|(2r)-2-[(3r,5r,10s,13r,14r,16r,17r)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid(C30H46O5) (Pubchem CID:137654023) (DCABM ID:BC664_S)|polyporenic acid c(C31H46O4) (Pubchem CID:9805290) (DCABM ID:BC2675_S)|pachymic acid(C33H52O5) (Pubchem CID:5484385) (DCABM ID:BC3085_S)|eburicoic acid(C31H50O3) (Pubchem CID:73402) (DCABM ID:BC1971_S)|dehydropachymic acid(C33H50O5) (Pubchem CID:15226717) (DCABM ID:BC373_S)|6-hydroxy-dehydrotumulosic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC571)|3β-hydroxy-16-acetoxylanosta-7,-9(11)-24-trien-21-oic acid(C32H48O5) (Pubchem CID:-) (DCABM ID:BC836)|3β,16α-dihydroxy-lanosta-8,24-dien-21-oic acid(C30H48O4) (Pubchem CID:-) (DCABM ID:BC2049)|3β,16α-dihydroxy-7-oxolanosta-8,24-dien-21-oic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC138)|3α,16β-dihydroxylanosta-7,9(11),24-trien-21-oic acid(C30H46O4) (Pubchem CID:-) (DCABM ID:BC3308)|3-oxo-16α-hydroxylanosta-7,9(11),24-trien-21-oic acid(C31H44O4) (Pubchem CID:-) (DCABM ID:BC1586)|3-o-acetyl-16α,26-dihydroxytrametenolic acid(C32H50O6) (Pubchem CID:-) (DCABM ID:BC1438)|3-o-acetyl-16alpha-hydroxytrametenolic acid(C32H50O5) (Pubchem CID:15226712) (DCABM ID:BC2731_S)|3-o-16α,25-dihydroxy-lanosta-8,24(3)-dieen-21-oic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC1057)|3-epidehydrotumulosic acid(C31H48O4) (Pubchem CID:10005581) (DCABM ID:BC514_S)|3-epidehydropachymic acid(C33H50O5) (Pubchem CID:15226716) (DCABM ID:BC2875_S)|3-epi-(3'-hydroxy-3'-methylglutaryloxyl)-dehydrotum ulosic acid(C37H56O8) (Pubchem CID:-) (DCABM ID:BC2949)|3-dehydrotrametenolic acid(C30H46O3) (Pubchem CID:15391340) (DCABM ID:BC3203_S)|29-hydroxydehydropachymic acid(C33H50O6) (Pubchem CID:137355885) (DCABM ID:BC54_S)|26-hydroxy-poricoic acid g(C30H46O6) (Pubchem CID:-) (DCABM ID:BC1196)|26-hydroxy-dehydrotumuloosic acid(C31H48O5) (Pubchem CID:-) (DCABM ID:BC1698)|25α-hydroxytumulosic acid(C31H50O5) (Pubchem CID:-) (DCABM ID:BC1530)|25-hydroxytumulosic acid(C31H50O5) (Pubchem CID:-) (DCABM ID:BC1838)|25-hydroxyporicoic acid h(C31H48O6) (Pubchem CID:16736865) (DCABM ID:BC1420_S)|25-hydroxypachymic acid(C33H52O6) (Pubchem CID:-) (DCABM ID:BC1594)|25-hydroxl-3β,16α-diacetoxylanosta-8-en-21-oic acid(C35H54O7) (Pubchem CID:-) (DCABM ID:BC1714)|25-hydroxyporicoic acid c(C31H46O5) (Pubchem CID:44556811) (DCABM ID:BC1079_S)|16α,25-hydroxydehydroeburicoinic acid(C31H46O5) (Pubchem CID:-) (DCABM ID:BC1626)|daedaleanic acid b(C30H48O5) (Pubchem CID:11465951) (DCABM ID:BC2276_S)|poricoic acid ce(C33H50O4) (Pubchem CID:102480393) (DCABM ID:BC3473_S)|ursolic acid acetate(C32H50O4) (Pubchem CID:6475119) (DCABM ID:BC3306_S)|pachymic acid c(C31H46O4) (Pubchem CID:-) (DCABM ID:BC1316)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxidation,glucuronide conjugation of benzoic acid(C13H14O9) (Pubchem CID:-) (DCABM ID:BC2642)|tumulosic acid(C31H50O4) (Pubchem CID:12314446) (DCABM ID:BC1732_S)|dehydropachymic acid(C33H50O5) (Pubchem CID:15226717) (DCABM ID:BC373_S)|unknown(C33H48O4) (Pubchem CID:-) (DCABM ID:BC2224)|(5ξ,20s)-24- methylene-3- oxolanosta-7,9(11)- dien-21-oic acid(C31H46O3) (Pubchem CID:-) (DCABM ID:BC2214)|tumulosic acid +o(C31H50O5) (Pubchem CID:-) (DCABM ID:BC3266)|trametenolic acid+o2-h2(C30H46O5) (Pubchem CID:-) (DCABM ID:BC726)|trametenolic acid+o2(C30H48O5) (Pubchem CID:-) (DCABM ID:BC2563)|poricoic bm+o-h2(C32H48O5) (Pubchem CID:-) (DCABM ID:BC2771)|poricoic b+o(C31H46O5) (Pubchem CID:-) (DCABM ID:BC2560)|poricoic acid h+o(C31H46O6) (Pubchem CID:-) (DCABM ID:BC2183)|polyporenic acid c+o(C31H46O5) (Pubchem CID:-) (DCABM ID:BC2857)|hydroxyporicoic acid h+o(C31H48O6) (Pubchem CID:-) (DCABM ID:BC3372)|eburiconic acid+o2-h2(C31H48O4) (Pubchem CID:-) (DCABM ID:BC378)|eburiconic acid +o(C31H50O4) (Pubchem CID:-) (DCABM ID:BC2699)|dehydrotumulosic acid+o-2h(C31H46O5) (Pubchem CID:-) (DCABM ID:BC2674)|dehydrotumulosic acid+2o-2h(C31H46O6) (Pubchem CID:-) (DCABM ID:BC1527)|dehydrotumulosic acid+o2(C31H48O6) (Pubchem CID:-) (DCABM ID:BC1630)|dehydrotumulosic acid +o(C31H48O5) (Pubchem CID:-) (DCABM ID:BC2885)|dehydrotrametenoic acid +o-h2(C30H46O4) (Pubchem CID:-) (DCABM ID:BC1856)|dehydrotrametenoic acid +o(C30H48O4) (Pubchem CID:-) (DCABM ID:BC1296)|2-[(2r,3r,3ar,6s,7s,9br)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid(C30H44O5) (Pubchem CID:3086648) (DCABM ID:BC186_S)|3β-hydroxy-16-acetoxylanosta-7,-9(11)-24-trien-21-oic acid(C32H48O5) (Pubchem CID:-) (DCABM ID:BC836)|3-dehydrotrametenolic acid(C30H46O3) (Pubchem CID:15391340) (DCABM ID:BC3203_S)|16-oxy-acetoxypachymic acid methyl ester)(C36H56O6) (Pubchem CID:-) (DCABM ID:BC107)|16-oxy-acetoxypachymic acid(C35H54O6) (Pubchem CID:-) (DCABM ID:BC3218)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白芍</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAI SHAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paeoniae Radix Alba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paeonia lactiflora Pall.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paeoniflorin(C23H28O11) (Pubchem CID:442534) (DCABM ID:BC1367_S)|desbenzoylpaeoniflorin(C16H24O10) (Pubchem CID:-) (DCABM ID:BC741)|pinellic acid(C18H34O5) (Pubchem CID:9858729) (DCABM ID:BC3302_S)|oxidation of unknown(C23H28O12) (Pubchem CID:-) (DCABM ID:BC1984)|methylation of unknown(C24H30O11) (Pubchem CID:-) (DCABM ID:BC622)|glucuronide conjugation of unknown(C29H36O17) (Pubchem CID:-) (DCABM ID:BC5)|gallic acid(C7H6O5) (Pubchem CID:370) (DCABM ID:BC2804_S)|cianidanol(C15H14O6) (Pubchem CID:9064) (DCABM ID:BC3510_S)|[(1r,4r)-4-hydroxy-6-methyl-8-oxo-1-[(2s,3r,4s,5s,6r)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-7-oxatricyclo[4.3.0.03,9]nonan-9-yl]methyl benzoate(C23H28O11) (Pubchem CID:51346141) (DCABM ID:BC3242_S)|(-)-epicatechin(C15H14O6) (Pubchem CID:72276) (DCABM ID:BC2294_S)|gallic acid glucuronide(C13H14O11) (Pubchem CID:-) (DCABM ID:BC1220)|ferulic acid 4-sulfate(C10H10O7S) (Pubchem CID:6305574) (DCABM ID:BC3254_S)|3'-o-methyl (epi)catechin 7- or 4'-o-glucuronide(C22H24O12) (Pubchem CID:-) (DCABM ID:BC1507)|3-methoxy-4-hydroxy-phenylpropionic acid sulfate(C10H12O7S) (Pubchem CID:-) (DCABM ID:BC2704)|unknown(C9H10O3) (Pubchem CID:-) (DCABM ID:BC2922)|oxypaeoniflora(C23H28O12) (Pubchem CID:21631105) (DCABM ID:BC388_S)|paeoniflorin sulfonate(C23H28O14S) (Pubchem CID:101382399) (DCABM ID:BC245_S)|galloyl paeoniflorin or galloylalbiflorin(C30H32O15) (Pubchem CID:-) (DCABM ID:BC2915)|debenzoylgalloylpaeoniflorin(C23H28O14) (Pubchem CID:101001427) (DCABM ID:BC2518_S)|pentagalloylglucose(C41H32O26) (Pubchem CID:65238) (DCABM ID:BC1515_S)|paeoniflorin sulfite(C23H28O13S) (Pubchem CID:162642241) (DCABM ID:BC588_S)|naringenin(C15H12O5) (Pubchem CID:439246) (DCABM ID:BC614_S)|dephenyl paeoniflorin(C16H24O10) (Pubchem CID:-) (DCABM ID:BC1894)|benzoylpaeoniflorin(C30H32O12) (Pubchem CID:21631106) (DCABM ID:BC66_S)|[(1r,2s,3r,5r,6s,8s)-6-hydroxy-8-methyl-3-[(2s,3r,4s,5s,6r)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-2-yl]methyl benzoate(C23H28O11) (Pubchem CID:132616773) (DCABM ID:BC800_S)|isobenzoyl paeoniflorin(C30H32O12) (Pubchem CID:-) (DCABM ID:BC1835)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paeoniflorin(C23H28O11) (Pubchem CID:442534) (DCABM ID:BC1367_S)|desbenzoylpaeoniflorin(C16H24O10) (Pubchem CID:-) (DCABM ID:BC741)|pinellic acid(C18H34O5) (Pubchem CID:9858729) (DCABM ID:BC3302_S)|gallic acid(C7H6O5) (Pubchem CID:370) (DCABM ID:BC2804_S)|cianidanol(C15H14O6) (Pubchem CID:9064) (DCABM ID:BC3510_S)|[(1r,4r)-4-hydroxy-6-methyl-8-oxo-1-[(2s,3r,4s,5s,6r)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-7-oxatricyclo[4.3.0.03,9]nonan-9-yl]methyl benzoate(C23H28O11) (Pubchem CID:51346141) (DCABM ID:BC3242_S)|(-)-epicatechin(C15H14O6) (Pubchem CID:72276) (DCABM ID:BC2294_S)|paeoniflorin sulfonate(C23H28O14S) (Pubchem CID:101382399) (DCABM ID:BC245_S)|galloyl paeoniflorin or galloylalbiflorin(C30H32O15) (Pubchem CID:-) (DCABM ID:BC2915)|debenzoylgalloylpaeoniflorin(C23H28O14) (Pubchem CID:101001427) (DCABM ID:BC2518_S)|pentagalloylglucose(C41H32O26) (Pubchem CID:65238) (DCABM ID:BC1515_S)|oxypaeoniflora(C23H28O12) (Pubchem CID:21631105) (DCABM ID:BC388_S)|benzoylpaeoniflorin(C30H32O12) (Pubchem CID:21631106) (DCABM ID:BC66_S)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxidation of unknown(C23H28O12) (Pubchem CID:-) (DCABM ID:BC1984)|methylation of unknown(C24H30O11) (Pubchem CID:-) (DCABM ID:BC622)|glucuronide conjugation of unknown(C29H36O17) (Pubchem CID:-) (DCABM ID:BC5)|gallic acid glucuronide(C13H14O11) (Pubchem CID:-) (DCABM ID:BC1220)|ferulic acid 4-sulfate(C10H10O7S) (Pubchem CID:6305574) (DCABM ID:BC3254_S)|3'-o-methyl (epi)catechin 7- or 4'-o-glucuronide(C22H24O12) (Pubchem CID:-) (DCABM ID:BC1507)|3-methoxy-4-hydroxy-phenylpropionic acid sulfate(C10H12O7S) (Pubchem CID:-) (DCABM ID:BC2704)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生姜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHENG JIANG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zingiberis Rhizoma Recens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zingiber officinale Roscoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gingerol(C17H26O4) (Pubchem CID:442793) (DCABM ID:BC2314_S)|shogaol(C17H24O3) (Pubchem CID:5281794) (DCABM ID:BC1238_S)|(8)-gingerol(C19H30O4) (Pubchem CID:168114) (DCABM ID:BC3561_S)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gingerol(C17H26O4) (Pubchem CID:442793) (DCABM ID:BC2314_S)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talatisamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H39NO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neoline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H39NO6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">441747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mesaconitine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C33H45NO11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">441737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hypaconitine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C33H45NO10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24832659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">benzoylmesaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H43NO10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20055771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">benzoylaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C32H45NO10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101596809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acetyltalatisamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C26H41NO6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78358526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">benzoylhypaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H43NO9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14163819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">senbusine c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H39NO7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20055812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toroko base ii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25H41NO6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glucuronide conjugation of fuziline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H47NO13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71456946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">songorine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H31NO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">senbusine b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H37NO6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">senbusine a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76189547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8,14-pentol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H39NO9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">245005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aconitine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C34H47NO11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101636479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-hydroxytalatizamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sulfate conjugation of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25H41NO9S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s-cysteine conjugation of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25H36N2O5S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C28H46N2O11S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reduction of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H45NO10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H33NO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">methylation +sulfate conjugation of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H39NO9S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydroxymethylene loss of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydroxylation + sulfation of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydration of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25H43NO7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glycine conjugation of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C27H44N2O7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C26H42N2O7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demethylation of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H37NO9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cysteine conjugation of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C28H46N2O7S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C28H46N2O10S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C27H44N2O6S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acetylation of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122173204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">benzoylmesaconitine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13343336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">441742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carmicheline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H35NO4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21598997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-deoxyaconitine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C34H47NO10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-o-acetyl-talatisamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3084020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-ethyl-16-methoxy-4-(methoxymethyl)aconitane-1,8,14-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H37NO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demethylated metabolite of talatizamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demethylated metabolite of neoline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demethylated metabolite of isotalatizidine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H35NO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dehydrated benzoylmesaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H41O9N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dehydrated benzoylhypaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H41O8N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">441715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cammaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78358536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-oh-mesaconitine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C33H45NO12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acetyltalatizamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C26H41O6N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-oh-benzoylmesaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H43O11N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isotalatisamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102146471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isodelphinine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C33H45NO9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24832662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1s,2r,3r,4r,5r,6s,7s,8r,9r,10r,13s,16s,17r,18r)-5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20054813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jesaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25H41NO9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3047329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">benzoylhypacoitine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,13-deoxybenzoylaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H44NO8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-oh-benzoylaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H43NO11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5280378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formononetin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16H12O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5280448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calycosin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16H12O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16H12O7S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C19H17NO7S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydroxylation + glucuronide conjugation of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H20O11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glucuronide conjugation of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C21H21O9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decarboxylation + glucuronidation of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C21H20O10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">442813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ononin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H22O9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5319733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">methylnissolin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C17H16O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5318267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calycosin 7-o-glucoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H22O10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13943297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">astragaloside iv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C41H68O14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86566448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,10-dimethoxypterocarpan-3-o-beta-d-glucoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H26O10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10380176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(r)-isomucronulatol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C17H18O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13996693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">astragaloside ii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C43H70O15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71316927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formononetin 7-o-glucuronide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H20O10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11316354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daidzein-7-o-glucuronide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C21H18O10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calycosin-7-β-glucoside-3'-glucuronide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C28H30O16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calycosin-3'-o-glucuronide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tyrosine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9H11NO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tryptophan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11H12N2O2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5316860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">syringin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C17H24O9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">syringic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9H10O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">syringaldehyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9H10O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soyasaponin i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C48H78O18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">637775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sinapic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11H12O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44259548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rhamnocitrin 3,4'-diglucoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C28H32O16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">439242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raffinose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C18H32O16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44257307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pratensein 7-o-glucoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H22O11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phenylalanine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9H11NO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nicotinic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6H5NO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101182651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">markhamioside f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C19H26O13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leucine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6H13NO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isomucronulatol-2',5'-di-o-glucoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C29H38O16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isomucronulatol 7-o-glucoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H28O10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15689653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isomucronulatol 7,2'-di-o-glucoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C29H38O15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">736186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isoferulic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10H10O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60148697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isoastragaloside i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C45H72O16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hexose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6H12O6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma-aminobutyric acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4H9NO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">445858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ferulic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emodin-di-o-glucoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C27H30O15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3749604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-(hydroxymethyl)-6-[[3,4,5-trihydroxy-5-(hydroxymethyl)oxolan-2-yl]methoxy]oxane-3,4,5-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C12H22O11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5280704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cosmosiin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54498674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nona-2,4-dienoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9H14O2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5H14NO+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">689043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caffeic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9H8O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">azelaic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9H16O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21634074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wistariasaponin c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C47H76O17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14241100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">astragaloside vii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C47H78O19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71448940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">astragaloside vi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71448939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">astragaloside v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">441905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">astragaloside iii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13996685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">astrasieversianin iv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asparagine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4H8N2O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adenosine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10H13N5O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acetyl astragaloside i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C47H74O17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102463148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6''-o-acetylononin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H24O10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,4-dihydroxybenzoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C7H6O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21633193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cyclocanthoside e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C41H70O14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sulfated isomucronulatol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C17H18O8S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sulfated formononetin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sulfated calycosin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16H12O8S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5320946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rhamnocitrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16H12O6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">602152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isomucronulatol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glucuronidated rhamnocitrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H20O12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glucuronidated isomucronulatol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H26O11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101220281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formononetin 7-glucuronide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glucuronidated calycosin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">betaine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5H11NO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-hydroxy-7,8-dimethoxyflavanone + glucuronide conjugation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H24O11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isomer of 3-hydro-9, 10-dimethoxypterocarpan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5281708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daidzein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15H10O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydroxylation of calycosin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glucuronic acid conjugate of formononetin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glucuronic acid conjugate of demethylcalycosin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C21H18O11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glucuronic acid conjugate of daidzein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glucuronic acid conjugate of calycosin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glucuronic acid conjugate of 3-hydro-9, 10-dimp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5486199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kaempferitrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C27H30O14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71306915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">astragaloside-ii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C41H66O15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53461957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,4-dihydro-3-(2-hydroxy-3,4-dimethoxyphenyl)-2h-1-benzopyran-7-yl beta-d-glucopyranoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5281703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wogonin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5318767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nicotiflorin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5281426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">umbelliferone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9H6O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14448070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">atractylenolide ii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15H20O2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5321018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">atractylenolide i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15H18O2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">atractylenolide iii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15H20O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vanillin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C8H8O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sucrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">succinic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4H6O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d-mannose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">citric acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6H8O7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-tert-butyladipic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10H18O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxidation,glucuronide conjugation of benzoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C13H14O9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15225964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dehydrotumulosic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H48O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3086648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-[(2r,3r,3ar,6s,7s,9br)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H44O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3β,16α- dihydroxylanostene-triene-21-acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H46O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15225966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poricoic acid e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H44O6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12314446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tumulosic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H50O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15226717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dehydropachymic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C33H50O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10918099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poricoic acid h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H48O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5471966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poricoic acid g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H46O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11431307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fomefficinic acid a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H48O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11179164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daedaleanic acid a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H46O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adenine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5H5N5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3β-hydroxy-16α-acetoxy-lanosta-7,9(11),24-trien-21-oic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C32H48O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3β,16α-dihydroxylanosta-7,9(11),24-trien-21-oic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44556878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,7-dehydroporicoic acid h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H46O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16736458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16-deoxyporicoic acid b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H44O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11062697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(r)-dimethyl 2-hydroxysuccinate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6H10O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C33H48O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5ξ,20s)-24- methylene-3- oxolanosta-7,9(11)- dien-21-oic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H46O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12309443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trametenolic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H48O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101928114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poricoic acid f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H46O6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46882717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poricoic acid am</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137648664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2r)-2-[(3s,5r,10s,13r,14r,16r,17r)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137654023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2r)-2-[(3r,5r,10s,13r,14r,16r,17r)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9805290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">polyporenic acid c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5484385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pachymic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C33H52O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eburicoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H50O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-hydroxy-dehydrotumulosic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3β-hydroxy-16-acetoxylanosta-7,-9(11)-24-trien-21-oic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3β,16α-dihydroxy-lanosta-8,24-dien-21-oic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H48O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3β,16α-dihydroxy-7-oxolanosta-8,24-dien-21-oic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3α,16β-dihydroxylanosta-7,9(11),24-trien-21-oic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-oxo-16α-hydroxylanosta-7,9(11),24-trien-21-oic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H44O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-o-acetyl-16α,26-dihydroxytrametenolic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C32H50O6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15226712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-o-acetyl-16alpha-hydroxytrametenolic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C32H50O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-o-16α,25-dihydroxy-lanosta-8,24(3)-dieen-21-oic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10005581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-epidehydrotumulosic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15226716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-epidehydropachymic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-epi-(3'-hydroxy-3'-methylglutaryloxyl)-dehydrotum ulosic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C37H56O8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15391340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-dehydrotrametenolic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H46O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137355885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-hydroxydehydropachymic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C33H50O6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26-hydroxy-poricoic acid g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H46O6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26-hydroxy-dehydrotumuloosic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25α-hydroxytumulosic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H50O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-hydroxytumulosic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16736865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-hydroxyporicoic acid h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H48O6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-hydroxypachymic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C33H52O6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-hydroxl-3β,16α-diacetoxylanosta-8-en-21-oic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C35H54O7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44556811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-hydroxyporicoic acid c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16α,25-hydroxydehydroeburicoinic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11465951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daedaleanic acid b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H48O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102480393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poricoic acid ce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C33H50O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tumulosic acid +o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trametenolic acid+o2-h2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trametenolic acid+o2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poricoic bm+o-h2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poricoic b+o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poricoic acid h+o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">polyporenic acid c+o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydroxyporicoic acid h+o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eburiconic acid+o2-h2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eburiconic acid +o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dehydrotumulosic acid+o-2h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dehydrotumulosic acid+2o-2h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dehydrotumulosic acid+o2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dehydrotumulosic acid +o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dehydrotrametenoic acid +o-h2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dehydrotrametenoic acid +o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16-oxy-acetoxypachymic acid methyl ester)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C36H56O6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16-oxy-acetoxypachymic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C35H54O6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6475119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ursolic acid acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C32H50O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72202422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">methyl (2r)-2-[(3s,5r,10s,13r,14r,16r,17r)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1h-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C34H54O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pachymic acid c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">442534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paeoniflorin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H28O11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desbenzoylpaeoniflorin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16H24O10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9858729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pinellic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C18H34O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxidation of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H28O12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">methylation of unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H30O11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C29H36O17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gallic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C7H6O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cianidanol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15H14O6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51346141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1r,4r)-4-hydroxy-6-methyl-8-oxo-1-[(2s,3r,4s,5s,6r)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-7-oxatricyclo[4.3.0.03,9]nonan-9-yl]methyl benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-)-epicatechin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gallic acid glucuronide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C13H14O11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6305574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ferulic acid 4-sulfate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10H10O7S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3'-o-methyl (epi)catechin 7- or 4'-o-glucuronide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H24O12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-methoxy-4-hydroxy-phenylpropionic acid sulfate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10H12O7S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9H10O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21631105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxypaeoniflora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101382399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paeoniflorin sulfonate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H28O14S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">galloyl paeoniflorin or galloylalbiflorin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H32O15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101001427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">debenzoylgalloylpaeoniflorin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H28O14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pentagalloylglucose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C41H32O26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162642241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paeoniflorin sulfite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H28O13S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">439246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">naringenin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15H12O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dephenyl paeoniflorin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21631106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">benzoylpaeoniflorin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H32O12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132616773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1r,2s,3r,5r,6s,8s)-6-hydroxy-8-methyl-3-[(2s,3r,4s,5s,6r)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-2-yl]methyl benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isobenzoyl paeoniflorin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">442793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gingerol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C17H26O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5281794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shogaol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C17H24O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8)-gingerol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C19H30O4</t>
   </si>
   <si>
     <t xml:space="preserve"> Herb(Chinese)</t>
   </si>
   <si>
-    <t>Herb(Pinyin)</t>
-  </si>
-  <si>
-    <t>Herb(Latin)</t>
-  </si>
-  <si>
-    <t>Herb(English)</t>
-  </si>
-  <si>
-    <t>Compound Name</t>
-  </si>
-  <si>
-    <t>Compound Name (IUPAC)</t>
-  </si>
-  <si>
-    <t>Molecular Formula (g/mol)</t>
-  </si>
-  <si>
-    <t>MolecularWeight</t>
-  </si>
-  <si>
-    <t>Pubchme CID</t>
-  </si>
-  <si>
-    <t>SMILES</t>
-  </si>
-  <si>
-    <t>(R)-(+)-higenamine</t>
-  </si>
-  <si>
-    <t>(1R)-1-[(4-hydroxyphenyl)methyl]-1,2,3,4-tetrahydroisoquinoline-6,7-diol</t>
-  </si>
-  <si>
-    <t>C16H17NO3</t>
-  </si>
-  <si>
-    <t>271.31</t>
-  </si>
-  <si>
-    <t>440988</t>
-  </si>
-  <si>
-    <t>C1CN[C@@H](C2=CC(=C(C=C21)O)O)CC3=CC=C(C=C3)O</t>
-  </si>
-  <si>
-    <t>(S)-(-)-Higenamine</t>
-  </si>
-  <si>
-    <t>(1S)-1-[(4-hydroxyphenyl)methyl]-1,2,3,4-tetrahydroisoquinoline-6,7-diol</t>
-  </si>
-  <si>
-    <t>440927</t>
-  </si>
-  <si>
-    <t>C1CN[C@H](C2=CC(=C(C=C21)O)O)CC3=CC=C(C=C3)O</t>
-  </si>
-  <si>
-    <t>(1R,2R,5R,7R,8R,9R,10R,13R,16S,17R)-11-ethyl-7,16-dihydroxy-13-methyl-6-methylidene-11-azahexacyclo[7.7.2.15,8.01,10.02,8.013,17]nonadecan-4-one</t>
-  </si>
-  <si>
-    <t>357.5</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H]([C@H]31)[C@]56[C@H]4CC(=O)[C@H](C5)C(=C)[C@H]6O)O)C</t>
-  </si>
-  <si>
-    <t>karakoline</t>
-  </si>
-  <si>
-    <t>(1S,2R,3R,4S,5S,6S,8S,9S,13R,16S,17R)-11-ethyl-6-methoxy-13-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8,16-triol</t>
-  </si>
-  <si>
-    <t>377.5</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)O)C</t>
-  </si>
-  <si>
-    <t>isotalatizidine</t>
-  </si>
-  <si>
-    <t>(1S,2R,3R,4S,5S,6S,8S,9S,13S,16S,17R)-11-ethyl-6-methoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8,16-triol</t>
-  </si>
-  <si>
-    <t>407.5</t>
-  </si>
-  <si>
-    <t>16401028</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)O)COC</t>
-  </si>
-  <si>
-    <t>(1S,2R,3R,4S,5S,6S,8S,9S,13S,16S,17R)-11-ethyl-13-(hydroxymethyl)-6,16-dimethoxy-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8-diol</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)CO</t>
-  </si>
-  <si>
-    <t>(1S,2R,3R,4S,5S,6S,8R,9R,13S,16S,17R,18R)-11-ethyl-6-methoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8,16,18-tetrol</t>
-  </si>
-  <si>
-    <t>423.5</t>
-  </si>
-  <si>
-    <t>20056299</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)O)O)COC</t>
-  </si>
-  <si>
-    <t>(1R,2S,3S,4S,5S,6R,7S,8R,9S,10R,13S,16S,17R)-11-ethyl-6-methoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-3,4,7,8,16-pentol</t>
-  </si>
-  <si>
-    <t>C23H37NO7</t>
-  </si>
-  <si>
-    <t>439.5</t>
-  </si>
-  <si>
-    <t>101465272</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H]([C@H]31)[C@]5([C@H]([C@@H]([C@H]6C[C@@H]4[C@@]5([C@H]6O)O)OC)O)O)O)COC</t>
-  </si>
-  <si>
-    <t>(1S,2R,3R,4S,5S,6S,8S,9S,13S,16S,17R)-11-ethyl-6,16-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8-diol</t>
-  </si>
-  <si>
-    <t>421.6</t>
-  </si>
-  <si>
-    <t>441761</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)COC</t>
-  </si>
-  <si>
-    <t>(1R,2S,3S,4S,5S,6S,8S,9S,13S,16S,17R)-11-ethyl-6,16-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-3,4,8-triol</t>
-  </si>
-  <si>
-    <t>437.6</t>
-  </si>
-  <si>
-    <t>177827733</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@]5([C@H]6O)O)OC)O)OC)COC</t>
-  </si>
-  <si>
-    <t>(1R,2S,3R,4S,5S,6S,8S,9S,10R,13S,16S,17R)-11-ethyl-6,16-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-2,4,8-triol</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H]([C@H]31)[C@]5(C[C@@H]([C@H]6C[C@@]4([C@@H]5[C@H]6O)O)OC)O)OC)COC</t>
-  </si>
-  <si>
-    <t>(1S,2R,3R,4S,5S,6S,8R,9R,13S,16S,17R,18R)-11-ethyl-6,18-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8,16-triol</t>
-  </si>
-  <si>
-    <t>10003218</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)O)COC</t>
-  </si>
-  <si>
-    <t>(1S,2R,3R,4S,5S,6R,7S,8R,10R,13S,16S,17R)-11-ethyl-6,18-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,7,8,16-tetrol</t>
-  </si>
-  <si>
-    <t>453.6</t>
-  </si>
-  <si>
-    <t>122362201</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C(C([C@H]31)[C@@]5([C@@H]6[C@H]4C[C@@H]([C@@H]6O)[C@H]([C@@H]5O)OC)O)OC)O)COC</t>
-  </si>
-  <si>
-    <t>mesaconine</t>
-  </si>
-  <si>
-    <t>(2R,3R,4R,5S,6S,7S,8R,13R,14R,16S,17S,18R)-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8,14-pentol</t>
-  </si>
-  <si>
-    <t>485.6</t>
-  </si>
-  <si>
-    <t>168008621</t>
-  </si>
-  <si>
-    <t>CN1C[C@@]2([C@@H](C[C@@H](C34[C@@H]2[C@H](C(C31)[C@@]5([C@@H]6[C@H]4C[C@]([C@@H]6O)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
-  </si>
-  <si>
-    <t>chasmanine</t>
-  </si>
-  <si>
-    <t>(1S,2R,3R,4S,5S,6S,8R,9R,13S,16S,17R,18R)-11-ethyl-6,16,18-trimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8-diol</t>
-  </si>
-  <si>
-    <t>451.6</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)OC)COC</t>
-  </si>
-  <si>
-    <t>aconine</t>
-  </si>
-  <si>
-    <t>(1S,2R,3R,4R,5R,6S,7S,8R,9R,13R,14R,16S,17S,18R)-11-ethyl-6,16,18-trimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8,14-pentol</t>
-  </si>
-  <si>
-    <t>499.6</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6O)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
-  </si>
-  <si>
-    <t>14-acetyltalatizamine</t>
-  </si>
-  <si>
-    <t>[(1S,2R,3R,4S,5R,6S,8S,9S,10R,13S,16S,17R)-11-ethyl-8-hydroxy-6,16-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] acetate</t>
-  </si>
-  <si>
-    <t>463.6</t>
-  </si>
-  <si>
-    <t>101622120</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H]([C@H]31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6OC(=O)C)OC)O)OC)COC</t>
-  </si>
-  <si>
-    <t>[(1S,2R,3R,4R,5R,6S,7S,8R,9R,13R,14R,16S,17S,18R)-5,7,8,14-tetrahydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
-  </si>
-  <si>
-    <t>589.7</t>
-  </si>
-  <si>
-    <t>CN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
-  </si>
-  <si>
-    <t>[(2R,3R,4R,5R,6S,7S,8R,13S,16S,17R,18R)-5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
-  </si>
-  <si>
-    <t>573.7</t>
-  </si>
-  <si>
-    <t>CN1C[C@@]2(CC[C@@H](C34[C@@H]2[C@H](C(C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)OC)OC)COC</t>
-  </si>
-  <si>
-    <t>[(1S,2R,3R,4R,5R,6S,7S,8R,9R,13R,14R,16S,17S,18R)-11-ethyl-5,7,8,14-tetrahydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
-  </si>
-  <si>
-    <t>603.7</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
-  </si>
-  <si>
-    <t>[(1R,2S,3S,4R,5R,6S,7S,8S,9R,13R,14R,16S,17R,18R)-11-ethyl-2,5,7,8,14-pentahydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
-  </si>
-  <si>
-    <t>C32H45NO11</t>
-  </si>
-  <si>
-    <t>619.7</t>
-  </si>
-  <si>
-    <t>177827777</t>
-  </si>
-  <si>
-    <t>CCN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@]4(C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)O)OC)OC)O)COC</t>
-  </si>
-  <si>
-    <t>(E)-3-(4-hydroxy-3-methoxyphenyl)prop-2-enoic acid</t>
-  </si>
-  <si>
-    <t>194.18</t>
-  </si>
-  <si>
-    <t>COC1=C(C=CC(=C1)/C=C/C(=O)O)O</t>
-  </si>
-  <si>
-    <t>(E)-3-(3-hydroxy-4-methoxyphenyl)prop-2-enoic acid</t>
-  </si>
-  <si>
-    <t>COC1=C(C=C(C=C1)/C=C/C(=O)O)O</t>
-  </si>
-  <si>
-    <t>7-hydroxy-3-(4-hydroxyphenyl)chromen-4-one</t>
-  </si>
-  <si>
-    <t>254.24</t>
-  </si>
-  <si>
-    <t>C1=CC(=CC=C1C2=COC3=C(C2=O)C=CC(=C3)O)O</t>
-  </si>
-  <si>
-    <t>7-hydroxy-3-(4-methoxyphenyl)chromen-4-one</t>
-  </si>
-  <si>
-    <t>268.26</t>
-  </si>
-  <si>
-    <t>COC1=CC=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O</t>
-  </si>
-  <si>
-    <t>7-hydroxy-3-(3-hydroxy-4-methoxyphenyl)chromen-4-one</t>
-  </si>
-  <si>
-    <t>284.26</t>
-  </si>
-  <si>
-    <t>COC1=C(C=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O)O</t>
-  </si>
-  <si>
-    <t>5,7-dihydroxy-8-methoxy-2-phenylchromen-4-one</t>
-  </si>
-  <si>
-    <t>COC1=C(C=C(C2=C1OC(=CC2=O)C3=CC=CC=C3)O)O</t>
-  </si>
-  <si>
-    <t>3-(2-hydroxy-3,4-dimethoxyphenyl)-3,4-dihydro-2H-chromen-7-ol</t>
-  </si>
-  <si>
-    <t>302.32</t>
-  </si>
-  <si>
-    <t>COC1=C(C(=C(C=C1)C2CC3=C(C=C(C=C3)O)OC2)O)OC</t>
-  </si>
-  <si>
-    <t>(2R,3S,4S,5R,6S)-2-(hydroxymethyl)-6-[4-[(E)-3-hydroxyprop-1-enyl]-2,6-dimethoxyphenoxy]oxane-3,4,5-triol</t>
-  </si>
-  <si>
-    <t>372.4</t>
-  </si>
-  <si>
-    <t>COC1=CC(=CC(=C1O[C@H]2[C@@H]([C@H]([C@@H]([C@H](O2)CO)O)O)O)OC)/C=C/CO</t>
-  </si>
-  <si>
-    <t>(2S,3S,4S,5R,6S)-3,4,5-trihydroxy-6-[3-(4-hydroxyphenyl)-4-oxochromen-7-yl]oxyoxane-2-carboxylic acid</t>
-  </si>
-  <si>
-    <t>430.4</t>
-  </si>
-  <si>
-    <t>C1=CC(=CC=C1C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)C(=O)O)O)O)O)O</t>
-  </si>
-  <si>
-    <t>5-hydroxy-2-(4-hydroxyphenyl)-7-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxychromen-4-one</t>
-  </si>
-  <si>
-    <t>432.4</t>
-  </si>
-  <si>
-    <t>C1=CC(=CC=C1C2=CC(=O)C3=C(C=C(C=C3O2)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)CO)O)O)O)O)O</t>
-  </si>
-  <si>
-    <t>(2S,3S,4S,5R,6S)-3,4,5-trihydroxy-6-[3-(4-methoxyphenyl)-4-oxochromen-7-yl]oxyoxane-2-carboxylic acid</t>
-  </si>
-  <si>
-    <t>444.4</t>
-  </si>
-  <si>
-    <t>COC1=CC=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)C(=O)O)O)O)O</t>
-  </si>
-  <si>
-    <t>3-(3-hydroxy-4-methoxyphenyl)-7-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxychromen-4-one</t>
-  </si>
-  <si>
-    <t>446.4</t>
-  </si>
-  <si>
-    <t>COC1=C(C=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)CO)O)O)O)O</t>
-  </si>
-  <si>
-    <t>3-(4-methoxyphenyl)-7-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxychromen-4-one</t>
-  </si>
-  <si>
-    <t>COC1=CC=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)CO)O)O)O</t>
-  </si>
-  <si>
-    <t>(2S,3R,4S,5S,6R)-2-[(9,10-dimethoxy-6a,11a-dihydro-6H-[1]benzofuro[3,2-c]chromen-3-yl)oxy]-6-(hydroxymethyl)oxane-3,4,5-triol</t>
-  </si>
-  <si>
-    <t>462.4</t>
-  </si>
-  <si>
-    <t>COC1=C(C2=C(C=C1)C3COC4=C(C3O2)C=CC(=C4)O[C@H]5[C@@H]([C@H]([C@@H]([C@H](O5)CO)O)O)O)OC</t>
-  </si>
-  <si>
-    <t>(2S,3R,4S,5S,6R)-2-[[3-(2-hydroxy-3,4-dimethoxyphenyl)-3,4-dihydro-2H-chromen-7-yl]oxy]-6-(hydroxymethyl)oxane-3,4,5-triol</t>
-  </si>
-  <si>
-    <t>464.5</t>
-  </si>
-  <si>
-    <t>COC1=C(C(=C(C=C1)C2CC3=C(C=C(C=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)CO)O)O)O)OC2)O)OC</t>
-  </si>
-  <si>
-    <t>[(2R,3S,4S,5R,6S)-3,4,5-trihydroxy-6-[3-(4-methoxyphenyl)-4-oxochromen-7-yl]oxyoxan-2-yl]methyl acetate</t>
-  </si>
-  <si>
-    <t>472.4</t>
-  </si>
-  <si>
-    <t>CC(=O)OC[C@@H]1[C@H]([C@@H]([C@H]([C@@H](O1)OC2=CC3=C(C=C2)C(=O)C(=CO3)C4=CC=C(C=C4)OC)O)O)O</t>
-  </si>
-  <si>
-    <t>cycloastragenol</t>
-  </si>
-  <si>
-    <t>(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethylpentacyclo[9.7.0.01,3.03,8.012,16]octadecane-6,9,14-triol</t>
-  </si>
-  <si>
-    <t>C30H50O5</t>
-  </si>
-  <si>
-    <t>490.7</t>
-  </si>
-  <si>
-    <t>13943286</t>
-  </si>
-  <si>
-    <t>C[C@]12CC[C@@]34C[C@@]35CC[C@@H](C([C@@H]5[C@H](C[C@H]4[C@@]1(C[C@@H]([C@@H]2[C@]6(CC[C@H](O6)C(C)(C)O)C)O)C)O)(C)C)O</t>
-  </si>
-  <si>
-    <t>(2S,3R,4S,5S,6R)-2-[(2S,3R,4S,5R)-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-9,14-dihydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]-4,5-dihydroxyoxan-3-yl]oxy-6-(hydroxymethyl)oxane-3,4,5-triol</t>
-  </si>
-  <si>
-    <t>785.0</t>
-  </si>
-  <si>
-    <t>C[C@]12CC[C@@]34C[C@@]35CC[C@@H](C([C@@H]5[C@H](C[C@H]4[C@@]1(C[C@@H]([C@@H]2[C@]6(CC[C@H](O6)C(C)(C)O)C)O)C)O)(C)C)O[C@H]7[C@@H]([C@H]([C@@H](CO7)O)O)O[C@H]8[C@@H]([C@H]([C@@H]([C@H](O8)CO)O)O)O</t>
-  </si>
-  <si>
-    <t>(2R,3R,4S,5S,6R)-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-6-[(2S,3R,4S,5R)-3,4,5-trihydroxyoxan-2-yl]oxy-9-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]-6-(hydroxymethyl)oxane-3,4,5-triol</t>
-  </si>
-  <si>
-    <t>C[C@]12CC[C@@]34C[C@@]35CC[C@@H](C([C@@H]5[C@H](C[C@H]4[C@@]1(C[C@@H]([C@@H]2[C@]6(CC[C@H](O6)C(C)(C)O)C)O)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)(C)C)O[C@H]8[C@@H]([C@H]([C@@H](CO8)O)O)O</t>
-  </si>
-  <si>
-    <t>(2R,3R,4S,5S,6R)-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-15-[(2R,5S)-5,6-dihydroxy-6-methylheptan-2-yl]-14-hydroxy-7,7,12,16-tetramethyl-6-[(2S,3R,4S,5R)-3,4,5-trihydroxyoxan-2-yl]oxy-9-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]-6-(hydroxymethyl)oxane-3,4,5-triol</t>
-  </si>
-  <si>
-    <t>787.0</t>
-  </si>
-  <si>
-    <t>C[C@H](CC[C@@H](C(C)(C)O)O)[C@H]1[C@H](C[C@@]2([C@@]1(CC[C@]34[C@H]2C[C@@H]([C@@H]5[C@]3(C4)CC[C@@H](C5(C)C)O[C@H]6[C@@H]([C@H]([C@@H](CO6)O)O)O)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)C)O</t>
-  </si>
-  <si>
-    <t>[(2S,3R,4S,5R)-4,5-dihydroxy-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-9-[(2R,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]oxan-3-yl] acetate</t>
-  </si>
-  <si>
-    <t>827.0</t>
-  </si>
-  <si>
-    <t>CC(=O)O[C@@H]1[C@H]([C@@H](CO[C@H]1O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C)O)O</t>
-  </si>
-  <si>
-    <t>[(2S,3R,4S,5R)-3-acetyloxy-5-hydroxy-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-9-[(2R,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]oxan-4-yl] acetate</t>
-  </si>
-  <si>
-    <t>869.0</t>
-  </si>
-  <si>
-    <t>CC(=O)O[C@H]1[C@@H](CO[C@H]([C@@H]1OC(=O)C)O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C)O</t>
-  </si>
-  <si>
-    <t>[(3R,4S,5R,6S)-5-acetyloxy-4-hydroxy-6-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-9-[(2R,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]oxan-3-yl] acetate</t>
-  </si>
-  <si>
-    <t>CC(=O)O[C@@H]1CO[C@H]([C@@H]([C@H]1O)OC(=O)C)O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C</t>
-  </si>
-  <si>
-    <t>(2R,3S,4S,5R,6R)-2-(hydroxymethyl)-6-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-7,7,12,16-tetramethyl-15-[(2R,5S)-2-methyl-5-[2-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxypropan-2-yl]oxolan-2-yl]-6-[(2S,3R,4S,5R)-3,4,5-trihydroxyoxan-2-yl]oxy-9-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]oxane-3,4,5-triol</t>
-  </si>
-  <si>
-    <t>947.1</t>
-  </si>
-  <si>
-    <t>C[C@]12CC[C@@]34C[C@@]35CC[C@@H](C([C@@H]5[C@H](C[C@H]4[C@@]1(C[C@@H]([C@@H]2[C@]6(CC[C@H](O6)C(C)(C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)C)O[C@H]8[C@@H]([C@H]([C@@H]([C@H](O8)CO)O)O)O)(C)C)O[C@H]9[C@@H]([C@H]([C@@H](CO9)O)O)O</t>
-  </si>
-  <si>
-    <t>(2S,3R,4S,5S,6R)-2-[(2S,3R,4S,5R)-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-9,14-dihydroxy-7,7,12,16-tetramethyl-15-[(2R,5S)-2-methyl-5-[2-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxypropan-2-yl]oxolan-2-yl]-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]-4,5-dihydroxyoxan-3-yl]oxy-6-(hydroxymethyl)oxane-3,4,5-triol</t>
-  </si>
-  <si>
-    <t>C[C@]12CC[C@@]34C[C@@]35CC[C@@H](C([C@@H]5[C@H](C[C@H]4[C@@]1(C[C@@H]([C@@H]2[C@]6(CC[C@H](O6)C(C)(C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)C)O)(C)C)O[C@H]8[C@@H]([C@H]([C@@H](CO8)O)O)O[C@H]9[C@@H]([C@H]([C@@H]([C@H](O9)CO)O)O)O</t>
-  </si>
-  <si>
-    <t>(2S,3S,4S,5R,6R)-6-[[(3S,4S,4aR,6aR,6bS,8aR,9R,12aS,14aR,14bR)-9-hydroxy-4-(hydroxymethyl)-4,6a,6b,8a,11,11,14b-heptamethyl-1,2,3,4a,5,6,7,8,9,10,12,12a,14,14a-tetradecahydropicen-3-yl]oxy]-5-[(2S,3R,4S,5R,6R)-4,5-dihydroxy-6-(hydroxymethyl)-3-[(2S,3R,4R,5R,6S)-3,4,5-trihydroxy-6-methyloxan-2-yl]oxyoxan-2-yl]oxy-3,4-dihydroxyoxane-2-carboxylic acid</t>
-  </si>
-  <si>
-    <t>943.1</t>
-  </si>
-  <si>
-    <t>C[C@H]1[C@@H]([C@H]([C@H]([C@@H](O1)O[C@@H]2[C@H]([C@H]([C@H](O[C@H]2O[C@@H]3[C@H]([C@@H]([C@H](O[C@H]3O[C@H]4CC[C@]5([C@H]([C@@]4(C)CO)CC[C@@]6([C@@H]5CC=C7[C@]6(CC[C@@]8([C@H]7CC(C[C@H]8O)(C)C)C)C)C)C)C(=O)O)O)O)CO)O)O)O)O)O</t>
-  </si>
-  <si>
-    <t>protocatechuic acid</t>
-  </si>
-  <si>
-    <t>154.12</t>
-  </si>
-  <si>
-    <t>C1=CC(=C(C=C1C(=O)O)O)O</t>
-  </si>
-  <si>
-    <t>(E)-3-(3,4-dihydroxyphenyl)prop-2-enoic acid</t>
-  </si>
-  <si>
-    <t>180.16</t>
-  </si>
-  <si>
-    <t>C1=CC(=C(C=C1/C=C/C(=O)O)O)O</t>
-  </si>
-  <si>
-    <t>(4aS,8aS)-3,8a-dimethyl-5-methylidene-4a,6,7,8-tetrahydro-4H-benzo[f][1]benzofuran-2-one</t>
-  </si>
-  <si>
-    <t>230.30</t>
-  </si>
-  <si>
-    <t>CC1=C2C[C@H]3C(=C)CCC[C@@]3(C=C2OC1=O)C</t>
-  </si>
-  <si>
-    <t>(4aS,8aR,9aS)-3,8a-dimethyl-5-methylidene-4a,6,7,8,9,9a-hexahydro-4H-benzo[f][1]benzofuran-2-one</t>
-  </si>
-  <si>
-    <t>232.32</t>
-  </si>
-  <si>
-    <t>CC1=C2C[C@H]3C(=C)CCC[C@@]3(C[C@@H]2OC1=O)C</t>
-  </si>
-  <si>
-    <t>(4aS,8aR,9aS)-9a-hydroxy-3,8a-dimethyl-5-methylidene-4,4a,6,7,8,9-hexahydrobenzo[f][1]benzofuran-2-one</t>
-  </si>
-  <si>
-    <t>248.32</t>
-  </si>
-  <si>
-    <t>CC1=C2C[C@H]3C(=C)CCC[C@@]3(C[C@@]2(OC1=O)O)C</t>
-  </si>
-  <si>
-    <t>7-hydroxychromen-2-one</t>
-  </si>
-  <si>
-    <t>162.14</t>
-  </si>
-  <si>
-    <t>C1=CC(=CC2=C1C=CC(=O)O2)O</t>
-  </si>
-  <si>
-    <t>chlorogenic acid</t>
-  </si>
-  <si>
-    <t>(1S,3R,4R,5R)-3-[(E)-3-(3,4-dihydroxyphenyl)prop-2-enoyl]oxy-1,4,5-trihydroxycyclohexane-1-carboxylic acid</t>
-  </si>
-  <si>
-    <t>C16H18O9</t>
-  </si>
-  <si>
-    <t>354.31</t>
-  </si>
-  <si>
-    <t>1794427</t>
-  </si>
-  <si>
-    <t>C1[C@H]([C@H]([C@@H](C[C@@]1(C(=O)O)O)OC(=O)/C=C/C2=CC(=C(C=C2)O)O)O)O</t>
-  </si>
-  <si>
-    <t>vanillic acid</t>
-  </si>
-  <si>
-    <t>4-hydroxy-3-methoxybenzoic acid</t>
-  </si>
-  <si>
-    <t>C8H8O4</t>
-  </si>
-  <si>
-    <t>168.15</t>
-  </si>
-  <si>
-    <t>8468</t>
-  </si>
-  <si>
-    <t>COC1=C(C=CC(=C1)C(=O)O)O</t>
-  </si>
-  <si>
-    <t>2-[(3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid</t>
-  </si>
-  <si>
-    <t>468.7</t>
-  </si>
-  <si>
-    <t>CC(=CCCC([C@H]1CC[C@@]2([C@@]1(CC=C3C2=CC[C@H]([C@]3(C)CCC(=O)O)C(=C)C)C)C)C(=O)O)C</t>
-  </si>
-  <si>
-    <t>poricoic acid b</t>
-  </si>
-  <si>
-    <t>2-[(2R,3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid</t>
-  </si>
-  <si>
-    <t>484.7</t>
-  </si>
-  <si>
-    <t>CC(=CCCC([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@H]([C@]3(C)CCC(=O)O)C(=C)C)C)C)O)C(=O)O)C</t>
-  </si>
-  <si>
-    <t>(E,2R)-2-[(2R,3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-7-hydroxy-6-methylhept-5-enoic acid</t>
-  </si>
-  <si>
-    <t>500.7</t>
-  </si>
-  <si>
-    <t>CC(=C)[C@@H]1CC=C2C(=CC[C@]3([C@]2(C[C@H]([C@@H]3[C@@H](CC/C=C(\C)/CO)C(=O)O)O)C)C)[C@@]1(C)CCC(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3S,5R,10S,13R,14R,17R)-3-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methylhept-5-enoic acid</t>
-  </si>
-  <si>
-    <t>454.7</t>
-  </si>
-  <si>
-    <t>CC(=CCC[C@H]([C@H]1CC[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)O)C)C)C)C(=O)O)C</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(2R,3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,5,7,8,9-octahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid</t>
-  </si>
-  <si>
-    <t>486.7</t>
-  </si>
-  <si>
-    <t>CC(=CCC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@H]([C@]3(C)CCC(=O)O)C(=C)C)C)C)O)C(=O)O)C</t>
-  </si>
-  <si>
-    <t>poriacosone b</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid</t>
-  </si>
-  <si>
-    <t>CC(C)C(=O)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)O)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>poriacosone a</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3R,5R,10S,13R,14R,16R,17R)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid</t>
-  </si>
-  <si>
-    <t>CC(C)C(=O)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@H](C4(C)C)O)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3S,5R,10S,13R,14R,17R)-3-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methylhept-5-enoic acid</t>
-  </si>
-  <si>
-    <t>456.7</t>
-  </si>
-  <si>
-    <t>CC(=CCC[C@H]([C@H]1CC[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)O)C)C)C)C(=O)O)C</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3R,5R,10S,13R,14R,16R,17R)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid</t>
-  </si>
-  <si>
-    <t>488.7</t>
-  </si>
-  <si>
-    <t>CC(C)C(=O)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@H](C4(C)C)O)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(5R,10S,13R,14R,16R,17R)-16-hydroxy-4,4,10,13,14-pentamethyl-3-oxo-1,2,5,6,12,15,16,17-octahydrocyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>482.7</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CCC(=O)C4(C)C)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(2R,3R,3aR,9bR)-2-hydroxy-3a,7,9b-trimethyl-6-(4-methyl-3-oxopentyl)-2,3,4,5-tetrahydro-1H-cyclopenta[a]naphthalen-3-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>CC1=C(C2=C(C=C1)[C@@]3(C[C@H]([C@@H]([C@]3(CC2)C)[C@@H](CCC(=C)C(C)C)C(=O)O)O)C)CCC(=O)C(C)C</t>
-  </si>
-  <si>
-    <t>2-[(3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-hydroxy-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>498.7</t>
-  </si>
-  <si>
-    <t>CC(=C)[C@@H]1CC=C2C(=CC[C@]3([C@]2(CC[C@@H]3C(CCC(=C)C(C)(C)O)C(=O)O)C)C)[C@@]1(C)CCC(=O)O</t>
-  </si>
-  <si>
-    <t>2-[(2R,3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,5,7-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CCC([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2C=C[C@H]([C@]3(C)CCC(=O)O)C(=C)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(2R,3R,3aR,6S,7R,9bR)-6-(2-carboxyethyl)-2-hydroxy-7-(3-hydroxyprop-1-en-2-yl)-3a,6,9b-trimethyl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>514.7</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@H]([C@]3(C)CCC(=O)O)C(=C)CO)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-6-methyl-5-methylidene-2-[(5R,10S,13R,14R,17R)-4,4,10,13,14-pentamethyl-3-oxo-1,2,5,6,7,11,12,15,16,17-decahydrocyclopenta[a]phenanthren-17-yl]heptanoic acid</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1CC[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CCC(=O)C4(C)C)C)C)C)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3R,5R,10S,13R,14R,16R,17R)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@H](C4(C)C)O)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)O)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(2R,3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,5,7,8,9-octahydrocyclopenta[a]naphthalen-3-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@H]([C@]3(C)CCC(=O)O)C(=C)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>2-[(2R,3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,5,7,8,9-octahydrocyclopenta[a]naphthalen-3-yl]-6-hydroxy-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>516.7</t>
-  </si>
-  <si>
-    <t>CC(=C)[C@@H]1CCC2=C([C@@]1(C)CCC(=O)O)CC[C@]3([C@]2(C[C@H]([C@@H]3C(CCC(=C)C(C)(C)O)C(=O)O)O)C)C</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3S,5R,10S,13R,14R,17R)-3-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>470.7</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1CC[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)O)C)C)C)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)O)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(2R,3R,3aR,6S,7S,9bR)-2-hydroxy-6-(3-methoxy-3-oxopropyl)-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>512.7</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@H]([C@]3(C)CCC(=O)OC)C(=C)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methylhept-5-enoic acid</t>
-  </si>
-  <si>
-    <t>CC(=CCC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)OC(=O)C)C)C)C)O)C(=O)O)C</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3R,3aR,6S,7S,9bR)-6-(3-ethoxy-3-oxopropyl)-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>510.7</t>
-  </si>
-  <si>
-    <t>CCOC(=O)CC[C@]1([C@@H](CC=C2C1=CC[C@]3([C@]2(CC[C@@H]3[C@@H](CCC(=C)C(C)C)C(=O)O)C)C)C(=C)C)C</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3R,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>526.7</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@H](C4(C)C)OC(=O)C)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)OC(=O)C)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3S,4S,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4-(hydroxymethyl)-4,10,13,14-tetramethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>542.7</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@@H]([C@]4(C)CO)OC(=O)C)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>528.8</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)OC(=O)C)C)C)C)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-hydroxy-6-methyl-5-methylideneheptanoic acid</t>
-  </si>
-  <si>
-    <t>544.8</t>
-  </si>
-  <si>
-    <t>177826656</t>
-  </si>
-  <si>
-    <t>CC(=O)O[C@H]1CC[C@]2([C@H](C1(C)C)CCC3=C2CC[C@]4([C@]3(C[C@H]([C@@H]4[C@@H](CCC(=C)C(C)(C)O)C(=O)O)O)C)C)C</t>
-  </si>
-  <si>
-    <t>pachymic acid methyl ester</t>
-  </si>
-  <si>
-    <t>methyl (2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoate</t>
-  </si>
-  <si>
-    <t>542.8</t>
-  </si>
-  <si>
-    <t>CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)OC(=O)C)C)C)C)O)C(=O)OC</t>
-  </si>
-  <si>
-    <t>(E)-3-(3-methoxy-4-sulfooxyphenyl)prop-2-enoic acid</t>
-  </si>
-  <si>
-    <t>274.25</t>
-  </si>
-  <si>
-    <t>COC1=C(C=CC(=C1)/C=C/C(=O)O)OS(=O)(=O)O</t>
-  </si>
-  <si>
-    <t>(2S)-5,7-dihydroxy-2-(4-hydroxyphenyl)-2,3-dihydrochromen-4-one</t>
-  </si>
-  <si>
-    <t>272.25</t>
-  </si>
-  <si>
-    <t>C1[C@H](OC2=CC(=CC(=C2C1=O)O)O)C3=CC=C(C=C3)O</t>
-  </si>
-  <si>
-    <t>(2R,3R)-2-(3,4-dihydroxyphenyl)-3,4-dihydro-2H-chromene-3,5,7-triol</t>
-  </si>
-  <si>
-    <t>290.27</t>
-  </si>
-  <si>
-    <t>C1[C@H]([C@H](OC2=CC(=CC(=C21)O)O)C3=CC(=C(C=C3)O)O)O</t>
-  </si>
-  <si>
-    <t>catechin</t>
-  </si>
-  <si>
-    <t>(2R,3S)-2-(3,4-dihydroxyphenyl)-3,4-dihydro-2H-chromene-3,5,7-triol</t>
-  </si>
-  <si>
-    <t>C1[C@@H]([C@H](OC2=CC(=CC(=C21)O)O)C3=CC(=C(C=C3)O)O)O</t>
-  </si>
-  <si>
-    <t>8-dephenyl paeoniflorin</t>
-  </si>
-  <si>
-    <t>(2S,3R,4S,5S,6R)-2-[[(1R,2S,3R,5R,6R,8S)-6-hydroxy-2-(hydroxymethyl)-8-methyl-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-3-yl]oxy]-6-(hydroxymethyl)oxane-3,4,5-triol</t>
-  </si>
-  <si>
-    <t>376.36</t>
-  </si>
-  <si>
-    <t>71452333</t>
-  </si>
-  <si>
-    <t>C[C@]12C[C@@]3([C@@H]4C[C@]1([C@@]4([C@H](O2)O3)CO)O[C@H]5[C@@H]([C@H]([C@@H]([C@H](O5)CO)O)O)O)O</t>
-  </si>
-  <si>
-    <t>albiflorin</t>
-  </si>
-  <si>
-    <t>[(1R,2S,3R,5R,6S,8S)-6-hydroxy-8-methyl-3-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-2-yl]methyl benzoate</t>
-  </si>
-  <si>
-    <t>480.5</t>
-  </si>
-  <si>
-    <t>C[C@]12C[C@]3([C@@H]4C[C@]1([C@@]4([C@H](O2)O3)COC(=O)C5=CC=CC=C5)O[C@H]6[C@@H]([C@H]([C@@H]([C@H](O6)CO)O)O)O)O</t>
-  </si>
-  <si>
-    <t>[(1R,4R)-4-hydroxy-6-methyl-8-oxo-1-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-7-oxatricyclo[4.3.0.03,9]nonan-9-yl]methyl benzoate</t>
-  </si>
-  <si>
-    <t>CC12C[C@H](C3C[C@]1(C3(C(=O)O2)COC(=O)C4=CC=CC=C4)O[C@H]5[C@@H]([C@H]([C@@H]([C@H](O5)CO)O)O)O)O</t>
-  </si>
-  <si>
-    <t>oxypaeoniflorin</t>
-  </si>
-  <si>
-    <t>[(1R,2S,3R,5R,6R,8S)-6-hydroxy-8-methyl-3-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-2-yl]methyl 4-hydroxybenzoate</t>
-  </si>
-  <si>
-    <t>496.5</t>
-  </si>
-  <si>
-    <t>C[C@]12C[C@@]3([C@@H]4C[C@]1([C@@]4([C@H](O2)O3)COC(=O)C5=CC=C(C=C5)O)O[C@H]6[C@@H]([C@H]([C@@H]([C@H](O6)CO)O)O)O)O</t>
-  </si>
-  <si>
-    <t>[(2R,3S,4S,5R,6S)-6-[[(1R,2S,3R,5R,6R,8S)-2-(benzoyloxymethyl)-6-hydroxy-8-methyl-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-3-yl]oxy]-3,4,5-trihydroxyoxan-2-yl]methyl benzoate</t>
-  </si>
-  <si>
-    <t>584.6</t>
-  </si>
-  <si>
-    <t>C[C@]12C[C@@]3([C@@H]4C[C@]1([C@@]4([C@H](O2)O3)COC(=O)C5=CC=CC=C5)O[C@H]6[C@@H]([C@H]([C@@H]([C@H](O6)COC(=O)C7=CC=CC=C7)O)O)O)O</t>
-  </si>
-  <si>
-    <t>[(2R,3S,4S,5R,6S)-6-[[(1R,2S,3R,5R,6S,8S)-2-(benzoyloxymethyl)-6-hydroxy-8-methyl-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-3-yl]oxy]-3,4,5-trihydroxyoxan-2-yl]methyl benzoate</t>
-  </si>
-  <si>
-    <t>177827917</t>
-  </si>
-  <si>
-    <t>C[C@]12C[C@]3([C@@H]4C[C@]1([C@@]4([C@H](O2)O3)COC(=O)C5=CC=CC=C5)O[C@H]6[C@@H]([C@H]([C@@H]([C@H](O6)COC(=O)C7=CC=CC=C7)O)O)O)O</t>
-  </si>
-  <si>
-    <t>6'-O-galloyl paeoniflorin</t>
-  </si>
-  <si>
-    <t>[(2R,3S,4S,5R,6S)-6-[[(2S,3R,5R,6R,8S)-2-(benzoyloxymethyl)-6-hydroxy-8-methyl-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-3-yl]oxy]-3,4,5-trihydroxyoxan-2-yl]methyl 3,4,5-trihydroxybenzoate</t>
-  </si>
-  <si>
-    <t>632.6</t>
-  </si>
-  <si>
-    <t>122169317</t>
-  </si>
-  <si>
-    <t>C[C@]12C[C@@]3([C@@H]4C[C@]1([C@@]4(C(O2)O3)COC(=O)C5=CC=CC=C5)O[C@H]6[C@@H]([C@H]([C@@H]([C@H](O6)COC(=O)C7=CC(=C(C(=C7)O)O)O)O)O)O)O</t>
-  </si>
-  <si>
-    <t>galloylalbiflorin</t>
-  </si>
-  <si>
-    <t>[(2R,3S,4S,5R,6S)-6-[[(1R,3R,4R,6S,9S)-9-(benzoyloxymethyl)-4-hydroxy-6-methyl-8-oxo-7-oxatricyclo[4.3.0.03,9]nonan-1-yl]oxy]-3,4,5-trihydroxyoxan-2-yl]methyl 3,4,5-trihydroxybenzoate</t>
-  </si>
-  <si>
-    <t>124079396</t>
-  </si>
-  <si>
-    <t>C[C@]12C[C@H]([C@@H]3C[C@]1([C@@]3(C(=O)O2)COC(=O)C4=CC=CC=C4)O[C@H]5[C@@H]([C@H]([C@@H]([C@H](O5)COC(=O)C6=CC(=C(C(=C6)O)O)O)O)O)O)O</t>
-  </si>
-  <si>
-    <t>[(2R,3R,4S,5R,6S)-3,4,5,6-tetrakis[(3,4,5-trihydroxybenzoyl)oxy]oxan-2-yl]methyl 3,4,5-trihydroxybenzoate</t>
-  </si>
-  <si>
-    <t>940.7</t>
-  </si>
-  <si>
-    <t>C1=C(C=C(C(=C1O)O)O)C(=O)OC[C@@H]2[C@H]([C@@H]([C@H]([C@@H](O2)OC(=O)C3=CC(=C(C(=C3)O)O)O)OC(=O)C4=CC(=C(C(=C4)O)O)O)OC(=O)C5=CC(=C(C(=C5)O)O)O)OC(=O)C6=CC(=C(C(=C6)O)O)O</t>
-  </si>
-  <si>
-    <t>3,4,5-trihydroxybenzoic acid</t>
-  </si>
-  <si>
-    <t>170.12</t>
-  </si>
-  <si>
-    <t>C1=C(C=C(C(=C1O)O)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>6-Shogaol</t>
-  </si>
-  <si>
-    <t>(E)-1-(4-hydroxy-3-methoxyphenyl)dec-4-en-3-one</t>
-  </si>
-  <si>
-    <t>276.4</t>
-  </si>
-  <si>
-    <t>CCCCC/C=C/C(=O)CCC1=CC(=C(C=C1)O)OC</t>
-  </si>
-  <si>
-    <t>(–)-[6]-Gingerol</t>
-  </si>
-  <si>
-    <t>(5S)-5-hydroxy-1-(4-hydroxy-3-methoxyphenyl)decan-3-one</t>
-  </si>
-  <si>
-    <t>294.4</t>
-  </si>
-  <si>
-    <t>CCCCC[C@@H](CC(=O)CCC1=CC(=C(C=C1)O)OC)O</t>
-  </si>
-  <si>
-    <t>(–)-[8]-Gingerol</t>
-  </si>
-  <si>
-    <t>(5S)-5-hydroxy-1-(4-hydroxy-3-methoxyphenyl)dodecan-3-one</t>
-  </si>
-  <si>
-    <t>322.4</t>
-  </si>
-  <si>
-    <t>CCCCCCC[C@@H](CC(=O)CCC1=CC(=C(C=C1)O)OC)O</t>
-  </si>
-  <si>
-    <t>(–)-[10]-Gingerol</t>
-  </si>
-  <si>
-    <t>(5S)-5-hydroxy-1-(4-hydroxy-3-methoxyphenyl)tetradecan-3-one</t>
-  </si>
-  <si>
-    <t>C21H34O4</t>
-  </si>
-  <si>
-    <t>350.5</t>
-  </si>
-  <si>
-    <t>168115</t>
-  </si>
-  <si>
-    <t>CCCCCCCCC[C@@H](CC(=O)CCC1=CC(=C(C=C1)O)OC)O</t>
-  </si>
-  <si>
-    <t>zingerone</t>
-  </si>
-  <si>
-    <t>4-(4-hydroxy-3-methoxyphenyl)butan-2-one</t>
-  </si>
-  <si>
-    <t>C11H14O3</t>
-  </si>
-  <si>
-    <t>194.23</t>
-  </si>
-  <si>
-    <t>31211</t>
-  </si>
-  <si>
-    <t>CC(=O)CCC1=CC(=C(C=C1)O)OC</t>
+    <t xml:space="preserve">Herb(Pinyin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herb(Latin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herb(English)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compound Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compound Name (IUPAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molecular Formula (g/mol)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MolecularWeight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pubchme CID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMILES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(R)-(+)-higenamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1R)-1-[(4-hydroxyphenyl)methyl]-1,2,3,4-tetrahydroisoquinoline-6,7-diol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16H17NO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1CN[C@@H](C2=CC(=C(C=C21)O)O)CC3=CC=C(C=C3)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(S)-(-)-Higenamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S)-1-[(4-hydroxyphenyl)methyl]-1,2,3,4-tetrahydroisoquinoline-6,7-diol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1CN[C@H](C2=CC(=C(C=C21)O)O)CC3=CC=C(C=C3)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1R,2R,5R,7R,8R,9R,10R,13R,16S,17R)-11-ethyl-7,16-dihydroxy-13-methyl-6-methylidene-11-azahexacyclo[7.7.2.15,8.01,10.02,8.013,17]nonadecan-4-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H]([C@H]31)[C@]56[C@H]4CC(=O)[C@H](C5)C(=C)[C@H]6O)O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">karakoline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8S,9S,13R,16S,17R)-11-ethyl-6-methoxy-13-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8,16-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isotalatizidine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8S,9S,13S,16S,17R)-11-ethyl-6-methoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8,16-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16401028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8S,9S,13S,16S,17R)-11-ethyl-13-(hydroxymethyl)-6,16-dimethoxy-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8-diol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)CO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8R,9R,13S,16S,17R,18R)-11-ethyl-6-methoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8,16,18-tetrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20056299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)O)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1R,2S,3S,4S,5S,6R,7S,8R,9S,10R,13S,16S,17R)-11-ethyl-6-methoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-3,4,7,8,16-pentol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H37NO7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">439.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101465272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H]([C@H]31)[C@]5([C@H]([C@@H]([C@H]6C[C@@H]4[C@@]5([C@H]6O)O)OC)O)O)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8S,9S,13S,16S,17R)-11-ethyl-6,16-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8-diol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">441761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1R,2S,3S,4S,5S,6S,8S,9S,13S,16S,17R)-11-ethyl-6,16-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-3,4,8-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">437.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177827733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@]5([C@H]6O)O)OC)O)OC)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1R,2S,3R,4S,5S,6S,8S,9S,10R,13S,16S,17R)-11-ethyl-6,16-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-2,4,8-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H]([C@H]31)[C@]5(C[C@@H]([C@H]6C[C@@]4([C@@H]5[C@H]6O)O)OC)O)OC)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8R,9R,13S,16S,17R,18R)-11-ethyl-6,18-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8,16-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10003218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6R,7S,8R,10R,13S,16S,17R)-11-ethyl-6,18-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,7,8,16-tetrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">453.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122362201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C(C([C@H]31)[C@@]5([C@@H]6[C@H]4C[C@@H]([C@@H]6O)[C@H]([C@@H]5O)OC)O)OC)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mesaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R,3R,4R,5S,6S,7S,8R,13R,14R,16S,17S,18R)-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8,14-pentol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">485.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168008621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN1C[C@@]2([C@@H](C[C@@H](C34[C@@H]2[C@H](C(C31)[C@@]5([C@@H]6[C@H]4C[C@]([C@@H]6O)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chasmanine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8R,9R,13S,16S,17R,18R)-11-ethyl-6,16,18-trimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8-diol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">451.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)OC)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4R,5R,6S,7S,8R,9R,13R,14R,16S,17S,18R)-11-ethyl-6,16,18-trimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8,14-pentol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6O)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-acetyltalatizamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1S,2R,3R,4S,5R,6S,8S,9S,10R,13S,16S,17R)-11-ethyl-8-hydroxy-6,16-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">463.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101622120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H]([C@H]31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6OC(=O)C)OC)O)OC)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1S,2R,3R,4R,5R,6S,7S,8R,9R,13R,14R,16S,17S,18R)-5,7,8,14-tetrahydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">589.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(2R,3R,4R,5R,6S,7S,8R,13S,16S,17R,18R)-5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">573.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN1C[C@@]2(CC[C@@H](C34[C@@H]2[C@H](C(C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)OC)OC)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1S,2R,3R,4R,5R,6S,7S,8R,9R,13R,14R,16S,17S,18R)-11-ethyl-5,7,8,14-tetrahydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">603.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1R,2S,3S,4R,5R,6S,7S,8S,9R,13R,14R,16S,17R,18R)-11-ethyl-2,5,7,8,14-pentahydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C32H45NO11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">619.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177827777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@]4(C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)O)OC)OC)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(E)-3-(4-hydroxy-3-methoxyphenyl)prop-2-enoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=C(C=CC(=C1)/C=C/C(=O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(E)-3-(3-hydroxy-4-methoxyphenyl)prop-2-enoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=C(C=C(C=C1)/C=C/C(=O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-hydroxy-3-(4-hydroxyphenyl)chromen-4-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">254.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1=CC(=CC=C1C2=COC3=C(C2=O)C=CC(=C3)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-hydroxy-3-(4-methoxyphenyl)chromen-4-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=CC=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-hydroxy-3-(3-hydroxy-4-methoxyphenyl)chromen-4-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">284.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=C(C=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,7-dihydroxy-8-methoxy-2-phenylchromen-4-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=C(C=C(C2=C1OC(=CC2=O)C3=CC=CC=C3)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-(2-hydroxy-3,4-dimethoxyphenyl)-3,4-dihydro-2H-chromen-7-ol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=C(C(=C(C=C1)C2CC3=C(C=C(C=C3)O)OC2)O)OC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R,3S,4S,5R,6S)-2-(hydroxymethyl)-6-[4-[(E)-3-hydroxyprop-1-enyl]-2,6-dimethoxyphenoxy]oxane-3,4,5-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">372.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=CC(=CC(=C1O[C@H]2[C@@H]([C@H]([C@@H]([C@H](O2)CO)O)O)O)OC)/C=C/CO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2S,3S,4S,5R,6S)-3,4,5-trihydroxy-6-[3-(4-hydroxyphenyl)-4-oxochromen-7-yl]oxyoxane-2-carboxylic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">430.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1=CC(=CC=C1C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)C(=O)O)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-hydroxy-2-(4-hydroxyphenyl)-7-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxychromen-4-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">432.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1=CC(=CC=C1C2=CC(=O)C3=C(C=C(C=C3O2)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)CO)O)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2S,3S,4S,5R,6S)-3,4,5-trihydroxy-6-[3-(4-methoxyphenyl)-4-oxochromen-7-yl]oxyoxane-2-carboxylic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">444.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=CC=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)C(=O)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-(3-hydroxy-4-methoxyphenyl)-7-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxychromen-4-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">446.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=C(C=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)CO)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-(4-methoxyphenyl)-7-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxychromen-4-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=CC=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)CO)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2S,3R,4S,5S,6R)-2-[(9,10-dimethoxy-6a,11a-dihydro-6H-[1]benzofuro[3,2-c]chromen-3-yl)oxy]-6-(hydroxymethyl)oxane-3,4,5-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">462.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=C(C2=C(C=C1)C3COC4=C(C3O2)C=CC(=C4)O[C@H]5[C@@H]([C@H]([C@@H]([C@H](O5)CO)O)O)O)OC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2S,3R,4S,5S,6R)-2-[[3-(2-hydroxy-3,4-dimethoxyphenyl)-3,4-dihydro-2H-chromen-7-yl]oxy]-6-(hydroxymethyl)oxane-3,4,5-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">464.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=C(C(=C(C=C1)C2CC3=C(C=C(C=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)CO)O)O)O)OC2)O)OC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(2R,3S,4S,5R,6S)-3,4,5-trihydroxy-6-[3-(4-methoxyphenyl)-4-oxochromen-7-yl]oxyoxan-2-yl]methyl acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">472.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=O)OC[C@@H]1[C@H]([C@@H]([C@H]([C@@H](O1)OC2=CC3=C(C=C2)C(=O)C(=CO3)C4=CC=C(C=C4)OC)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cycloastragenol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethylpentacyclo[9.7.0.01,3.03,8.012,16]octadecane-6,9,14-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H50O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">490.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13943286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@]12CC[C@@]34C[C@@]35CC[C@@H](C([C@@H]5[C@H](C[C@H]4[C@@]1(C[C@@H]([C@@H]2[C@]6(CC[C@H](O6)C(C)(C)O)C)O)C)O)(C)C)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2S,3R,4S,5S,6R)-2-[(2S,3R,4S,5R)-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-9,14-dihydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]-4,5-dihydroxyoxan-3-yl]oxy-6-(hydroxymethyl)oxane-3,4,5-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">785.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@]12CC[C@@]34C[C@@]35CC[C@@H](C([C@@H]5[C@H](C[C@H]4[C@@]1(C[C@@H]([C@@H]2[C@]6(CC[C@H](O6)C(C)(C)O)C)O)C)O)(C)C)O[C@H]7[C@@H]([C@H]([C@@H](CO7)O)O)O[C@H]8[C@@H]([C@H]([C@@H]([C@H](O8)CO)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R,3R,4S,5S,6R)-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-6-[(2S,3R,4S,5R)-3,4,5-trihydroxyoxan-2-yl]oxy-9-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]-6-(hydroxymethyl)oxane-3,4,5-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@]12CC[C@@]34C[C@@]35CC[C@@H](C([C@@H]5[C@H](C[C@H]4[C@@]1(C[C@@H]([C@@H]2[C@]6(CC[C@H](O6)C(C)(C)O)C)O)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)(C)C)O[C@H]8[C@@H]([C@H]([C@@H](CO8)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R,3R,4S,5S,6R)-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-15-[(2R,5S)-5,6-dihydroxy-6-methylheptan-2-yl]-14-hydroxy-7,7,12,16-tetramethyl-6-[(2S,3R,4S,5R)-3,4,5-trihydroxyoxan-2-yl]oxy-9-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]-6-(hydroxymethyl)oxane-3,4,5-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">787.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@H](CC[C@@H](C(C)(C)O)O)[C@H]1[C@H](C[C@@]2([C@@]1(CC[C@]34[C@H]2C[C@@H]([C@@H]5[C@]3(C4)CC[C@@H](C5(C)C)O[C@H]6[C@@H]([C@H]([C@@H](CO6)O)O)O)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)C)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(2S,3R,4S,5R)-4,5-dihydroxy-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-9-[(2R,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]oxan-3-yl] acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">827.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=O)O[C@@H]1[C@H]([C@@H](CO[C@H]1O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(2S,3R,4S,5R)-3-acetyloxy-5-hydroxy-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-9-[(2R,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]oxan-4-yl] acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">869.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=O)O[C@H]1[C@@H](CO[C@H]([C@@H]1OC(=O)C)O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(3R,4S,5R,6S)-5-acetyloxy-4-hydroxy-6-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-9-[(2R,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]oxan-3-yl] acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=O)O[C@@H]1CO[C@H]([C@@H]([C@H]1O)OC(=O)C)O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R,3S,4S,5R,6R)-2-(hydroxymethyl)-6-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-7,7,12,16-tetramethyl-15-[(2R,5S)-2-methyl-5-[2-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxypropan-2-yl]oxolan-2-yl]-6-[(2S,3R,4S,5R)-3,4,5-trihydroxyoxan-2-yl]oxy-9-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]oxane-3,4,5-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">947.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@]12CC[C@@]34C[C@@]35CC[C@@H](C([C@@H]5[C@H](C[C@H]4[C@@]1(C[C@@H]([C@@H]2[C@]6(CC[C@H](O6)C(C)(C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)C)O[C@H]8[C@@H]([C@H]([C@@H]([C@H](O8)CO)O)O)O)(C)C)O[C@H]9[C@@H]([C@H]([C@@H](CO9)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2S,3R,4S,5S,6R)-2-[(2S,3R,4S,5R)-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-9,14-dihydroxy-7,7,12,16-tetramethyl-15-[(2R,5S)-2-methyl-5-[2-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxypropan-2-yl]oxolan-2-yl]-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]-4,5-dihydroxyoxan-3-yl]oxy-6-(hydroxymethyl)oxane-3,4,5-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@]12CC[C@@]34C[C@@]35CC[C@@H](C([C@@H]5[C@H](C[C@H]4[C@@]1(C[C@@H]([C@@H]2[C@]6(CC[C@H](O6)C(C)(C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)C)O)(C)C)O[C@H]8[C@@H]([C@H]([C@@H](CO8)O)O)O[C@H]9[C@@H]([C@H]([C@@H]([C@H](O9)CO)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2S,3S,4S,5R,6R)-6-[[(3S,4S,4aR,6aR,6bS,8aR,9R,12aS,14aR,14bR)-9-hydroxy-4-(hydroxymethyl)-4,6a,6b,8a,11,11,14b-heptamethyl-1,2,3,4a,5,6,7,8,9,10,12,12a,14,14a-tetradecahydropicen-3-yl]oxy]-5-[(2S,3R,4S,5R,6R)-4,5-dihydroxy-6-(hydroxymethyl)-3-[(2S,3R,4R,5R,6S)-3,4,5-trihydroxy-6-methyloxan-2-yl]oxyoxan-2-yl]oxy-3,4-dihydroxyoxane-2-carboxylic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@H]1[C@@H]([C@H]([C@H]([C@@H](O1)O[C@@H]2[C@H]([C@H]([C@H](O[C@H]2O[C@@H]3[C@H]([C@@H]([C@H](O[C@H]3O[C@H]4CC[C@]5([C@H]([C@@]4(C)CO)CC[C@@]6([C@@H]5CC=C7[C@]6(CC[C@@]8([C@H]7CC(C[C@H]8O)(C)C)C)C)C)C)C(=O)O)O)O)CO)O)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protocatechuic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1=CC(=C(C=C1C(=O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(E)-3-(3,4-dihydroxyphenyl)prop-2-enoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1=CC(=C(C=C1/C=C/C(=O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4aS,8aS)-3,8a-dimethyl-5-methylidene-4a,6,7,8-tetrahydro-4H-benzo[f][1]benzofuran-2-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC1=C2C[C@H]3C(=C)CCC[C@@]3(C=C2OC1=O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4aS,8aR,9aS)-3,8a-dimethyl-5-methylidene-4a,6,7,8,9,9a-hexahydro-4H-benzo[f][1]benzofuran-2-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC1=C2C[C@H]3C(=C)CCC[C@@]3(C[C@@H]2OC1=O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4aS,8aR,9aS)-9a-hydroxy-3,8a-dimethyl-5-methylidene-4,4a,6,7,8,9-hexahydrobenzo[f][1]benzofuran-2-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">248.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC1=C2C[C@H]3C(=C)CCC[C@@]3(C[C@@]2(OC1=O)O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-hydroxychromen-2-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1=CC(=CC2=C1C=CC(=O)O2)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chlorogenic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,3R,4R,5R)-3-[(E)-3-(3,4-dihydroxyphenyl)prop-2-enoyl]oxy-1,4,5-trihydroxycyclohexane-1-carboxylic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16H18O9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">354.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1794427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1[C@H]([C@H]([C@@H](C[C@@]1(C(=O)O)O)OC(=O)/C=C/C2=CC(=C(C=C2)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vanillic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-hydroxy-3-methoxybenzoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C8H8O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=C(C=CC(=C1)C(=O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-[(3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">468.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=CCCC([C@H]1CC[C@@]2([C@@]1(CC=C3C2=CC[C@H]([C@]3(C)CCC(=O)O)C(=C)C)C)C)C(=O)O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poricoic acid b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-[(2R,3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">484.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=CCCC([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@H]([C@]3(C)CCC(=O)O)C(=C)C)C)C)O)C(=O)O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(E,2R)-2-[(2R,3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-7-hydroxy-6-methylhept-5-enoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=C)[C@@H]1CC=C2C(=CC[C@]3([C@]2(C[C@H]([C@@H]3[C@@H](CC/C=C(\C)/CO)C(=O)O)O)C)C)[C@@]1(C)CCC(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3S,5R,10S,13R,14R,17R)-3-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methylhept-5-enoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">454.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=CCC[C@H]([C@H]1CC[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)O)C)C)C)C(=O)O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(2R,3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,5,7,8,9-octahydrocyclopenta[a]naphthalen-3-yl]-6-methylhept-5-enoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">486.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=CCC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@H]([C@]3(C)CCC(=O)O)C(=C)C)C)C)O)C(=O)O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poriacosone b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=O)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)O)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poriacosone a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3R,5R,10S,13R,14R,16R,17R)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=O)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@H](C4(C)C)O)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3S,5R,10S,13R,14R,17R)-3-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methylhept-5-enoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">456.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=CCC[C@H]([C@H]1CC[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)O)C)C)C)C(=O)O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3R,5R,10S,13R,14R,16R,17R)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-oxoheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">488.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=O)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@H](C4(C)C)O)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(5R,10S,13R,14R,16R,17R)-16-hydroxy-4,4,10,13,14-pentamethyl-3-oxo-1,2,5,6,12,15,16,17-octahydrocyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">482.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CCC(=O)C4(C)C)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(2R,3R,3aR,9bR)-2-hydroxy-3a,7,9b-trimethyl-6-(4-methyl-3-oxopentyl)-2,3,4,5-tetrahydro-1H-cyclopenta[a]naphthalen-3-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC1=C(C2=C(C=C1)[C@@]3(C[C@H]([C@@H]([C@]3(CC2)C)[C@@H](CCC(=C)C(C)C)C(=O)O)O)C)CCC(=O)C(C)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-[(3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-hydroxy-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">498.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=C)[C@@H]1CC=C2C(=CC[C@]3([C@]2(CC[C@@H]3C(CCC(=C)C(C)(C)O)C(=O)O)C)C)[C@@]1(C)CCC(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-[(2R,3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,5,7-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CCC([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2C=C[C@H]([C@]3(C)CCC(=O)O)C(=C)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(2R,3R,3aR,6S,7R,9bR)-6-(2-carboxyethyl)-2-hydroxy-7-(3-hydroxyprop-1-en-2-yl)-3a,6,9b-trimethyl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@H]([C@]3(C)CCC(=O)O)C(=C)CO)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-6-methyl-5-methylidene-2-[(5R,10S,13R,14R,17R)-4,4,10,13,14-pentamethyl-3-oxo-1,2,5,6,7,11,12,15,16,17-decahydrocyclopenta[a]phenanthren-17-yl]heptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1CC[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CCC(=O)C4(C)C)C)C)C)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3R,5R,10S,13R,14R,16R,17R)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@H](C4(C)C)O)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)O)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(2R,3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,5,7,8,9-octahydrocyclopenta[a]naphthalen-3-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@H]([C@]3(C)CCC(=O)O)C(=C)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-[(2R,3R,3aR,6S,7S,9bR)-6-(2-carboxyethyl)-2-hydroxy-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,5,7,8,9-octahydrocyclopenta[a]naphthalen-3-yl]-6-hydroxy-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">516.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=C)[C@@H]1CCC2=C([C@@]1(C)CCC(=O)O)CC[C@]3([C@]2(C[C@H]([C@@H]3C(CCC(=C)C(C)(C)O)C(=O)O)O)C)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3S,5R,10S,13R,14R,17R)-3-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1CC[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)O)C)C)C)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3,16-dihydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)O)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(2R,3R,3aR,6S,7S,9bR)-2-hydroxy-6-(3-methoxy-3-oxopropyl)-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">512.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@H]([C@]3(C)CCC(=O)OC)C(=C)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methylhept-5-enoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=CCC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)OC(=O)C)C)C)C)O)C(=O)O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3R,3aR,6S,7S,9bR)-6-(3-ethoxy-3-oxopropyl)-3a,6,9b-trimethyl-7-prop-1-en-2-yl-1,2,3,4,7,8-hexahydrocyclopenta[a]naphthalen-3-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">510.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCOC(=O)CC[C@]1([C@@H](CC=C2C1=CC[C@]3([C@]2(CC[C@@H]3[C@@H](CCC(=C)C(C)C)C(=O)O)C)C)C(=C)C)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3R,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">526.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@H](C4(C)C)OC(=O)C)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)OC(=O)C)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3S,4S,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4-(hydroxymethyl)-4,10,13,14-tetramethyl-2,3,5,6,12,15,16,17-octahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">542.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CC=C3C2=CC[C@@H]4[C@@]3(CC[C@@H]([C@]4(C)CO)OC(=O)C)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">528.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)OC(=O)C)C)C)C)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-hydroxy-6-methyl-5-methylideneheptanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">544.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177826656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=O)O[C@H]1CC[C@]2([C@H](C1(C)C)CCC3=C2CC[C@]4([C@]3(C[C@H]([C@@H]4[C@@H](CCC(=C)C(C)(C)O)C(=O)O)O)C)C)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pachymic acid methyl ester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">methyl (2R)-2-[(3S,5R,10S,13R,14R,16R,17R)-3-acetyloxy-16-hydroxy-4,4,10,13,14-pentamethyl-2,3,5,6,7,11,12,15,16,17-decahydro-1H-cyclopenta[a]phenanthren-17-yl]-6-methyl-5-methylideneheptanoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">542.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(C)C(=C)CC[C@H]([C@H]1[C@@H](C[C@@]2([C@@]1(CCC3=C2CC[C@@H]4[C@@]3(CC[C@@H](C4(C)C)OC(=O)C)C)C)C)O)C(=O)OC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(E)-3-(3-methoxy-4-sulfooxyphenyl)prop-2-enoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=C(C=CC(=C1)/C=C/C(=O)O)OS(=O)(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2S)-5,7-dihydroxy-2-(4-hydroxyphenyl)-2,3-dihydrochromen-4-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1[C@H](OC2=CC(=CC(=C2C1=O)O)O)C3=CC=C(C=C3)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R,3R)-2-(3,4-dihydroxyphenyl)-3,4-dihydro-2H-chromene-3,5,7-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">290.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1[C@H]([C@H](OC2=CC(=CC(=C21)O)O)C3=CC(=C(C=C3)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">catechin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R,3S)-2-(3,4-dihydroxyphenyl)-3,4-dihydro-2H-chromene-3,5,7-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1[C@@H]([C@H](OC2=CC(=CC(=C21)O)O)C3=CC(=C(C=C3)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-dephenyl paeoniflorin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2S,3R,4S,5S,6R)-2-[[(1R,2S,3R,5R,6R,8S)-6-hydroxy-2-(hydroxymethyl)-8-methyl-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-3-yl]oxy]-6-(hydroxymethyl)oxane-3,4,5-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71452333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@]12C[C@@]3([C@@H]4C[C@]1([C@@]4([C@H](O2)O3)CO)O[C@H]5[C@@H]([C@H]([C@@H]([C@H](O5)CO)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">albiflorin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1R,2S,3R,5R,6S,8S)-6-hydroxy-8-methyl-3-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-2-yl]methyl benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">480.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@]12C[C@]3([C@@H]4C[C@]1([C@@]4([C@H](O2)O3)COC(=O)C5=CC=CC=C5)O[C@H]6[C@@H]([C@H]([C@@H]([C@H](O6)CO)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1R,4R)-4-hydroxy-6-methyl-8-oxo-1-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-7-oxatricyclo[4.3.0.03,9]nonan-9-yl]methyl benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC12C[C@H](C3C[C@]1(C3(C(=O)O2)COC(=O)C4=CC=CC=C4)O[C@H]5[C@@H]([C@H]([C@@H]([C@H](O5)CO)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxypaeoniflorin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1R,2S,3R,5R,6R,8S)-6-hydroxy-8-methyl-3-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-2-yl]methyl 4-hydroxybenzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">496.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@]12C[C@@]3([C@@H]4C[C@]1([C@@]4([C@H](O2)O3)COC(=O)C5=CC=C(C=C5)O)O[C@H]6[C@@H]([C@H]([C@@H]([C@H](O6)CO)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(2R,3S,4S,5R,6S)-6-[[(1R,2S,3R,5R,6R,8S)-2-(benzoyloxymethyl)-6-hydroxy-8-methyl-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-3-yl]oxy]-3,4,5-trihydroxyoxan-2-yl]methyl benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">584.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@]12C[C@@]3([C@@H]4C[C@]1([C@@]4([C@H](O2)O3)COC(=O)C5=CC=CC=C5)O[C@H]6[C@@H]([C@H]([C@@H]([C@H](O6)COC(=O)C7=CC=CC=C7)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(2R,3S,4S,5R,6S)-6-[[(1R,2S,3R,5R,6S,8S)-2-(benzoyloxymethyl)-6-hydroxy-8-methyl-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-3-yl]oxy]-3,4,5-trihydroxyoxan-2-yl]methyl benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177827917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@]12C[C@]3([C@@H]4C[C@]1([C@@]4([C@H](O2)O3)COC(=O)C5=CC=CC=C5)O[C@H]6[C@@H]([C@H]([C@@H]([C@H](O6)COC(=O)C7=CC=CC=C7)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6'-O-galloyl paeoniflorin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(2R,3S,4S,5R,6S)-6-[[(2S,3R,5R,6R,8S)-2-(benzoyloxymethyl)-6-hydroxy-8-methyl-9,10-dioxatetracyclo[4.3.1.02,5.03,8]decan-3-yl]oxy]-3,4,5-trihydroxyoxan-2-yl]methyl 3,4,5-trihydroxybenzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">632.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122169317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@]12C[C@@]3([C@@H]4C[C@]1([C@@]4(C(O2)O3)COC(=O)C5=CC=CC=C5)O[C@H]6[C@@H]([C@H]([C@@H]([C@H](O6)COC(=O)C7=CC(=C(C(=C7)O)O)O)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">galloylalbiflorin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(2R,3S,4S,5R,6S)-6-[[(1R,3R,4R,6S,9S)-9-(benzoyloxymethyl)-4-hydroxy-6-methyl-8-oxo-7-oxatricyclo[4.3.0.03,9]nonan-1-yl]oxy]-3,4,5-trihydroxyoxan-2-yl]methyl 3,4,5-trihydroxybenzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124079396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@]12C[C@H]([C@@H]3C[C@]1([C@@]3(C(=O)O2)COC(=O)C4=CC=CC=C4)O[C@H]5[C@@H]([C@H]([C@@H]([C@H](O5)COC(=O)C6=CC(=C(C(=C6)O)O)O)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(2R,3R,4S,5R,6S)-3,4,5,6-tetrakis[(3,4,5-trihydroxybenzoyl)oxy]oxan-2-yl]methyl 3,4,5-trihydroxybenzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">940.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1=C(C=C(C(=C1O)O)O)C(=O)OC[C@@H]2[C@H]([C@@H]([C@H]([C@@H](O2)OC(=O)C3=CC(=C(C(=C3)O)O)O)OC(=O)C4=CC(=C(C(=C4)O)O)O)OC(=O)C5=CC(=C(C(=C5)O)O)O)OC(=O)C6=CC(=C(C(=C6)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,4,5-trihydroxybenzoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1=C(C=C(C(=C1O)O)O)C(=O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-Shogaol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(E)-1-(4-hydroxy-3-methoxyphenyl)dec-4-en-3-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">276.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCCCC/C=C/C(=O)CCC1=CC(=C(C=C1)O)OC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(–)-[6]-Gingerol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5S)-5-hydroxy-1-(4-hydroxy-3-methoxyphenyl)decan-3-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCCCC[C@@H](CC(=O)CCC1=CC(=C(C=C1)O)OC)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(–)-[8]-Gingerol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5S)-5-hydroxy-1-(4-hydroxy-3-methoxyphenyl)dodecan-3-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">322.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCCCCCC[C@@H](CC(=O)CCC1=CC(=C(C=C1)O)OC)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(–)-[10]-Gingerol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5S)-5-hydroxy-1-(4-hydroxy-3-methoxyphenyl)tetradecan-3-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C21H34O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCCCCCCCC[C@@H](CC(=O)CCC1=CC(=C(C=C1)O)OC)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zingerone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-(4-hydroxy-3-methoxyphenyl)butan-2-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11H14O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=O)CCC1=CC(=C(C=C1)O)OC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2972,23 +2951,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -3270,11 +3239,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3294,7 +3263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -3314,7 +3283,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -3334,7 +3303,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -3354,7 +3323,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -3374,7 +3343,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -3394,7 +3363,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3414,7 +3383,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -3434,7 +3403,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -3454,7 +3423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -3467,11 +3436,12 @@
       <c r="D10" t="s">
         <v>26</v>
       </c>
+      <c r="E10"/>
       <c r="F10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -3491,7 +3461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -3511,7 +3481,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -3531,7 +3501,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -3551,7 +3521,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -3571,7 +3541,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -3591,7 +3561,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -3611,7 +3581,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -3631,7 +3601,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -3644,23 +3614,23 @@
       <c r="D19" t="s">
         <v>45</v>
       </c>
+      <c r="E19"/>
       <c r="F19" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G253"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3683,7 +3653,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -3706,7 +3676,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -3729,7 +3699,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -3752,7 +3722,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -3775,7 +3745,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -3798,7 +3768,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3821,7 +3791,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3844,7 +3814,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -3867,7 +3837,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -3890,7 +3860,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -3913,7 +3883,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -3936,7 +3906,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -3959,7 +3929,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -3982,7 +3952,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -4005,7 +3975,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -4028,7 +3998,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -4051,7 +4021,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -4074,7 +4044,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -4097,7 +4067,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -4120,7 +4090,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -4143,7 +4113,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -4166,7 +4136,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -4189,7 +4159,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -4212,7 +4182,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -4235,7 +4205,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -4258,7 +4228,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -4281,7 +4251,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -4304,7 +4274,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -4327,7 +4297,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -4350,7 +4320,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -4373,7 +4343,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -4396,7 +4366,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -4419,7 +4389,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -4442,7 +4412,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -4465,7 +4435,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -4488,7 +4458,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -4511,7 +4481,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -4534,7 +4504,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -4557,7 +4527,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -4580,7 +4550,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -4603,7 +4573,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -4626,7 +4596,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -4649,7 +4619,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -4672,7 +4642,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -4695,7 +4665,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -4718,7 +4688,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -4741,7 +4711,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -4764,7 +4734,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -4787,7 +4757,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -4810,7 +4780,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -4833,7 +4803,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -4856,7 +4826,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -4879,7 +4849,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -4902,7 +4872,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -4925,7 +4895,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -4948,7 +4918,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" t="s">
         <v>16</v>
       </c>
@@ -4971,7 +4941,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -4994,7 +4964,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" t="s">
         <v>16</v>
       </c>
@@ -5017,7 +4987,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60" t="s">
         <v>16</v>
       </c>
@@ -5040,7 +5010,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61" t="s">
         <v>16</v>
       </c>
@@ -5063,7 +5033,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62" t="s">
         <v>16</v>
       </c>
@@ -5086,7 +5056,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63" t="s">
         <v>16</v>
       </c>
@@ -5109,7 +5079,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="A64" t="s">
         <v>16</v>
       </c>
@@ -5132,7 +5102,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="A65" t="s">
         <v>16</v>
       </c>
@@ -5155,7 +5125,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="A66" t="s">
         <v>16</v>
       </c>
@@ -5178,7 +5148,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="A67" t="s">
         <v>16</v>
       </c>
@@ -5201,7 +5171,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="A68" t="s">
         <v>16</v>
       </c>
@@ -5224,7 +5194,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="A69" t="s">
         <v>16</v>
       </c>
@@ -5247,7 +5217,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="A70" t="s">
         <v>16</v>
       </c>
@@ -5270,7 +5240,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="A71" t="s">
         <v>16</v>
       </c>
@@ -5293,7 +5263,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="A72" t="s">
         <v>16</v>
       </c>
@@ -5316,7 +5286,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73" t="s">
         <v>16</v>
       </c>
@@ -5339,7 +5309,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="A74" t="s">
         <v>16</v>
       </c>
@@ -5362,7 +5332,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="A75" t="s">
         <v>16</v>
       </c>
@@ -5385,7 +5355,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -5408,7 +5378,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="A77" t="s">
         <v>16</v>
       </c>
@@ -5431,7 +5401,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="A78" t="s">
         <v>16</v>
       </c>
@@ -5454,7 +5424,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="A79" t="s">
         <v>16</v>
       </c>
@@ -5477,7 +5447,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="A80" t="s">
         <v>16</v>
       </c>
@@ -5500,7 +5470,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="A81" t="s">
         <v>16</v>
       </c>
@@ -5523,7 +5493,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="A82" t="s">
         <v>16</v>
       </c>
@@ -5546,7 +5516,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -5569,7 +5539,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -5592,7 +5562,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85">
       <c r="A85" t="s">
         <v>16</v>
       </c>
@@ -5615,7 +5585,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86">
       <c r="A86" t="s">
         <v>16</v>
       </c>
@@ -5638,7 +5608,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87">
       <c r="A87" t="s">
         <v>16</v>
       </c>
@@ -5661,7 +5631,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88">
       <c r="A88" t="s">
         <v>16</v>
       </c>
@@ -5684,7 +5654,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89">
       <c r="A89" t="s">
         <v>16</v>
       </c>
@@ -5707,7 +5677,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90">
       <c r="A90" t="s">
         <v>16</v>
       </c>
@@ -5730,7 +5700,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91">
       <c r="A91" t="s">
         <v>16</v>
       </c>
@@ -5753,7 +5723,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92">
       <c r="A92" t="s">
         <v>16</v>
       </c>
@@ -5776,7 +5746,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93">
       <c r="A93" t="s">
         <v>16</v>
       </c>
@@ -5799,7 +5769,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94">
       <c r="A94" t="s">
         <v>16</v>
       </c>
@@ -5822,7 +5792,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -5845,7 +5815,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -5868,7 +5838,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -5891,7 +5861,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -5914,7 +5884,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99">
       <c r="A99" t="s">
         <v>16</v>
       </c>
@@ -5937,7 +5907,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100">
       <c r="A100" t="s">
         <v>16</v>
       </c>
@@ -5960,7 +5930,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -5983,7 +5953,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -6006,7 +5976,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -6029,7 +5999,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -6052,7 +6022,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -6075,7 +6045,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106">
       <c r="A106" t="s">
         <v>16</v>
       </c>
@@ -6098,7 +6068,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107">
       <c r="A107" t="s">
         <v>16</v>
       </c>
@@ -6121,7 +6091,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108">
       <c r="A108" t="s">
         <v>16</v>
       </c>
@@ -6144,7 +6114,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109">
       <c r="A109" t="s">
         <v>16</v>
       </c>
@@ -6167,7 +6137,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110">
       <c r="A110" t="s">
         <v>16</v>
       </c>
@@ -6190,7 +6160,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111">
       <c r="A111" t="s">
         <v>16</v>
       </c>
@@ -6213,7 +6183,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112">
       <c r="A112" t="s">
         <v>16</v>
       </c>
@@ -6236,7 +6206,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113">
       <c r="A113" t="s">
         <v>16</v>
       </c>
@@ -6259,7 +6229,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114">
       <c r="A114" t="s">
         <v>16</v>
       </c>
@@ -6282,7 +6252,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115">
       <c r="A115" t="s">
         <v>16</v>
       </c>
@@ -6305,7 +6275,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116">
       <c r="A116" t="s">
         <v>16</v>
       </c>
@@ -6328,7 +6298,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117">
       <c r="A117" t="s">
         <v>16</v>
       </c>
@@ -6351,7 +6321,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118">
       <c r="A118" t="s">
         <v>16</v>
       </c>
@@ -6374,7 +6344,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119">
       <c r="A119" t="s">
         <v>16</v>
       </c>
@@ -6397,7 +6367,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120">
       <c r="A120" t="s">
         <v>16</v>
       </c>
@@ -6420,7 +6390,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121">
       <c r="A121" t="s">
         <v>16</v>
       </c>
@@ -6443,7 +6413,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122">
       <c r="A122" t="s">
         <v>16</v>
       </c>
@@ -6466,7 +6436,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123">
       <c r="A123" t="s">
         <v>16</v>
       </c>
@@ -6489,7 +6459,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124">
       <c r="A124" t="s">
         <v>16</v>
       </c>
@@ -6512,7 +6482,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125">
       <c r="A125" t="s">
         <v>16</v>
       </c>
@@ -6535,7 +6505,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126">
       <c r="A126" t="s">
         <v>16</v>
       </c>
@@ -6558,7 +6528,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127">
       <c r="A127" t="s">
         <v>16</v>
       </c>
@@ -6581,7 +6551,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128">
       <c r="A128" t="s">
         <v>16</v>
       </c>
@@ -6604,7 +6574,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129">
       <c r="A129" t="s">
         <v>16</v>
       </c>
@@ -6627,7 +6597,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130">
       <c r="A130" t="s">
         <v>16</v>
       </c>
@@ -6650,7 +6620,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131">
       <c r="A131" t="s">
         <v>16</v>
       </c>
@@ -6673,7 +6643,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132">
       <c r="A132" t="s">
         <v>16</v>
       </c>
@@ -6696,7 +6666,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133">
       <c r="A133" t="s">
         <v>16</v>
       </c>
@@ -6719,7 +6689,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134">
       <c r="A134" t="s">
         <v>16</v>
       </c>
@@ -6742,7 +6712,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135">
       <c r="A135" t="s">
         <v>16</v>
       </c>
@@ -6765,7 +6735,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136">
       <c r="A136" t="s">
         <v>16</v>
       </c>
@@ -6788,7 +6758,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -6811,7 +6781,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -6834,7 +6804,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139">
       <c r="A139" t="s">
         <v>16</v>
       </c>
@@ -6857,7 +6827,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140">
       <c r="A140" t="s">
         <v>23</v>
       </c>
@@ -6880,7 +6850,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141">
       <c r="A141" t="s">
         <v>23</v>
       </c>
@@ -6903,7 +6873,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142">
       <c r="A142" t="s">
         <v>23</v>
       </c>
@@ -6926,7 +6896,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143">
       <c r="A143" t="s">
         <v>23</v>
       </c>
@@ -6949,7 +6919,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144">
       <c r="A144" t="s">
         <v>28</v>
       </c>
@@ -6972,7 +6942,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145">
       <c r="A145" t="s">
         <v>28</v>
       </c>
@@ -6995,7 +6965,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146">
       <c r="A146" t="s">
         <v>28</v>
       </c>
@@ -7018,7 +6988,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147">
       <c r="A147" t="s">
         <v>28</v>
       </c>
@@ -7041,7 +7011,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148">
       <c r="A148" t="s">
         <v>28</v>
       </c>
@@ -7064,7 +7034,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149">
       <c r="A149" t="s">
         <v>28</v>
       </c>
@@ -7087,7 +7057,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150">
       <c r="A150" t="s">
         <v>28</v>
       </c>
@@ -7110,7 +7080,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151">
       <c r="A151" t="s">
         <v>28</v>
       </c>
@@ -7133,7 +7103,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152">
       <c r="A152" t="s">
         <v>28</v>
       </c>
@@ -7156,7 +7126,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153">
       <c r="A153" t="s">
         <v>28</v>
       </c>
@@ -7179,7 +7149,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154">
       <c r="A154" t="s">
         <v>28</v>
       </c>
@@ -7202,7 +7172,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155">
       <c r="A155" t="s">
         <v>28</v>
       </c>
@@ -7225,7 +7195,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156">
       <c r="A156" t="s">
         <v>28</v>
       </c>
@@ -7248,7 +7218,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157">
       <c r="A157" t="s">
         <v>28</v>
       </c>
@@ -7271,7 +7241,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158">
       <c r="A158" t="s">
         <v>28</v>
       </c>
@@ -7294,7 +7264,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159">
       <c r="A159" t="s">
         <v>28</v>
       </c>
@@ -7317,7 +7287,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160">
       <c r="A160" t="s">
         <v>28</v>
       </c>
@@ -7340,7 +7310,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161">
       <c r="A161" t="s">
         <v>28</v>
       </c>
@@ -7363,7 +7333,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162">
       <c r="A162" t="s">
         <v>28</v>
       </c>
@@ -7386,7 +7356,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163">
       <c r="A163" t="s">
         <v>28</v>
       </c>
@@ -7409,7 +7379,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164">
       <c r="A164" t="s">
         <v>28</v>
       </c>
@@ -7432,7 +7402,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165">
       <c r="A165" t="s">
         <v>28</v>
       </c>
@@ -7455,7 +7425,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166">
       <c r="A166" t="s">
         <v>28</v>
       </c>
@@ -7478,7 +7448,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167">
       <c r="A167" t="s">
         <v>28</v>
       </c>
@@ -7501,7 +7471,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168">
       <c r="A168" t="s">
         <v>28</v>
       </c>
@@ -7524,7 +7494,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169">
       <c r="A169" t="s">
         <v>28</v>
       </c>
@@ -7547,7 +7517,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170">
       <c r="A170" t="s">
         <v>28</v>
       </c>
@@ -7570,7 +7540,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171">
       <c r="A171" t="s">
         <v>28</v>
       </c>
@@ -7593,7 +7563,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172">
       <c r="A172" t="s">
         <v>28</v>
       </c>
@@ -7616,7 +7586,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173">
       <c r="A173" t="s">
         <v>28</v>
       </c>
@@ -7639,7 +7609,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174">
       <c r="A174" t="s">
         <v>28</v>
       </c>
@@ -7662,7 +7632,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175">
       <c r="A175" t="s">
         <v>28</v>
       </c>
@@ -7685,7 +7655,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176">
       <c r="A176" t="s">
         <v>28</v>
       </c>
@@ -7708,7 +7678,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177">
       <c r="A177" t="s">
         <v>28</v>
       </c>
@@ -7731,7 +7701,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178">
       <c r="A178" t="s">
         <v>28</v>
       </c>
@@ -7754,7 +7724,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179">
       <c r="A179" t="s">
         <v>28</v>
       </c>
@@ -7777,7 +7747,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180">
       <c r="A180" t="s">
         <v>28</v>
       </c>
@@ -7800,7 +7770,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181">
       <c r="A181" t="s">
         <v>28</v>
       </c>
@@ -7823,7 +7793,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182">
       <c r="A182" t="s">
         <v>28</v>
       </c>
@@ -7846,7 +7816,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183">
       <c r="A183" t="s">
         <v>28</v>
       </c>
@@ -7869,7 +7839,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184">
       <c r="A184" t="s">
         <v>28</v>
       </c>
@@ -7892,7 +7862,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185">
       <c r="A185" t="s">
         <v>28</v>
       </c>
@@ -7915,7 +7885,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186">
       <c r="A186" t="s">
         <v>28</v>
       </c>
@@ -7938,7 +7908,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187">
       <c r="A187" t="s">
         <v>28</v>
       </c>
@@ -7961,7 +7931,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188">
       <c r="A188" t="s">
         <v>28</v>
       </c>
@@ -7984,7 +7954,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189">
       <c r="A189" t="s">
         <v>28</v>
       </c>
@@ -8007,7 +7977,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190">
       <c r="A190" t="s">
         <v>28</v>
       </c>
@@ -8030,7 +8000,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191">
       <c r="A191" t="s">
         <v>28</v>
       </c>
@@ -8053,7 +8023,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192">
       <c r="A192" t="s">
         <v>28</v>
       </c>
@@ -8076,7 +8046,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193">
       <c r="A193" t="s">
         <v>28</v>
       </c>
@@ -8099,7 +8069,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194">
       <c r="A194" t="s">
         <v>28</v>
       </c>
@@ -8122,7 +8092,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195">
       <c r="A195" t="s">
         <v>28</v>
       </c>
@@ -8145,7 +8115,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196">
       <c r="A196" t="s">
         <v>28</v>
       </c>
@@ -8168,7 +8138,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197">
       <c r="A197" t="s">
         <v>28</v>
       </c>
@@ -8191,7 +8161,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198">
       <c r="A198" t="s">
         <v>28</v>
       </c>
@@ -8214,7 +8184,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199">
       <c r="A199" t="s">
         <v>28</v>
       </c>
@@ -8237,7 +8207,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200">
       <c r="A200" t="s">
         <v>28</v>
       </c>
@@ -8260,7 +8230,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201">
       <c r="A201" t="s">
         <v>28</v>
       </c>
@@ -8283,7 +8253,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202">
       <c r="A202" t="s">
         <v>28</v>
       </c>
@@ -8306,7 +8276,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203">
       <c r="A203" t="s">
         <v>28</v>
       </c>
@@ -8329,7 +8299,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204">
       <c r="A204" t="s">
         <v>28</v>
       </c>
@@ -8352,7 +8322,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205">
       <c r="A205" t="s">
         <v>28</v>
       </c>
@@ -8375,7 +8345,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206">
       <c r="A206" t="s">
         <v>28</v>
       </c>
@@ -8398,7 +8368,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207">
       <c r="A207" t="s">
         <v>28</v>
       </c>
@@ -8421,7 +8391,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208">
       <c r="A208" t="s">
         <v>28</v>
       </c>
@@ -8444,7 +8414,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209">
       <c r="A209" t="s">
         <v>28</v>
       </c>
@@ -8467,7 +8437,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210">
       <c r="A210" t="s">
         <v>28</v>
       </c>
@@ -8490,7 +8460,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211">
       <c r="A211" t="s">
         <v>28</v>
       </c>
@@ -8513,7 +8483,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212">
       <c r="A212" t="s">
         <v>28</v>
       </c>
@@ -8536,7 +8506,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213">
       <c r="A213" t="s">
         <v>28</v>
       </c>
@@ -8559,7 +8529,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214">
       <c r="A214" t="s">
         <v>28</v>
       </c>
@@ -8582,7 +8552,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215">
       <c r="A215" t="s">
         <v>28</v>
       </c>
@@ -8605,7 +8575,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216">
       <c r="A216" t="s">
         <v>28</v>
       </c>
@@ -8628,7 +8598,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217">
       <c r="A217" t="s">
         <v>28</v>
       </c>
@@ -8651,7 +8621,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218">
       <c r="A218" t="s">
         <v>28</v>
       </c>
@@ -8674,7 +8644,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219">
       <c r="A219" t="s">
         <v>28</v>
       </c>
@@ -8697,7 +8667,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220">
       <c r="A220" t="s">
         <v>28</v>
       </c>
@@ -8720,7 +8690,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221">
       <c r="A221" t="s">
         <v>28</v>
       </c>
@@ -8743,7 +8713,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222">
       <c r="A222" t="s">
         <v>28</v>
       </c>
@@ -8766,7 +8736,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223">
       <c r="A223" t="s">
         <v>28</v>
       </c>
@@ -8789,7 +8759,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224">
       <c r="A224" t="s">
         <v>28</v>
       </c>
@@ -8812,7 +8782,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225">
       <c r="A225" t="s">
         <v>35</v>
       </c>
@@ -8835,7 +8805,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226">
       <c r="A226" t="s">
         <v>35</v>
       </c>
@@ -8858,7 +8828,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227">
       <c r="A227" t="s">
         <v>35</v>
       </c>
@@ -8881,7 +8851,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228">
       <c r="A228" t="s">
         <v>35</v>
       </c>
@@ -8904,7 +8874,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229">
       <c r="A229" t="s">
         <v>35</v>
       </c>
@@ -8927,7 +8897,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230">
       <c r="A230" t="s">
         <v>35</v>
       </c>
@@ -8950,7 +8920,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231">
       <c r="A231" t="s">
         <v>35</v>
       </c>
@@ -8973,7 +8943,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232">
       <c r="A232" t="s">
         <v>35</v>
       </c>
@@ -8996,7 +8966,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233">
       <c r="A233" t="s">
         <v>35</v>
       </c>
@@ -9019,7 +8989,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234">
       <c r="A234" t="s">
         <v>35</v>
       </c>
@@ -9042,7 +9012,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235">
       <c r="A235" t="s">
         <v>35</v>
       </c>
@@ -9065,7 +9035,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236">
       <c r="A236" t="s">
         <v>35</v>
       </c>
@@ -9088,7 +9058,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237">
       <c r="A237" t="s">
         <v>35</v>
       </c>
@@ -9111,7 +9081,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238">
       <c r="A238" t="s">
         <v>35</v>
       </c>
@@ -9134,7 +9104,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239">
       <c r="A239" t="s">
         <v>35</v>
       </c>
@@ -9157,7 +9127,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240">
       <c r="A240" t="s">
         <v>35</v>
       </c>
@@ -9180,7 +9150,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241">
       <c r="A241" t="s">
         <v>35</v>
       </c>
@@ -9203,7 +9173,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242">
       <c r="A242" t="s">
         <v>35</v>
       </c>
@@ -9226,7 +9196,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243">
       <c r="A243" t="s">
         <v>35</v>
       </c>
@@ -9249,7 +9219,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244">
       <c r="A244" t="s">
         <v>35</v>
       </c>
@@ -9272,7 +9242,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245">
       <c r="A245" t="s">
         <v>35</v>
       </c>
@@ -9295,7 +9265,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246">
       <c r="A246" t="s">
         <v>35</v>
       </c>
@@ -9318,7 +9288,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247">
       <c r="A247" t="s">
         <v>35</v>
       </c>
@@ -9341,7 +9311,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248">
       <c r="A248" t="s">
         <v>35</v>
       </c>
@@ -9364,7 +9334,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249">
       <c r="A249" t="s">
         <v>35</v>
       </c>
@@ -9387,7 +9357,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250">
       <c r="A250" t="s">
         <v>35</v>
       </c>
@@ -9410,7 +9380,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251">
       <c r="A251" t="s">
         <v>42</v>
       </c>
@@ -9433,7 +9403,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252">
       <c r="A252" t="s">
         <v>42</v>
       </c>
@@ -9456,7 +9426,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253">
       <c r="A253" t="s">
         <v>42</v>
       </c>
@@ -9480,53 +9450,49 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J107"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="s">
         <v>614</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>615</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>616</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>617</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>618</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>619</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>620</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>621</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>622</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -9558,7 +9524,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -9590,7 +9556,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -9622,7 +9588,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -9654,7 +9620,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -9686,7 +9652,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -9718,7 +9684,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -9750,7 +9716,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -9782,7 +9748,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -9814,7 +9780,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -9846,7 +9812,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -9878,7 +9844,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -9910,7 +9876,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -9942,7 +9908,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -9974,7 +9940,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -10006,7 +9972,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -10038,7 +10004,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -10070,7 +10036,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -10102,7 +10068,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -10134,7 +10100,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -10166,7 +10132,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -10198,7 +10164,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -10230,7 +10196,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -10262,7 +10228,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -10294,7 +10260,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -10326,7 +10292,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -10358,7 +10324,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -10390,7 +10356,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -10422,7 +10388,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -10454,7 +10420,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -10486,7 +10452,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -10518,7 +10484,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -10550,7 +10516,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -10582,7 +10548,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -10614,7 +10580,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" t="s">
         <v>16</v>
       </c>
@@ -10646,7 +10612,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -10678,7 +10644,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -10710,7 +10676,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
         <v>16</v>
       </c>
@@ -10742,7 +10708,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" t="s">
         <v>16</v>
       </c>
@@ -10774,7 +10740,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -10806,7 +10772,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" t="s">
         <v>16</v>
       </c>
@@ -10838,7 +10804,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" t="s">
         <v>16</v>
       </c>
@@ -10870,7 +10836,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -10902,7 +10868,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" t="s">
         <v>16</v>
       </c>
@@ -10934,7 +10900,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -10966,7 +10932,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" t="s">
         <v>16</v>
       </c>
@@ -10998,7 +10964,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" t="s">
         <v>16</v>
       </c>
@@ -11030,7 +10996,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" t="s">
         <v>16</v>
       </c>
@@ -11062,7 +11028,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" t="s">
         <v>16</v>
       </c>
@@ -11094,7 +11060,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" t="s">
         <v>23</v>
       </c>
@@ -11126,7 +11092,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -11158,7 +11124,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" t="s">
         <v>23</v>
       </c>
@@ -11190,7 +11156,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" t="s">
         <v>23</v>
       </c>
@@ -11222,7 +11188,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" t="s">
         <v>23</v>
       </c>
@@ -11254,7 +11220,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" t="s">
         <v>23</v>
       </c>
@@ -11286,7 +11252,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" t="s">
         <v>23</v>
       </c>
@@ -11318,7 +11284,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" t="s">
         <v>28</v>
       </c>
@@ -11350,7 +11316,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" t="s">
         <v>28</v>
       </c>
@@ -11382,7 +11348,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60" t="s">
         <v>28</v>
       </c>
@@ -11414,7 +11380,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61" t="s">
         <v>28</v>
       </c>
@@ -11446,7 +11412,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62" t="s">
         <v>28</v>
       </c>
@@ -11478,7 +11444,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63" t="s">
         <v>28</v>
       </c>
@@ -11510,7 +11476,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="A64" t="s">
         <v>28</v>
       </c>
@@ -11542,7 +11508,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="A65" t="s">
         <v>28</v>
       </c>
@@ -11574,7 +11540,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -11606,7 +11572,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="A67" t="s">
         <v>28</v>
       </c>
@@ -11638,7 +11604,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="A68" t="s">
         <v>28</v>
       </c>
@@ -11670,7 +11636,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="A69" t="s">
         <v>28</v>
       </c>
@@ -11702,7 +11668,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="A70" t="s">
         <v>28</v>
       </c>
@@ -11734,7 +11700,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="A71" t="s">
         <v>28</v>
       </c>
@@ -11766,7 +11732,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="A72" t="s">
         <v>28</v>
       </c>
@@ -11798,7 +11764,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73" t="s">
         <v>28</v>
       </c>
@@ -11830,7 +11796,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="A74" t="s">
         <v>28</v>
       </c>
@@ -11862,7 +11828,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="A75" t="s">
         <v>28</v>
       </c>
@@ -11894,7 +11860,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="A76" t="s">
         <v>28</v>
       </c>
@@ -11926,7 +11892,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="A77" t="s">
         <v>28</v>
       </c>
@@ -11958,7 +11924,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="A78" t="s">
         <v>28</v>
       </c>
@@ -11990,7 +11956,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="A79" t="s">
         <v>28</v>
       </c>
@@ -12022,7 +11988,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="A80" t="s">
         <v>28</v>
       </c>
@@ -12054,7 +12020,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="A81" t="s">
         <v>28</v>
       </c>
@@ -12086,7 +12052,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="A82" t="s">
         <v>28</v>
       </c>
@@ -12118,7 +12084,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="A83" t="s">
         <v>28</v>
       </c>
@@ -12150,7 +12116,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="A84" t="s">
         <v>28</v>
       </c>
@@ -12182,7 +12148,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85">
       <c r="A85" t="s">
         <v>28</v>
       </c>
@@ -12214,7 +12180,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86">
       <c r="A86" t="s">
         <v>28</v>
       </c>
@@ -12246,7 +12212,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87">
       <c r="A87" t="s">
         <v>28</v>
       </c>
@@ -12278,7 +12244,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88">
       <c r="A88" t="s">
         <v>28</v>
       </c>
@@ -12310,7 +12276,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89">
       <c r="A89" t="s">
         <v>35</v>
       </c>
@@ -12342,7 +12308,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90">
       <c r="A90" t="s">
         <v>35</v>
       </c>
@@ -12374,7 +12340,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91">
       <c r="A91" t="s">
         <v>35</v>
       </c>
@@ -12406,7 +12372,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92">
       <c r="A92" t="s">
         <v>35</v>
       </c>
@@ -12438,7 +12404,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93">
       <c r="A93" t="s">
         <v>35</v>
       </c>
@@ -12470,7 +12436,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94">
       <c r="A94" t="s">
         <v>35</v>
       </c>
@@ -12502,7 +12468,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95">
       <c r="A95" t="s">
         <v>35</v>
       </c>
@@ -12534,7 +12500,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96">
       <c r="A96" t="s">
         <v>35</v>
       </c>
@@ -12566,7 +12532,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97">
       <c r="A97" t="s">
         <v>35</v>
       </c>
@@ -12598,7 +12564,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98">
       <c r="A98" t="s">
         <v>35</v>
       </c>
@@ -12630,7 +12596,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99">
       <c r="A99" t="s">
         <v>35</v>
       </c>
@@ -12662,7 +12628,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100">
       <c r="A100" t="s">
         <v>35</v>
       </c>
@@ -12694,7 +12660,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101">
       <c r="A101" t="s">
         <v>35</v>
       </c>
@@ -12726,7 +12692,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102">
       <c r="A102" t="s">
         <v>35</v>
       </c>
@@ -12758,7 +12724,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103">
       <c r="A103" t="s">
         <v>42</v>
       </c>
@@ -12790,7 +12756,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104">
       <c r="A104" t="s">
         <v>42</v>
       </c>
@@ -12822,7 +12788,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105">
       <c r="A105" t="s">
         <v>42</v>
       </c>
@@ -12854,7 +12820,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106">
       <c r="A106" t="s">
         <v>42</v>
       </c>
@@ -12886,7 +12852,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107">
       <c r="A107" t="s">
         <v>42</v>
       </c>
@@ -12919,8 +12885,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>